--- a/00.data/01.incertezas/Global_Policy_Uncertainty_Data.xlsx
+++ b/00.data/01.incertezas/Global_Policy_Uncertainty_Data.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29328"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kms12\Documents\R\EPU\Monthly Files\2025-10-16\Submission 2025-10-21\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kms12\Documents\R\EPU\Monthly Files\2025-11-17\Submission 2025-11-21\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1EA5A9F4-4C56-4A71-B168-FB8BEA3836A0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6FA747CA-6362-453B-801B-D1A06A97AA11}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -426,7 +426,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D348"/>
+  <dimension ref="A1:D349"/>
   <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.3">
@@ -451,10 +451,10 @@
         <v>1</v>
       </c>
       <c r="C2">
-        <v>75.585468467290752</v>
+        <v>75.741271974917922</v>
       </c>
       <c r="D2">
-        <v>78.571180724215637</v>
+        <v>78.956962338546234</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.3">
@@ -465,10 +465,10 @@
         <v>2</v>
       </c>
       <c r="C3">
-        <v>76.104191634932121</v>
+        <v>76.076042743994904</v>
       </c>
       <c r="D3">
-        <v>75.664772595555306</v>
+        <v>75.59514446381327</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.3">
@@ -479,10 +479,10 @@
         <v>3</v>
       </c>
       <c r="C4">
-        <v>66.568757405486039</v>
+        <v>66.713953414947468</v>
       </c>
       <c r="D4">
-        <v>64.209641320864947</v>
+        <v>64.571995448278926</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.3">
@@ -493,10 +493,10 @@
         <v>4</v>
       </c>
       <c r="C5">
-        <v>71.689527290212055</v>
+        <v>71.674360425624855</v>
       </c>
       <c r="D5">
-        <v>71.701272714045288</v>
+        <v>71.665830735704347</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.3">
@@ -507,10 +507,10 @@
         <v>5</v>
       </c>
       <c r="C6">
-        <v>75.359956878982587</v>
+        <v>75.49898252954236</v>
       </c>
       <c r="D6">
-        <v>82.298049582334741</v>
+        <v>82.644865614066916</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.3">
@@ -521,10 +521,10 @@
         <v>6</v>
       </c>
       <c r="C7">
-        <v>79.496588375325189</v>
+        <v>79.464736680604275</v>
       </c>
       <c r="D7">
-        <v>83.000373581312658</v>
+        <v>82.923131972643333</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.3">
@@ -535,10 +535,10 @@
         <v>7</v>
       </c>
       <c r="C8">
-        <v>66.037545253758339</v>
+        <v>66.059779564206423</v>
       </c>
       <c r="D8">
-        <v>66.414801683480221</v>
+        <v>66.468540431614869</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.3">
@@ -549,10 +549,10 @@
         <v>8</v>
       </c>
       <c r="C9">
-        <v>62.784866919034656</v>
+        <v>62.882588072218006</v>
       </c>
       <c r="D9">
-        <v>57.952762308742578</v>
+        <v>58.197200450363866</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.3">
@@ -563,10 +563,10 @@
         <v>9</v>
       </c>
       <c r="C10">
-        <v>65.85963166387377</v>
+        <v>66.022761864324622</v>
       </c>
       <c r="D10">
-        <v>60.651293172159754</v>
+        <v>61.058892961155038</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.3">
@@ -577,10 +577,10 @@
         <v>10</v>
       </c>
       <c r="C11">
-        <v>81.6606993376286</v>
+        <v>81.711155273417205</v>
       </c>
       <c r="D11">
-        <v>75.950659920478358</v>
+        <v>76.079478789908848</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.3">
@@ -591,10 +591,10 @@
         <v>11</v>
       </c>
       <c r="C12">
-        <v>93.201897109725252</v>
+        <v>93.562786052259213</v>
       </c>
       <c r="D12">
-        <v>83.950289238710653</v>
+        <v>84.848888510154637</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.3">
@@ -605,10 +605,10 @@
         <v>12</v>
       </c>
       <c r="C13">
-        <v>104.5351075645451</v>
+        <v>104.86962521486274</v>
       </c>
       <c r="D13">
-        <v>92.459980529137582</v>
+        <v>93.288841785802319</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.3">
@@ -619,10 +619,10 @@
         <v>1</v>
       </c>
       <c r="C14">
-        <v>95.097440150427346</v>
+        <v>95.486482633788128</v>
       </c>
       <c r="D14">
-        <v>88.1445689993093</v>
+        <v>89.091089046791879</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.3">
@@ -633,10 +633,10 @@
         <v>2</v>
       </c>
       <c r="C15">
-        <v>81.993069395063131</v>
+        <v>82.305402880717622</v>
       </c>
       <c r="D15">
-        <v>75.63332218241041</v>
+        <v>76.394379378260453</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.3">
@@ -647,10 +647,10 @@
         <v>3</v>
       </c>
       <c r="C16">
-        <v>83.661263702291023</v>
+        <v>83.904021815981707</v>
       </c>
       <c r="D16">
-        <v>76.085118317501639</v>
+        <v>76.678629226405391</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.3">
@@ -661,10 +661,10 @@
         <v>4</v>
       </c>
       <c r="C17">
-        <v>77.991060295727891</v>
+        <v>78.404300080683782</v>
       </c>
       <c r="D17">
-        <v>71.303680642765627</v>
+        <v>72.315120241281676</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.3">
@@ -675,10 +675,10 @@
         <v>5</v>
       </c>
       <c r="C18">
-        <v>84.535942632330034</v>
+        <v>84.88282871996428</v>
       </c>
       <c r="D18">
-        <v>77.8988796701544</v>
+        <v>78.74670606033294</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.3">
@@ -689,10 +689,10 @@
         <v>6</v>
       </c>
       <c r="C19">
-        <v>82.253966081416465</v>
+        <v>82.59879531237199</v>
       </c>
       <c r="D19">
-        <v>76.072200144927976</v>
+        <v>76.913655011295972</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.3">
@@ -703,10 +703,10 @@
         <v>7</v>
       </c>
       <c r="C20">
-        <v>99.306226756332975</v>
+        <v>99.661022668137235</v>
       </c>
       <c r="D20">
-        <v>91.770591197924119</v>
+        <v>92.634730937769731</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.3">
@@ -717,10 +717,10 @@
         <v>8</v>
       </c>
       <c r="C21">
-        <v>112.50158291033887</v>
+        <v>112.88676109434741</v>
       </c>
       <c r="D21">
-        <v>103.0937688080636</v>
+        <v>104.03405217450583</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.3">
@@ -731,10 +731,10 @@
         <v>9</v>
       </c>
       <c r="C22">
-        <v>143.52536533238219</v>
+        <v>143.43068625949803</v>
       </c>
       <c r="D22">
-        <v>142.68581398014015</v>
+        <v>142.45621416166168</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.3">
@@ -745,10 +745,10 @@
         <v>10</v>
       </c>
       <c r="C23">
-        <v>116.95169058861013</v>
+        <v>117.28978490824011</v>
       </c>
       <c r="D23">
-        <v>108.06888720198313</v>
+        <v>108.8959631388216</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.3">
@@ -759,10 +759,10 @@
         <v>11</v>
       </c>
       <c r="C24">
-        <v>96.815928335961246</v>
+        <v>96.897584529865966</v>
       </c>
       <c r="D24">
-        <v>90.071614227082492</v>
+        <v>90.270998857486489</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.3">
@@ -773,10 +773,10 @@
         <v>12</v>
       </c>
       <c r="C25">
-        <v>91.425728101479365</v>
+        <v>91.497155512588549</v>
       </c>
       <c r="D25">
-        <v>88.970842940219782</v>
+        <v>89.142614723016663</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.3">
@@ -787,10 +787,10 @@
         <v>1</v>
       </c>
       <c r="C26">
-        <v>94.695194009687313</v>
+        <v>94.613555897534269</v>
       </c>
       <c r="D26">
-        <v>91.49401821271482</v>
+        <v>91.292705367495302</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.3">
@@ -801,10 +801,10 @@
         <v>2</v>
       </c>
       <c r="C27">
-        <v>78.422000836515849</v>
+        <v>78.375353224557017</v>
       </c>
       <c r="D27">
-        <v>74.697052247642077</v>
+        <v>74.581348825718038</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.3">
@@ -815,10 +815,10 @@
         <v>3</v>
       </c>
       <c r="C28">
-        <v>61.880852797032709</v>
+        <v>61.848730858458445</v>
       </c>
       <c r="D28">
-        <v>56.51740925169905</v>
+        <v>56.437649029044834</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.3">
@@ -829,10 +829,10 @@
         <v>4</v>
       </c>
       <c r="C29">
-        <v>65.058784928009956</v>
+        <v>65.0666578411807</v>
       </c>
       <c r="D29">
-        <v>63.242179647005145</v>
+        <v>63.263372900847777</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.3">
@@ -843,10 +843,10 @@
         <v>5</v>
       </c>
       <c r="C30">
-        <v>68.463228898915091</v>
+        <v>68.581072312852143</v>
       </c>
       <c r="D30">
-        <v>67.152366078247852</v>
+        <v>67.442301378869828</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.3">
@@ -857,10 +857,10 @@
         <v>6</v>
       </c>
       <c r="C31">
-        <v>69.74847081060912</v>
+        <v>69.730600844356886</v>
       </c>
       <c r="D31">
-        <v>66.872818634470988</v>
+        <v>66.828817347899331</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.3">
@@ -871,10 +871,10 @@
         <v>7</v>
       </c>
       <c r="C32">
-        <v>71.8381628661147</v>
+        <v>71.759326676688787</v>
       </c>
       <c r="D32">
-        <v>70.108201077815082</v>
+        <v>69.911706624109186</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.3">
@@ -885,10 +885,10 @@
         <v>8</v>
       </c>
       <c r="C33">
-        <v>64.947245444260886</v>
+        <v>64.838825179004175</v>
       </c>
       <c r="D33">
-        <v>67.849251051870311</v>
+        <v>67.58128577468824</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.3">
@@ -899,10 +899,10 @@
         <v>9</v>
       </c>
       <c r="C34">
-        <v>65.683290509758578</v>
+        <v>65.664987011020742</v>
       </c>
       <c r="D34">
-        <v>61.481585300085015</v>
+        <v>61.436560592437942</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.3">
@@ -913,10 +913,10 @@
         <v>10</v>
       </c>
       <c r="C35">
-        <v>65.370103255852953</v>
+        <v>65.329385570292928</v>
       </c>
       <c r="D35">
-        <v>66.062174621213856</v>
+        <v>65.961620630961846</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.3">
@@ -927,10 +927,10 @@
         <v>11</v>
       </c>
       <c r="C36">
-        <v>68.055878706936113</v>
+        <v>67.988962847201478</v>
       </c>
       <c r="D36">
-        <v>65.045779942671871</v>
+        <v>64.880002960339056</v>
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.3">
@@ -941,10 +941,10 @@
         <v>12</v>
       </c>
       <c r="C37">
-        <v>60.750952090381958</v>
+        <v>60.791443824699634</v>
       </c>
       <c r="D37">
-        <v>57.752033008152239</v>
+        <v>57.849748743464836</v>
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.3">
@@ -955,10 +955,10 @@
         <v>1</v>
       </c>
       <c r="C38">
-        <v>65.282606464068508</v>
+        <v>65.26429532311559</v>
       </c>
       <c r="D38">
-        <v>66.405312285478132</v>
+        <v>66.361770280124475</v>
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.3">
@@ -969,10 +969,10 @@
         <v>2</v>
       </c>
       <c r="C39">
-        <v>59.307426757865329</v>
+        <v>59.302564206118653</v>
       </c>
       <c r="D39">
-        <v>55.576822457587163</v>
+        <v>55.56510488772031</v>
       </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.3">
@@ -983,10 +983,10 @@
         <v>3</v>
       </c>
       <c r="C40">
-        <v>61.968276707393557</v>
+        <v>61.953916818540655</v>
       </c>
       <c r="D40">
-        <v>60.558732130534267</v>
+        <v>60.524437341035785</v>
       </c>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.3">
@@ -997,10 +997,10 @@
         <v>4</v>
       </c>
       <c r="C41">
-        <v>64.58891296605546</v>
+        <v>64.579859732348737</v>
       </c>
       <c r="D41">
-        <v>61.630697194711239</v>
+        <v>61.609651227572165</v>
       </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.3">
@@ -1011,10 +1011,10 @@
         <v>5</v>
       </c>
       <c r="C42">
-        <v>85.838279146660142</v>
+        <v>85.828628393036183</v>
       </c>
       <c r="D42">
-        <v>81.436330762810186</v>
+        <v>81.413188620036493</v>
       </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.3">
@@ -1025,10 +1025,10 @@
         <v>6</v>
       </c>
       <c r="C43">
-        <v>89.207361876072227</v>
+        <v>89.195279047981586</v>
       </c>
       <c r="D43">
-        <v>85.218310714618781</v>
+        <v>85.187133087690512</v>
       </c>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.3">
@@ -1039,10 +1039,10 @@
         <v>7</v>
       </c>
       <c r="C44">
-        <v>67.347985966079477</v>
+        <v>67.335125022949626</v>
       </c>
       <c r="D44">
-        <v>63.43967656618085</v>
+        <v>63.40839146880375</v>
       </c>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.3">
@@ -1053,10 +1053,10 @@
         <v>8</v>
       </c>
       <c r="C45">
-        <v>54.472746821526727</v>
+        <v>54.464186431620753</v>
       </c>
       <c r="D45">
-        <v>52.810097886527949</v>
+        <v>52.789840192965059</v>
       </c>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.3">
@@ -1067,10 +1067,10 @@
         <v>9</v>
       </c>
       <c r="C46">
-        <v>60.737612803044989</v>
+        <v>60.727859792997876</v>
       </c>
       <c r="D46">
-        <v>61.684008110877393</v>
+        <v>61.660764538394368</v>
       </c>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.3">
@@ -1081,10 +1081,10 @@
         <v>10</v>
       </c>
       <c r="C47">
-        <v>68.83145865215505</v>
+        <v>68.818372297765009</v>
       </c>
       <c r="D47">
-        <v>67.746849060602699</v>
+        <v>67.715651680325394</v>
       </c>
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.3">
@@ -1095,10 +1095,10 @@
         <v>11</v>
       </c>
       <c r="C48">
-        <v>104.56230909231985</v>
+        <v>104.55919709819041</v>
       </c>
       <c r="D48">
-        <v>93.841561087458203</v>
+        <v>93.834101541392684</v>
       </c>
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.3">
@@ -1109,10 +1109,10 @@
         <v>12</v>
       </c>
       <c r="C49">
-        <v>100.82106674659708</v>
+        <v>100.80643184348025</v>
       </c>
       <c r="D49">
-        <v>94.691399980880973</v>
+        <v>94.655840948819758</v>
       </c>
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.3">
@@ -1123,10 +1123,10 @@
         <v>1</v>
       </c>
       <c r="C50">
-        <v>99.234223998031609</v>
+        <v>99.216299060737285</v>
       </c>
       <c r="D50">
-        <v>93.389403546677244</v>
+        <v>93.348563200213178</v>
       </c>
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.3">
@@ -1137,10 +1137,10 @@
         <v>2</v>
       </c>
       <c r="C51">
-        <v>99.967007681646422</v>
+        <v>99.95321108586576</v>
       </c>
       <c r="D51">
-        <v>93.619537854435407</v>
+        <v>93.5879803245857</v>
       </c>
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.3">
@@ -1151,10 +1151,10 @@
         <v>3</v>
       </c>
       <c r="C52">
-        <v>112.17185780885319</v>
+        <v>112.15196178453434</v>
       </c>
       <c r="D52">
-        <v>104.13188998692254</v>
+        <v>104.08670423544652</v>
       </c>
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.3">
@@ -1165,10 +1165,10 @@
         <v>4</v>
       </c>
       <c r="C53">
-        <v>107.03171968667128</v>
+        <v>107.02347144131578</v>
       </c>
       <c r="D53">
-        <v>95.979752621552365</v>
+        <v>95.959881268817881</v>
       </c>
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.3">
@@ -1179,10 +1179,10 @@
         <v>5</v>
       </c>
       <c r="C54">
-        <v>82.960721575984024</v>
+        <v>82.950789716204781</v>
       </c>
       <c r="D54">
-        <v>76.249077872349972</v>
+        <v>76.227253937215011</v>
       </c>
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.3">
@@ -1193,10 +1193,10 @@
         <v>6</v>
       </c>
       <c r="C55">
-        <v>74.098995628868792</v>
+        <v>74.085197568082762</v>
       </c>
       <c r="D55">
-        <v>70.414411253941225</v>
+        <v>70.382551445700969</v>
       </c>
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.3">
@@ -1207,10 +1207,10 @@
         <v>7</v>
       </c>
       <c r="C56">
-        <v>97.396699273581945</v>
+        <v>97.386014075993316</v>
       </c>
       <c r="D56">
-        <v>89.339135399396469</v>
+        <v>89.315377227686312</v>
       </c>
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.3">
@@ -1221,10 +1221,10 @@
         <v>8</v>
       </c>
       <c r="C57">
-        <v>82.608107303243187</v>
+        <v>82.594543443486856</v>
       </c>
       <c r="D57">
-        <v>78.65587821853363</v>
+        <v>78.625569002556261</v>
       </c>
     </row>
     <row r="58" spans="1:4" x14ac:dyDescent="0.3">
@@ -1235,10 +1235,10 @@
         <v>9</v>
       </c>
       <c r="C58">
-        <v>174.99224774086284</v>
+        <v>174.97706150021304</v>
       </c>
       <c r="D58">
-        <v>157.90030349227098</v>
+        <v>157.86632351885626</v>
       </c>
     </row>
     <row r="59" spans="1:4" x14ac:dyDescent="0.3">
@@ -1249,10 +1249,10 @@
         <v>10</v>
       </c>
       <c r="C59">
-        <v>163.70517792606978</v>
+        <v>163.6873969752921</v>
       </c>
       <c r="D59">
-        <v>149.69514381551471</v>
+        <v>149.65525801828673</v>
       </c>
     </row>
     <row r="60" spans="1:4" x14ac:dyDescent="0.3">
@@ -1263,10 +1263,10 @@
         <v>11</v>
       </c>
       <c r="C60">
-        <v>123.76772292311455</v>
+        <v>123.74895249709455</v>
       </c>
       <c r="D60">
-        <v>116.22299254024315</v>
+        <v>116.18126533469467</v>
       </c>
     </row>
     <row r="61" spans="1:4" x14ac:dyDescent="0.3">
@@ -1277,10 +1277,10 @@
         <v>12</v>
       </c>
       <c r="C61">
-        <v>106.27107879060475</v>
+        <v>106.24967153560777</v>
       </c>
       <c r="D61">
-        <v>100.62598934847722</v>
+        <v>100.57844336403146</v>
       </c>
     </row>
     <row r="62" spans="1:4" x14ac:dyDescent="0.3">
@@ -1291,10 +1291,10 @@
         <v>1</v>
       </c>
       <c r="C62">
-        <v>104.13182671465928</v>
+        <v>104.10876727013027</v>
       </c>
       <c r="D62">
-        <v>99.571308490765603</v>
+        <v>99.519537095862063</v>
       </c>
     </row>
     <row r="63" spans="1:4" x14ac:dyDescent="0.3">
@@ -1305,10 +1305,10 @@
         <v>2</v>
       </c>
       <c r="C63">
-        <v>86.329636826171679</v>
+        <v>86.314764573232793</v>
       </c>
       <c r="D63">
-        <v>80.794132859426597</v>
+        <v>80.760350683622733</v>
       </c>
     </row>
     <row r="64" spans="1:4" x14ac:dyDescent="0.3">
@@ -1319,10 +1319,10 @@
         <v>3</v>
       </c>
       <c r="C64">
-        <v>76.843425173926875</v>
+        <v>76.823632845254565</v>
       </c>
       <c r="D64">
-        <v>74.635885452442892</v>
+        <v>74.591100086801347</v>
       </c>
     </row>
     <row r="65" spans="1:4" x14ac:dyDescent="0.3">
@@ -1333,10 +1333,10 @@
         <v>4</v>
       </c>
       <c r="C65">
-        <v>81.842045099514024</v>
+        <v>81.825405387532726</v>
       </c>
       <c r="D65">
-        <v>79.169114628386296</v>
+        <v>79.131244989375872</v>
       </c>
     </row>
     <row r="66" spans="1:4" x14ac:dyDescent="0.3">
@@ -1347,10 +1347,10 @@
         <v>5</v>
       </c>
       <c r="C66">
-        <v>80.100298287036424</v>
+        <v>80.083482714086387</v>
       </c>
       <c r="D66">
-        <v>78.005371315046062</v>
+        <v>77.966731288645846</v>
       </c>
     </row>
     <row r="67" spans="1:4" x14ac:dyDescent="0.3">
@@ -1361,10 +1361,10 @@
         <v>6</v>
       </c>
       <c r="C67">
-        <v>91.968151640805544</v>
+        <v>91.957544118240477</v>
       </c>
       <c r="D67">
-        <v>88.865277640280027</v>
+        <v>88.840467065699883</v>
       </c>
     </row>
     <row r="68" spans="1:4" x14ac:dyDescent="0.3">
@@ -1375,10 +1375,10 @@
         <v>7</v>
       </c>
       <c r="C68">
-        <v>99.871486801947071</v>
+        <v>99.851642861998101</v>
       </c>
       <c r="D68">
-        <v>94.100676060510608</v>
+        <v>94.055731628433648</v>
       </c>
     </row>
     <row r="69" spans="1:4" x14ac:dyDescent="0.3">
@@ -1389,10 +1389,10 @@
         <v>8</v>
       </c>
       <c r="C69">
-        <v>104.3799144030003</v>
+        <v>104.36415652958401</v>
       </c>
       <c r="D69">
-        <v>98.694837109703073</v>
+        <v>98.658565473958234</v>
       </c>
     </row>
     <row r="70" spans="1:4" x14ac:dyDescent="0.3">
@@ -1403,10 +1403,10 @@
         <v>9</v>
       </c>
       <c r="C70">
-        <v>119.32246799613887</v>
+        <v>119.30208016201752</v>
       </c>
       <c r="D70">
-        <v>113.87617666245835</v>
+        <v>113.83021082902694</v>
       </c>
     </row>
     <row r="71" spans="1:4" x14ac:dyDescent="0.3">
@@ -1417,10 +1417,10 @@
         <v>10</v>
       </c>
       <c r="C71">
-        <v>115.11689618896469</v>
+        <v>115.09632039492662</v>
       </c>
       <c r="D71">
-        <v>113.18791986382824</v>
+        <v>113.14112637942536</v>
       </c>
     </row>
     <row r="72" spans="1:4" x14ac:dyDescent="0.3">
@@ -1431,10 +1431,10 @@
         <v>11</v>
       </c>
       <c r="C72">
-        <v>121.30231727139063</v>
+        <v>121.2803413704422</v>
       </c>
       <c r="D72">
-        <v>114.43439248846485</v>
+        <v>114.38480041804431</v>
       </c>
     </row>
     <row r="73" spans="1:4" x14ac:dyDescent="0.3">
@@ -1445,10 +1445,10 @@
         <v>12</v>
       </c>
       <c r="C73">
-        <v>119.650912124477</v>
+        <v>119.61762104177213</v>
       </c>
       <c r="D73">
-        <v>115.98980722981017</v>
+        <v>115.91450090188592</v>
       </c>
     </row>
     <row r="74" spans="1:4" x14ac:dyDescent="0.3">
@@ -1459,10 +1459,10 @@
         <v>1</v>
       </c>
       <c r="C74">
-        <v>125.74509050269135</v>
+        <v>125.72825392086349</v>
       </c>
       <c r="D74">
-        <v>113.27802180499552</v>
+        <v>113.23760649377601</v>
       </c>
     </row>
     <row r="75" spans="1:4" x14ac:dyDescent="0.3">
@@ -1473,10 +1473,10 @@
         <v>2</v>
       </c>
       <c r="C75">
-        <v>134.79193311474361</v>
+        <v>134.78164906361948</v>
       </c>
       <c r="D75">
-        <v>122.6962068545575</v>
+        <v>122.67165175404271</v>
       </c>
     </row>
     <row r="76" spans="1:4" x14ac:dyDescent="0.3">
@@ -1487,10 +1487,10 @@
         <v>3</v>
       </c>
       <c r="C76">
-        <v>167.66774285195254</v>
+        <v>167.64179719519376</v>
       </c>
       <c r="D76">
-        <v>155.0111181696256</v>
+        <v>154.94883124591124</v>
       </c>
     </row>
     <row r="77" spans="1:4" x14ac:dyDescent="0.3">
@@ -1501,10 +1501,10 @@
         <v>4</v>
       </c>
       <c r="C77">
-        <v>136.21120412991505</v>
+        <v>136.17379935542564</v>
       </c>
       <c r="D77">
-        <v>130.49876926619871</v>
+        <v>130.40963813715462</v>
       </c>
     </row>
     <row r="78" spans="1:4" x14ac:dyDescent="0.3">
@@ -1515,10 +1515,10 @@
         <v>5</v>
       </c>
       <c r="C78">
-        <v>106.37803413685992</v>
+        <v>106.35312377094233</v>
       </c>
       <c r="D78">
-        <v>101.73539192318086</v>
+        <v>101.67527236480038</v>
       </c>
     </row>
     <row r="79" spans="1:4" x14ac:dyDescent="0.3">
@@ -1529,10 +1529,10 @@
         <v>6</v>
       </c>
       <c r="C79">
-        <v>88.894691432896536</v>
+        <v>88.874366577549821</v>
       </c>
       <c r="D79">
-        <v>82.560563383811441</v>
+        <v>82.512261577475172</v>
       </c>
     </row>
     <row r="80" spans="1:4" x14ac:dyDescent="0.3">
@@ -1543,10 +1543,10 @@
         <v>7</v>
       </c>
       <c r="C80">
-        <v>80.635059567811027</v>
+        <v>80.6042365435015</v>
       </c>
       <c r="D80">
-        <v>82.637177855357521</v>
+        <v>82.56268589989422</v>
       </c>
     </row>
     <row r="81" spans="1:4" x14ac:dyDescent="0.3">
@@ -1557,10 +1557,10 @@
         <v>8</v>
       </c>
       <c r="C81">
-        <v>69.287322026450127</v>
+        <v>69.264723904202555</v>
       </c>
       <c r="D81">
-        <v>71.278191415885587</v>
+        <v>71.224510445060901</v>
       </c>
     </row>
     <row r="82" spans="1:4" x14ac:dyDescent="0.3">
@@ -1571,10 +1571,10 @@
         <v>9</v>
       </c>
       <c r="C82">
-        <v>80.198351894632651</v>
+        <v>80.180830002876036</v>
       </c>
       <c r="D82">
-        <v>76.247358426521913</v>
+        <v>76.204235513587733</v>
       </c>
     </row>
     <row r="83" spans="1:4" x14ac:dyDescent="0.3">
@@ -1585,10 +1585,10 @@
         <v>10</v>
       </c>
       <c r="C83">
-        <v>76.365209126162654</v>
+        <v>76.342662612994701</v>
       </c>
       <c r="D83">
-        <v>78.386804541345086</v>
+        <v>78.332028901963767</v>
       </c>
     </row>
     <row r="84" spans="1:4" x14ac:dyDescent="0.3">
@@ -1599,10 +1599,10 @@
         <v>11</v>
       </c>
       <c r="C84">
-        <v>73.770080362747009</v>
+        <v>73.756235787073308</v>
       </c>
       <c r="D84">
-        <v>75.241238677578338</v>
+        <v>75.207438526504106</v>
       </c>
     </row>
     <row r="85" spans="1:4" x14ac:dyDescent="0.3">
@@ -1613,10 +1613,10 @@
         <v>12</v>
       </c>
       <c r="C85">
-        <v>70.266222052200703</v>
+        <v>70.246752894268894</v>
       </c>
       <c r="D85">
-        <v>69.947161437700785</v>
+        <v>69.900595219219753</v>
       </c>
     </row>
     <row r="86" spans="1:4" x14ac:dyDescent="0.3">
@@ -1627,10 +1627,10 @@
         <v>1</v>
       </c>
       <c r="C86">
-        <v>72.327634508077566</v>
+        <v>72.306003728001912</v>
       </c>
       <c r="D86">
-        <v>76.781159366381615</v>
+        <v>76.729604645015513</v>
       </c>
     </row>
     <row r="87" spans="1:4" x14ac:dyDescent="0.3">
@@ -1641,10 +1641,10 @@
         <v>2</v>
       </c>
       <c r="C87">
-        <v>72.543554015630363</v>
+        <v>72.52157832623783</v>
       </c>
       <c r="D87">
-        <v>79.627588119362059</v>
+        <v>79.574678355574065</v>
       </c>
     </row>
     <row r="88" spans="1:4" x14ac:dyDescent="0.3">
@@ -1655,10 +1655,10 @@
         <v>3</v>
       </c>
       <c r="C88">
-        <v>77.941957597483253</v>
+        <v>77.923399752810198</v>
       </c>
       <c r="D88">
-        <v>75.03600589485724</v>
+        <v>74.991797178746992</v>
       </c>
     </row>
     <row r="89" spans="1:4" x14ac:dyDescent="0.3">
@@ -1669,10 +1669,10 @@
         <v>4</v>
       </c>
       <c r="C89">
-        <v>77.717233176990661</v>
+        <v>77.694399210345324</v>
       </c>
       <c r="D89">
-        <v>79.768900667797141</v>
+        <v>79.71451570607465</v>
       </c>
     </row>
     <row r="90" spans="1:4" x14ac:dyDescent="0.3">
@@ -1683,10 +1683,10 @@
         <v>5</v>
       </c>
       <c r="C90">
-        <v>89.326962402139515</v>
+        <v>89.312722630667608</v>
       </c>
       <c r="D90">
-        <v>94.438241070989719</v>
+        <v>94.404070347978134</v>
       </c>
     </row>
     <row r="91" spans="1:4" x14ac:dyDescent="0.3">
@@ -1697,10 +1697,10 @@
         <v>6</v>
       </c>
       <c r="C91">
-        <v>77.419368254039028</v>
+        <v>77.400231302055545</v>
       </c>
       <c r="D91">
-        <v>77.996027947968983</v>
+        <v>77.949313547690139</v>
       </c>
     </row>
     <row r="92" spans="1:4" x14ac:dyDescent="0.3">
@@ -1711,10 +1711,10 @@
         <v>7</v>
       </c>
       <c r="C92">
-        <v>74.688711569898743</v>
+        <v>74.67048544760739</v>
       </c>
       <c r="D92">
-        <v>71.939613721937903</v>
+        <v>71.895974191386699</v>
       </c>
     </row>
     <row r="93" spans="1:4" x14ac:dyDescent="0.3">
@@ -1725,10 +1725,10 @@
         <v>8</v>
       </c>
       <c r="C93">
-        <v>68.752327314962571</v>
+        <v>68.73517108160722</v>
       </c>
       <c r="D93">
-        <v>67.810010825503767</v>
+        <v>67.769108892345301</v>
       </c>
     </row>
     <row r="94" spans="1:4" x14ac:dyDescent="0.3">
@@ -1739,10 +1739,10 @@
         <v>9</v>
       </c>
       <c r="C94">
-        <v>78.029839591510196</v>
+        <v>78.016656002505911</v>
       </c>
       <c r="D94">
-        <v>74.02283791029636</v>
+        <v>73.991043208792789</v>
       </c>
     </row>
     <row r="95" spans="1:4" x14ac:dyDescent="0.3">
@@ -1753,10 +1753,10 @@
         <v>10</v>
       </c>
       <c r="C95">
-        <v>89.039254325823848</v>
+        <v>89.01513790143153</v>
       </c>
       <c r="D95">
-        <v>88.972105007277889</v>
+        <v>88.914887543513629</v>
       </c>
     </row>
     <row r="96" spans="1:4" x14ac:dyDescent="0.3">
@@ -1767,10 +1767,10 @@
         <v>11</v>
       </c>
       <c r="C96">
-        <v>84.103702616951125</v>
+        <v>84.084835377592427</v>
       </c>
       <c r="D96">
-        <v>80.455436407781903</v>
+        <v>80.410519724177746</v>
       </c>
     </row>
     <row r="97" spans="1:4" x14ac:dyDescent="0.3">
@@ -1781,10 +1781,10 @@
         <v>12</v>
       </c>
       <c r="C97">
-        <v>65.558151676111962</v>
+        <v>65.529927145519721</v>
       </c>
       <c r="D97">
-        <v>67.885880888706268</v>
+        <v>67.818390775672285</v>
       </c>
     </row>
     <row r="98" spans="1:4" x14ac:dyDescent="0.3">
@@ -1795,10 +1795,10 @@
         <v>1</v>
       </c>
       <c r="C98">
-        <v>57.949295276846811</v>
+        <v>57.928471982838623</v>
       </c>
       <c r="D98">
-        <v>64.206325831488115</v>
+        <v>64.158296141692304</v>
       </c>
     </row>
     <row r="99" spans="1:4" x14ac:dyDescent="0.3">
@@ -1809,10 +1809,10 @@
         <v>2</v>
       </c>
       <c r="C99">
-        <v>55.204438885205136</v>
+        <v>55.187655537309354</v>
       </c>
       <c r="D99">
-        <v>58.088694408555298</v>
+        <v>58.049763571554614</v>
       </c>
     </row>
     <row r="100" spans="1:4" x14ac:dyDescent="0.3">
@@ -1823,10 +1823,10 @@
         <v>3</v>
       </c>
       <c r="C100">
-        <v>53.244632894239267</v>
+        <v>53.226919907999473</v>
       </c>
       <c r="D100">
-        <v>56.303500503513312</v>
+        <v>56.262886237224464</v>
       </c>
     </row>
     <row r="101" spans="1:4" x14ac:dyDescent="0.3">
@@ -1837,10 +1837,10 @@
         <v>4</v>
       </c>
       <c r="C101">
-        <v>70.876125919950397</v>
+        <v>70.842665439278235</v>
       </c>
       <c r="D101">
-        <v>76.305033946053811</v>
+        <v>76.227136955251396</v>
       </c>
     </row>
     <row r="102" spans="1:4" x14ac:dyDescent="0.3">
@@ -1851,10 +1851,10 @@
         <v>5</v>
       </c>
       <c r="C102">
-        <v>67.570059898875726</v>
+        <v>67.560138267198965</v>
       </c>
       <c r="D102">
-        <v>63.991709424755783</v>
+        <v>63.968503658058665</v>
       </c>
     </row>
     <row r="103" spans="1:4" x14ac:dyDescent="0.3">
@@ -1865,10 +1865,10 @@
         <v>6</v>
       </c>
       <c r="C103">
-        <v>70.904812727931997</v>
+        <v>70.884755955470524</v>
       </c>
       <c r="D103">
-        <v>71.58625175209211</v>
+        <v>71.540138273339082</v>
       </c>
     </row>
     <row r="104" spans="1:4" x14ac:dyDescent="0.3">
@@ -1879,10 +1879,10 @@
         <v>7</v>
       </c>
       <c r="C104">
-        <v>63.182374668204417</v>
+        <v>63.156059400822762</v>
       </c>
       <c r="D104">
-        <v>64.888900037881143</v>
+        <v>64.828271432721664</v>
       </c>
     </row>
     <row r="105" spans="1:4" x14ac:dyDescent="0.3">
@@ -1893,10 +1893,10 @@
         <v>8</v>
       </c>
       <c r="C105">
-        <v>61.627839995374359</v>
+        <v>61.602579998646398</v>
       </c>
       <c r="D105">
-        <v>63.096255539764456</v>
+        <v>63.037839434542462</v>
       </c>
     </row>
     <row r="106" spans="1:4" x14ac:dyDescent="0.3">
@@ -1907,10 +1907,10 @@
         <v>9</v>
       </c>
       <c r="C106">
-        <v>94.149054808169197</v>
+        <v>94.119182407570918</v>
       </c>
       <c r="D106">
-        <v>92.224900050288198</v>
+        <v>92.156031063569827</v>
       </c>
     </row>
     <row r="107" spans="1:4" x14ac:dyDescent="0.3">
@@ -1921,10 +1921,10 @@
         <v>10</v>
       </c>
       <c r="C107">
-        <v>66.11988181768487</v>
+        <v>66.097850049160272</v>
       </c>
       <c r="D107">
-        <v>68.603982159925025</v>
+        <v>68.552573636736895</v>
       </c>
     </row>
     <row r="108" spans="1:4" x14ac:dyDescent="0.3">
@@ -1935,10 +1935,10 @@
         <v>11</v>
       </c>
       <c r="C108">
-        <v>66.62782648274019</v>
+        <v>66.613204119469458</v>
       </c>
       <c r="D108">
-        <v>64.453809190824629</v>
+        <v>64.41922156653618</v>
       </c>
     </row>
     <row r="109" spans="1:4" x14ac:dyDescent="0.3">
@@ -1949,10 +1949,10 @@
         <v>12</v>
       </c>
       <c r="C109">
-        <v>61.942508867812869</v>
+        <v>61.915390934351123</v>
       </c>
       <c r="D109">
-        <v>66.756090642301444</v>
+        <v>66.693136483989193</v>
       </c>
     </row>
     <row r="110" spans="1:4" x14ac:dyDescent="0.3">
@@ -1963,10 +1963,10 @@
         <v>1</v>
       </c>
       <c r="C110">
-        <v>71.081187665071155</v>
+        <v>71.034827910902749</v>
       </c>
       <c r="D110">
-        <v>78.296739220393931</v>
+        <v>78.193822760742066</v>
       </c>
     </row>
     <row r="111" spans="1:4" x14ac:dyDescent="0.3">
@@ -1977,10 +1977,10 @@
         <v>2</v>
       </c>
       <c r="C111">
-        <v>59.429709257088696</v>
+        <v>59.399210435757844</v>
       </c>
       <c r="D111">
-        <v>61.242770561383857</v>
+        <v>61.175646762355058</v>
       </c>
     </row>
     <row r="112" spans="1:4" x14ac:dyDescent="0.3">
@@ -1991,10 +1991,10 @@
         <v>3</v>
       </c>
       <c r="C112">
-        <v>58.571954495277531</v>
+        <v>58.545748350794497</v>
       </c>
       <c r="D112">
-        <v>61.445679029508213</v>
+        <v>61.387590105134528</v>
       </c>
     </row>
     <row r="113" spans="1:4" x14ac:dyDescent="0.3">
@@ -2005,10 +2005,10 @@
         <v>4</v>
       </c>
       <c r="C113">
-        <v>71.861292676974557</v>
+        <v>71.832899123677961</v>
       </c>
       <c r="D113">
-        <v>74.035657975816022</v>
+        <v>73.972998077200529</v>
       </c>
     </row>
     <row r="114" spans="1:4" x14ac:dyDescent="0.3">
@@ -2019,10 +2019,10 @@
         <v>5</v>
       </c>
       <c r="C114">
-        <v>63.027152668155942</v>
+        <v>63.009013231846588</v>
       </c>
       <c r="D114">
-        <v>62.969694549282828</v>
+        <v>62.929691555249654</v>
       </c>
     </row>
     <row r="115" spans="1:4" x14ac:dyDescent="0.3">
@@ -2033,10 +2033,10 @@
         <v>6</v>
       </c>
       <c r="C115">
-        <v>72.491506262017083</v>
+        <v>72.469081422108232</v>
       </c>
       <c r="D115">
-        <v>72.655013660381996</v>
+        <v>72.605461192089834</v>
       </c>
     </row>
     <row r="116" spans="1:4" x14ac:dyDescent="0.3">
@@ -2047,10 +2047,10 @@
         <v>7</v>
       </c>
       <c r="C116">
-        <v>69.528722554616039</v>
+        <v>69.501950165844534</v>
       </c>
       <c r="D116">
-        <v>71.166843424953214</v>
+        <v>71.107835154440679</v>
       </c>
     </row>
     <row r="117" spans="1:4" x14ac:dyDescent="0.3">
@@ -2061,10 +2061,10 @@
         <v>8</v>
       </c>
       <c r="C117">
-        <v>60.602896254321614</v>
+        <v>60.581174960935883</v>
       </c>
       <c r="D117">
-        <v>64.578729016920065</v>
+        <v>64.521915290767367</v>
       </c>
     </row>
     <row r="118" spans="1:4" x14ac:dyDescent="0.3">
@@ -2075,10 +2075,10 @@
         <v>9</v>
       </c>
       <c r="C118">
-        <v>58.355460008940362</v>
+        <v>58.343876175420192</v>
       </c>
       <c r="D118">
-        <v>57.094747292957045</v>
+        <v>57.068721001145555</v>
       </c>
     </row>
     <row r="119" spans="1:4" x14ac:dyDescent="0.3">
@@ -2089,10 +2089,10 @@
         <v>10</v>
       </c>
       <c r="C119">
-        <v>61.344821590381081</v>
+        <v>61.310714292824635</v>
       </c>
       <c r="D119">
-        <v>66.888032310552973</v>
+        <v>66.813134666119197</v>
       </c>
     </row>
     <row r="120" spans="1:4" x14ac:dyDescent="0.3">
@@ -2103,10 +2103,10 @@
         <v>11</v>
       </c>
       <c r="C120">
-        <v>58.828569701999193</v>
+        <v>58.800429309634971</v>
       </c>
       <c r="D120">
-        <v>64.260074784264049</v>
+        <v>64.197817726037997</v>
       </c>
     </row>
     <row r="121" spans="1:4" x14ac:dyDescent="0.3">
@@ -2117,10 +2117,10 @@
         <v>12</v>
       </c>
       <c r="C121">
-        <v>58.034947703199606</v>
+        <v>58.004377266198993</v>
       </c>
       <c r="D121">
-        <v>61.901662502263157</v>
+        <v>61.834027131581443</v>
       </c>
     </row>
     <row r="122" spans="1:4" x14ac:dyDescent="0.3">
@@ -2131,10 +2131,10 @@
         <v>1</v>
       </c>
       <c r="C122">
-        <v>64.427837819372513</v>
+        <v>64.411734916868653</v>
       </c>
       <c r="D122">
-        <v>65.136011029792257</v>
+        <v>65.102754764795407</v>
       </c>
     </row>
     <row r="123" spans="1:4" x14ac:dyDescent="0.3">
@@ -2145,10 +2145,10 @@
         <v>2</v>
       </c>
       <c r="C123">
-        <v>54.692299747103014</v>
+        <v>54.670458876511475</v>
       </c>
       <c r="D123">
-        <v>57.861224848914354</v>
+        <v>57.815821932646344</v>
       </c>
     </row>
     <row r="124" spans="1:4" x14ac:dyDescent="0.3">
@@ -2159,10 +2159,10 @@
         <v>3</v>
       </c>
       <c r="C124">
-        <v>65.043651912496827</v>
+        <v>65.01010984404968</v>
       </c>
       <c r="D124">
-        <v>67.531201171796368</v>
+        <v>67.46203687893771</v>
       </c>
     </row>
     <row r="125" spans="1:4" x14ac:dyDescent="0.3">
@@ -2173,10 +2173,10 @@
         <v>4</v>
       </c>
       <c r="C125">
-        <v>60.520566312705988</v>
+        <v>60.49784118077531</v>
       </c>
       <c r="D125">
-        <v>64.522185158207208</v>
+        <v>64.475155351281458</v>
       </c>
     </row>
     <row r="126" spans="1:4" x14ac:dyDescent="0.3">
@@ -2187,10 +2187,10 @@
         <v>5</v>
       </c>
       <c r="C126">
-        <v>57.1880679975921</v>
+        <v>57.167739618079054</v>
       </c>
       <c r="D126">
-        <v>57.210148200481619</v>
+        <v>57.167881809554288</v>
       </c>
     </row>
     <row r="127" spans="1:4" x14ac:dyDescent="0.3">
@@ -2201,10 +2201,10 @@
         <v>6</v>
       </c>
       <c r="C127">
-        <v>56.816366381682535</v>
+        <v>56.791507307845656</v>
       </c>
       <c r="D127">
-        <v>57.473263948719698</v>
+        <v>57.422152938489603</v>
       </c>
     </row>
     <row r="128" spans="1:4" x14ac:dyDescent="0.3">
@@ -2215,10 +2215,10 @@
         <v>7</v>
       </c>
       <c r="C128">
-        <v>47.889177802690583</v>
+        <v>47.856428285814843</v>
       </c>
       <c r="D128">
-        <v>52.375349096367209</v>
+        <v>52.307810272909428</v>
       </c>
     </row>
     <row r="129" spans="1:4" x14ac:dyDescent="0.3">
@@ -2229,10 +2229,10 @@
         <v>8</v>
       </c>
       <c r="C129">
-        <v>78.463197381862173</v>
+        <v>78.435149664217477</v>
       </c>
       <c r="D129">
-        <v>76.588155335833633</v>
+        <v>76.530487118929642</v>
       </c>
     </row>
     <row r="130" spans="1:4" x14ac:dyDescent="0.3">
@@ -2243,10 +2243,10 @@
         <v>9</v>
       </c>
       <c r="C130">
-        <v>100.13580402024451</v>
+        <v>100.1027954086818</v>
       </c>
       <c r="D130">
-        <v>94.344330056621757</v>
+        <v>94.276442963390735</v>
       </c>
     </row>
     <row r="131" spans="1:4" x14ac:dyDescent="0.3">
@@ -2257,10 +2257,10 @@
         <v>10</v>
       </c>
       <c r="C131">
-        <v>79.85012269319428</v>
+        <v>79.819488322885633</v>
       </c>
       <c r="D131">
-        <v>79.117789629571774</v>
+        <v>79.054579642079915</v>
       </c>
     </row>
     <row r="132" spans="1:4" x14ac:dyDescent="0.3">
@@ -2271,10 +2271,10 @@
         <v>11</v>
       </c>
       <c r="C132">
-        <v>83.538191077522796</v>
+        <v>83.512107860190241</v>
       </c>
       <c r="D132">
-        <v>79.294225938876579</v>
+        <v>79.240565703151674</v>
       </c>
     </row>
     <row r="133" spans="1:4" x14ac:dyDescent="0.3">
@@ -2285,10 +2285,10 @@
         <v>12</v>
       </c>
       <c r="C133">
-        <v>97.116858987909481</v>
+        <v>97.070141851370479</v>
       </c>
       <c r="D133">
-        <v>99.594075602700642</v>
+        <v>99.497646246992133</v>
       </c>
     </row>
     <row r="134" spans="1:4" x14ac:dyDescent="0.3">
@@ -2299,10 +2299,10 @@
         <v>1</v>
       </c>
       <c r="C134">
-        <v>134.8296422865001</v>
+        <v>134.77515414054008</v>
       </c>
       <c r="D134">
-        <v>132.76960131320854</v>
+        <v>132.66898606166689</v>
       </c>
     </row>
     <row r="135" spans="1:4" x14ac:dyDescent="0.3">
@@ -2313,10 +2313,10 @@
         <v>2</v>
       </c>
       <c r="C135">
-        <v>99.375012514368933</v>
+        <v>99.338493453900668</v>
       </c>
       <c r="D135">
-        <v>97.758319638716401</v>
+        <v>97.691320536507092</v>
       </c>
     </row>
     <row r="136" spans="1:4" x14ac:dyDescent="0.3">
@@ -2327,10 +2327,10 @@
         <v>3</v>
       </c>
       <c r="C136">
-        <v>120.36782465363814</v>
+        <v>120.27834070222642</v>
       </c>
       <c r="D136">
-        <v>129.65116999232424</v>
+        <v>129.4850567162087</v>
       </c>
     </row>
     <row r="137" spans="1:4" x14ac:dyDescent="0.3">
@@ -2341,10 +2341,10 @@
         <v>4</v>
       </c>
       <c r="C137">
-        <v>92.311522858488274</v>
+        <v>92.250734739189483</v>
       </c>
       <c r="D137">
-        <v>98.95335063460783</v>
+        <v>98.841048787499489</v>
       </c>
     </row>
     <row r="138" spans="1:4" x14ac:dyDescent="0.3">
@@ -2355,10 +2355,10 @@
         <v>5</v>
       </c>
       <c r="C138">
-        <v>78.621999706099643</v>
+        <v>78.577100598634146</v>
       </c>
       <c r="D138">
-        <v>81.730853942189697</v>
+        <v>81.647949053082414</v>
       </c>
     </row>
     <row r="139" spans="1:4" x14ac:dyDescent="0.3">
@@ -2369,10 +2369,10 @@
         <v>6</v>
       </c>
       <c r="C139">
-        <v>86.431595835410931</v>
+        <v>86.389794661552557</v>
       </c>
       <c r="D139">
-        <v>90.959517261619538</v>
+        <v>90.882326039109643</v>
       </c>
     </row>
     <row r="140" spans="1:4" x14ac:dyDescent="0.3">
@@ -2383,10 +2383,10 @@
         <v>7</v>
       </c>
       <c r="C140">
-        <v>96.932217244775771</v>
+        <v>96.848888398427235</v>
       </c>
       <c r="D140">
-        <v>108.19194283693473</v>
+        <v>108.03765492218241</v>
       </c>
     </row>
     <row r="141" spans="1:4" x14ac:dyDescent="0.3">
@@ -2397,10 +2397,10 @@
         <v>8</v>
       </c>
       <c r="C141">
-        <v>90.586944263792134</v>
+        <v>90.502000110391975</v>
       </c>
       <c r="D141">
-        <v>99.107293947332138</v>
+        <v>98.950066651527948</v>
       </c>
     </row>
     <row r="142" spans="1:4" x14ac:dyDescent="0.3">
@@ -2411,10 +2411,10 @@
         <v>9</v>
       </c>
       <c r="C142">
-        <v>162.55008346347645</v>
+        <v>162.48119206840639</v>
       </c>
       <c r="D142">
-        <v>159.50504239959145</v>
+        <v>159.37768378815611</v>
       </c>
     </row>
     <row r="143" spans="1:4" x14ac:dyDescent="0.3">
@@ -2425,10 +2425,10 @@
         <v>10</v>
       </c>
       <c r="C143">
-        <v>208.50990148476842</v>
+        <v>208.41027406746682</v>
       </c>
       <c r="D143">
-        <v>209.28606703380117</v>
+        <v>209.10172236225122</v>
       </c>
     </row>
     <row r="144" spans="1:4" x14ac:dyDescent="0.3">
@@ -2439,10 +2439,10 @@
         <v>11</v>
       </c>
       <c r="C144">
-        <v>144.04532983459791</v>
+        <v>143.96182891276595</v>
       </c>
       <c r="D144">
-        <v>146.50234035898521</v>
+        <v>146.34789749835605</v>
       </c>
     </row>
     <row r="145" spans="1:4" x14ac:dyDescent="0.3">
@@ -2453,10 +2453,10 @@
         <v>12</v>
       </c>
       <c r="C145">
-        <v>144.81124465175793</v>
+        <v>144.72867735615071</v>
       </c>
       <c r="D145">
-        <v>148.72386432197706</v>
+        <v>148.57080577500147</v>
       </c>
     </row>
     <row r="146" spans="1:4" x14ac:dyDescent="0.3">
@@ -2467,10 +2467,10 @@
         <v>1</v>
       </c>
       <c r="C146">
-        <v>146.21370989891858</v>
+        <v>146.11124849470096</v>
       </c>
       <c r="D146">
-        <v>146.61916855908365</v>
+        <v>146.4392207254933</v>
       </c>
     </row>
     <row r="147" spans="1:4" x14ac:dyDescent="0.3">
@@ -2481,10 +2481,10 @@
         <v>2</v>
       </c>
       <c r="C147">
-        <v>147.7813088727105</v>
+        <v>147.70314387306672</v>
       </c>
       <c r="D147">
-        <v>144.45254603137005</v>
+        <v>144.31469084392114</v>
       </c>
     </row>
     <row r="148" spans="1:4" x14ac:dyDescent="0.3">
@@ -2495,10 +2495,10 @@
         <v>3</v>
       </c>
       <c r="C148">
-        <v>132.66995619446729</v>
+        <v>132.58174913289</v>
       </c>
       <c r="D148">
-        <v>136.53352740277384</v>
+        <v>136.37799488741189</v>
       </c>
     </row>
     <row r="149" spans="1:4" x14ac:dyDescent="0.3">
@@ -2509,10 +2509,10 @@
         <v>4</v>
       </c>
       <c r="C149">
-        <v>102.68521694590871</v>
+        <v>102.62313480280388</v>
       </c>
       <c r="D149">
-        <v>104.85473267745004</v>
+        <v>104.745746029674</v>
       </c>
     </row>
     <row r="150" spans="1:4" x14ac:dyDescent="0.3">
@@ -2523,10 +2523,10 @@
         <v>5</v>
       </c>
       <c r="C150">
-        <v>103.77731344678871</v>
+        <v>103.7335007984622</v>
       </c>
       <c r="D150">
-        <v>100.59883206137975</v>
+        <v>100.52189852815273</v>
       </c>
     </row>
     <row r="151" spans="1:4" x14ac:dyDescent="0.3">
@@ -2537,10 +2537,10 @@
         <v>6</v>
       </c>
       <c r="C151">
-        <v>117.85497888622257</v>
+        <v>117.71767536856736</v>
       </c>
       <c r="D151">
-        <v>130.82173873368339</v>
+        <v>130.58030763815603</v>
       </c>
     </row>
     <row r="152" spans="1:4" x14ac:dyDescent="0.3">
@@ -2551,10 +2551,10 @@
         <v>7</v>
       </c>
       <c r="C152">
-        <v>106.99861536877442</v>
+        <v>106.89572722047274</v>
       </c>
       <c r="D152">
-        <v>117.98013429551442</v>
+        <v>117.79920388662993</v>
       </c>
     </row>
     <row r="153" spans="1:4" x14ac:dyDescent="0.3">
@@ -2565,10 +2565,10 @@
         <v>8</v>
       </c>
       <c r="C153">
-        <v>103.55615350207776</v>
+        <v>103.4630222944608</v>
       </c>
       <c r="D153">
-        <v>109.43930800850262</v>
+        <v>109.27559248451905</v>
       </c>
     </row>
     <row r="154" spans="1:4" x14ac:dyDescent="0.3">
@@ -2579,10 +2579,10 @@
         <v>9</v>
       </c>
       <c r="C154">
-        <v>106.87609415475221</v>
+        <v>106.7308047259959</v>
       </c>
       <c r="D154">
-        <v>119.83411536491056</v>
+        <v>119.5786353129479</v>
       </c>
     </row>
     <row r="155" spans="1:4" x14ac:dyDescent="0.3">
@@ -2593,10 +2593,10 @@
         <v>10</v>
       </c>
       <c r="C155">
-        <v>92.371311286372091</v>
+        <v>92.278554370963391</v>
       </c>
       <c r="D155">
-        <v>98.21574209666818</v>
+        <v>98.052842841680786</v>
       </c>
     </row>
     <row r="156" spans="1:4" x14ac:dyDescent="0.3">
@@ -2607,10 +2607,10 @@
         <v>11</v>
       </c>
       <c r="C156">
-        <v>105.94022927034759</v>
+        <v>105.84607192905921</v>
       </c>
       <c r="D156">
-        <v>109.51134232768956</v>
+        <v>109.34600522650734</v>
       </c>
     </row>
     <row r="157" spans="1:4" x14ac:dyDescent="0.3">
@@ -2621,10 +2621,10 @@
         <v>12</v>
       </c>
       <c r="C157">
-        <v>103.06707522029565</v>
+        <v>102.98740772532891</v>
       </c>
       <c r="D157">
-        <v>105.8216448535447</v>
+        <v>105.68220373236775</v>
       </c>
     </row>
     <row r="158" spans="1:4" x14ac:dyDescent="0.3">
@@ -2635,10 +2635,10 @@
         <v>1</v>
       </c>
       <c r="C158">
-        <v>118.40906810200008</v>
+        <v>118.30959251807451</v>
       </c>
       <c r="D158">
-        <v>120.82213755523738</v>
+        <v>120.6541925646326</v>
       </c>
     </row>
     <row r="159" spans="1:4" x14ac:dyDescent="0.3">
@@ -2649,10 +2649,10 @@
         <v>2</v>
       </c>
       <c r="C159">
-        <v>115.14575790117331</v>
+        <v>115.05661675702144</v>
       </c>
       <c r="D159">
-        <v>120.62374088708437</v>
+        <v>120.4738756830882</v>
       </c>
     </row>
     <row r="160" spans="1:4" x14ac:dyDescent="0.3">
@@ -2663,10 +2663,10 @@
         <v>3</v>
       </c>
       <c r="C160">
-        <v>115.37551282428605</v>
+        <v>115.25458490062186</v>
       </c>
       <c r="D160">
-        <v>121.65199970058633</v>
+        <v>121.44864991675993</v>
       </c>
     </row>
     <row r="161" spans="1:4" x14ac:dyDescent="0.3">
@@ -2677,10 +2677,10 @@
         <v>4</v>
       </c>
       <c r="C161">
-        <v>109.62809520501062</v>
+        <v>109.54859358290922</v>
       </c>
       <c r="D161">
-        <v>109.4240408827375</v>
+        <v>109.2899844711115</v>
       </c>
     </row>
     <row r="162" spans="1:4" x14ac:dyDescent="0.3">
@@ -2691,10 +2691,10 @@
         <v>5</v>
       </c>
       <c r="C162">
-        <v>147.9308076757253</v>
+        <v>147.84150852003191</v>
       </c>
       <c r="D162">
-        <v>143.40030447978191</v>
+        <v>143.24957781356943</v>
       </c>
     </row>
     <row r="163" spans="1:4" x14ac:dyDescent="0.3">
@@ -2705,10 +2705,10 @@
         <v>6</v>
       </c>
       <c r="C163">
-        <v>139.05418844435559</v>
+        <v>138.93798811972377</v>
       </c>
       <c r="D163">
-        <v>142.24290742680066</v>
+        <v>142.0473363347887</v>
       </c>
     </row>
     <row r="164" spans="1:4" x14ac:dyDescent="0.3">
@@ -2719,10 +2719,10 @@
         <v>7</v>
       </c>
       <c r="C164">
-        <v>149.32207484249966</v>
+        <v>149.21505375128004</v>
       </c>
       <c r="D164">
-        <v>147.06953387778725</v>
+        <v>146.88945589613454</v>
       </c>
     </row>
     <row r="165" spans="1:4" x14ac:dyDescent="0.3">
@@ -2733,10 +2733,10 @@
         <v>8</v>
       </c>
       <c r="C165">
-        <v>123.90725413824791</v>
+        <v>123.82712516722994</v>
       </c>
       <c r="D165">
-        <v>122.02515913357033</v>
+        <v>121.89059236448537</v>
       </c>
     </row>
     <row r="166" spans="1:4" x14ac:dyDescent="0.3">
@@ -2747,10 +2747,10 @@
         <v>9</v>
       </c>
       <c r="C166">
-        <v>133.38351906356752</v>
+        <v>133.31452141086339</v>
       </c>
       <c r="D166">
-        <v>127.51285481080329</v>
+        <v>127.39682959466751</v>
       </c>
     </row>
     <row r="167" spans="1:4" x14ac:dyDescent="0.3">
@@ -2761,10 +2761,10 @@
         <v>10</v>
       </c>
       <c r="C167">
-        <v>127.43972867719292</v>
+        <v>127.35779814017353</v>
       </c>
       <c r="D167">
-        <v>123.52524353653872</v>
+        <v>123.38713121942504</v>
       </c>
     </row>
     <row r="168" spans="1:4" x14ac:dyDescent="0.3">
@@ -2775,10 +2775,10 @@
         <v>11</v>
       </c>
       <c r="C168">
-        <v>131.30009666965734</v>
+        <v>131.22173687914412</v>
       </c>
       <c r="D168">
-        <v>127.8192903329097</v>
+        <v>127.68749403835716</v>
       </c>
     </row>
     <row r="169" spans="1:4" x14ac:dyDescent="0.3">
@@ -2789,10 +2789,10 @@
         <v>12</v>
       </c>
       <c r="C169">
-        <v>135.5249864850025</v>
+        <v>135.41963436562136</v>
       </c>
       <c r="D169">
-        <v>140.03165491278358</v>
+        <v>139.85416432526088</v>
       </c>
     </row>
     <row r="170" spans="1:4" x14ac:dyDescent="0.3">
@@ -2803,10 +2803,10 @@
         <v>1</v>
       </c>
       <c r="C170">
-        <v>115.52693121099483</v>
+        <v>115.38021090456377</v>
       </c>
       <c r="D170">
-        <v>124.65272723983915</v>
+        <v>124.42186230123907</v>
       </c>
     </row>
     <row r="171" spans="1:4" x14ac:dyDescent="0.3">
@@ -2817,10 +2817,10 @@
         <v>2</v>
       </c>
       <c r="C171">
-        <v>96.964745423395513</v>
+        <v>96.909062688281139</v>
       </c>
       <c r="D171">
-        <v>97.681569421163857</v>
+        <v>97.593801926649249</v>
       </c>
     </row>
     <row r="172" spans="1:4" x14ac:dyDescent="0.3">
@@ -2831,10 +2831,10 @@
         <v>3</v>
       </c>
       <c r="C172">
-        <v>131.3547450671152</v>
+        <v>131.24021257844836</v>
       </c>
       <c r="D172">
-        <v>132.22263957321127</v>
+        <v>132.04265241427061</v>
       </c>
     </row>
     <row r="173" spans="1:4" x14ac:dyDescent="0.3">
@@ -2845,10 +2845,10 @@
         <v>4</v>
       </c>
       <c r="C173">
-        <v>120.12214190143386</v>
+        <v>119.99429139631967</v>
       </c>
       <c r="D173">
-        <v>124.48960967112373</v>
+        <v>124.28837725370009</v>
       </c>
     </row>
     <row r="174" spans="1:4" x14ac:dyDescent="0.3">
@@ -2859,10 +2859,10 @@
         <v>5</v>
       </c>
       <c r="C174">
-        <v>94.823739155250095</v>
+        <v>94.753682188479971</v>
       </c>
       <c r="D174">
-        <v>94.819902219294562</v>
+        <v>94.709584346828038</v>
       </c>
     </row>
     <row r="175" spans="1:4" x14ac:dyDescent="0.3">
@@ -2873,10 +2873,10 @@
         <v>6</v>
       </c>
       <c r="C175">
-        <v>125.11295272796939</v>
+        <v>125.01542788786777</v>
       </c>
       <c r="D175">
-        <v>124.46252963080987</v>
+        <v>124.30942851034966</v>
       </c>
     </row>
     <row r="176" spans="1:4" x14ac:dyDescent="0.3">
@@ -2887,10 +2887,10 @@
         <v>7</v>
       </c>
       <c r="C176">
-        <v>154.23676317759197</v>
+        <v>154.14254867495367</v>
       </c>
       <c r="D176">
-        <v>151.39372681479594</v>
+        <v>151.24522723383021</v>
       </c>
     </row>
     <row r="177" spans="1:4" x14ac:dyDescent="0.3">
@@ -2901,10 +2901,10 @@
         <v>8</v>
       </c>
       <c r="C177">
-        <v>217.68556592612867</v>
+        <v>217.55313259953877</v>
       </c>
       <c r="D177">
-        <v>215.86311677389253</v>
+        <v>215.6544495486055</v>
       </c>
     </row>
     <row r="178" spans="1:4" x14ac:dyDescent="0.3">
@@ -2915,10 +2915,10 @@
         <v>9</v>
       </c>
       <c r="C178">
-        <v>195.09360108164151</v>
+        <v>194.95863798422059</v>
       </c>
       <c r="D178">
-        <v>194.87105315233762</v>
+        <v>194.65878153918371</v>
       </c>
     </row>
     <row r="179" spans="1:4" x14ac:dyDescent="0.3">
@@ -2929,10 +2929,10 @@
         <v>10</v>
       </c>
       <c r="C179">
-        <v>167.68349123396976</v>
+        <v>167.5341554010823</v>
       </c>
       <c r="D179">
-        <v>173.55853855618329</v>
+        <v>173.32363643136401</v>
       </c>
     </row>
     <row r="180" spans="1:4" x14ac:dyDescent="0.3">
@@ -2943,10 +2943,10 @@
         <v>11</v>
       </c>
       <c r="C180">
-        <v>192.40340238198755</v>
+        <v>192.25005987697205</v>
       </c>
       <c r="D180">
-        <v>195.56031404539314</v>
+        <v>195.31919839452877</v>
       </c>
     </row>
     <row r="181" spans="1:4" x14ac:dyDescent="0.3">
@@ -2957,10 +2957,10 @@
         <v>12</v>
       </c>
       <c r="C181">
-        <v>179.12894643902976</v>
+        <v>178.97791106415752</v>
       </c>
       <c r="D181">
-        <v>186.60382047126404</v>
+        <v>186.36615866290614</v>
       </c>
     </row>
     <row r="182" spans="1:4" x14ac:dyDescent="0.3">
@@ -2971,10 +2971,10 @@
         <v>1</v>
       </c>
       <c r="C182">
-        <v>155.35598984340595</v>
+        <v>155.22841912913435</v>
       </c>
       <c r="D182">
-        <v>158.67060514096315</v>
+        <v>158.48274509811742</v>
       </c>
     </row>
     <row r="183" spans="1:4" x14ac:dyDescent="0.3">
@@ -2985,10 +2985,10 @@
         <v>2</v>
       </c>
       <c r="C183">
-        <v>142.20391709602424</v>
+        <v>142.05671042941958</v>
       </c>
       <c r="D183">
-        <v>148.55308845317953</v>
+        <v>148.33616981716602</v>
       </c>
     </row>
     <row r="184" spans="1:4" x14ac:dyDescent="0.3">
@@ -2999,10 +2999,10 @@
         <v>3</v>
       </c>
       <c r="C184">
-        <v>133.57146019165384</v>
+        <v>133.42707057269976</v>
       </c>
       <c r="D184">
-        <v>147.07931936130018</v>
+        <v>146.86629413299869</v>
       </c>
     </row>
     <row r="185" spans="1:4" x14ac:dyDescent="0.3">
@@ -3013,10 +3013,10 @@
         <v>4</v>
       </c>
       <c r="C185">
-        <v>131.01891039309612</v>
+        <v>130.88523693433663</v>
       </c>
       <c r="D185">
-        <v>136.69962070450498</v>
+        <v>136.50267736600006</v>
       </c>
     </row>
     <row r="186" spans="1:4" x14ac:dyDescent="0.3">
@@ -3027,10 +3027,10 @@
         <v>5</v>
       </c>
       <c r="C186">
-        <v>160.61588120457785</v>
+        <v>160.47509910769094</v>
       </c>
       <c r="D186">
-        <v>165.78003104131801</v>
+        <v>165.57251078982361</v>
       </c>
     </row>
     <row r="187" spans="1:4" x14ac:dyDescent="0.3">
@@ -3041,10 +3041,10 @@
         <v>6</v>
       </c>
       <c r="C187">
-        <v>184.1491743545555</v>
+        <v>184.00226936645751</v>
       </c>
       <c r="D187">
-        <v>188.52712704437315</v>
+        <v>188.31049549704892</v>
       </c>
     </row>
     <row r="188" spans="1:4" x14ac:dyDescent="0.3">
@@ -3055,10 +3055,10 @@
         <v>7</v>
       </c>
       <c r="C188">
-        <v>153.43437486018883</v>
+        <v>153.30700667004788</v>
       </c>
       <c r="D188">
-        <v>153.18026056200284</v>
+        <v>152.99256430944016</v>
       </c>
     </row>
     <row r="189" spans="1:4" x14ac:dyDescent="0.3">
@@ -3069,10 +3069,10 @@
         <v>8</v>
       </c>
       <c r="C189">
-        <v>117.4472925302037</v>
+        <v>117.36385982738729</v>
       </c>
       <c r="D189">
-        <v>118.75687835023851</v>
+        <v>118.63401845140011</v>
       </c>
     </row>
     <row r="190" spans="1:4" x14ac:dyDescent="0.3">
@@ -3083,10 +3083,10 @@
         <v>9</v>
       </c>
       <c r="C190">
-        <v>154.54409103525293</v>
+        <v>154.41709628193945</v>
       </c>
       <c r="D190">
-        <v>156.29241824621417</v>
+        <v>156.10490579691134</v>
       </c>
     </row>
     <row r="191" spans="1:4" x14ac:dyDescent="0.3">
@@ -3097,10 +3097,10 @@
         <v>10</v>
       </c>
       <c r="C191">
-        <v>152.01963044346002</v>
+        <v>151.89991378511874</v>
       </c>
       <c r="D191">
-        <v>151.83270283909468</v>
+        <v>151.65634429573933</v>
       </c>
     </row>
     <row r="192" spans="1:4" x14ac:dyDescent="0.3">
@@ -3111,10 +3111,10 @@
         <v>11</v>
       </c>
       <c r="C192">
-        <v>166.86110489715719</v>
+        <v>166.73184187001465</v>
       </c>
       <c r="D192">
-        <v>161.22759281876458</v>
+        <v>161.03700011000601</v>
       </c>
     </row>
     <row r="193" spans="1:4" x14ac:dyDescent="0.3">
@@ -3125,10 +3125,10 @@
         <v>12</v>
       </c>
       <c r="C193">
-        <v>171.31880003627077</v>
+        <v>171.16874994689618</v>
       </c>
       <c r="D193">
-        <v>170.26582399887204</v>
+        <v>170.04450512292792</v>
       </c>
     </row>
     <row r="194" spans="1:4" x14ac:dyDescent="0.3">
@@ -3139,10 +3139,10 @@
         <v>1</v>
       </c>
       <c r="C194">
-        <v>168.41548367276397</v>
+        <v>168.2642680709402</v>
       </c>
       <c r="D194">
-        <v>166.16756384046681</v>
+        <v>165.96021311857433</v>
       </c>
     </row>
     <row r="195" spans="1:4" x14ac:dyDescent="0.3">
@@ -3153,10 +3153,10 @@
         <v>2</v>
       </c>
       <c r="C195">
-        <v>123.86940533838967</v>
+        <v>123.77125161209148</v>
       </c>
       <c r="D195">
-        <v>123.55080515867991</v>
+        <v>123.41635968507401</v>
       </c>
     </row>
     <row r="196" spans="1:4" x14ac:dyDescent="0.3">
@@ -3167,10 +3167,10 @@
         <v>3</v>
       </c>
       <c r="C196">
-        <v>146.3311288361657</v>
+        <v>146.22625713675311</v>
       </c>
       <c r="D196">
-        <v>145.41001172884808</v>
+        <v>145.26603936169289</v>
       </c>
     </row>
     <row r="197" spans="1:4" x14ac:dyDescent="0.3">
@@ -3181,10 +3181,10 @@
         <v>4</v>
       </c>
       <c r="C197">
-        <v>137.23729292255791</v>
+        <v>137.09818401956534</v>
       </c>
       <c r="D197">
-        <v>140.00289303080058</v>
+        <v>139.81218788794314</v>
       </c>
     </row>
     <row r="198" spans="1:4" x14ac:dyDescent="0.3">
@@ -3195,10 +3195,10 @@
         <v>5</v>
       </c>
       <c r="C198">
-        <v>108.82230244837918</v>
+        <v>108.73915324764916</v>
       </c>
       <c r="D198">
-        <v>108.56891237443489</v>
+        <v>108.45492731936986</v>
       </c>
     </row>
     <row r="199" spans="1:4" x14ac:dyDescent="0.3">
@@ -3209,10 +3209,10 @@
         <v>6</v>
       </c>
       <c r="C199">
-        <v>128.83709621512182</v>
+        <v>128.71741720497738</v>
       </c>
       <c r="D199">
-        <v>130.49792961060695</v>
+        <v>130.33402461196374</v>
       </c>
     </row>
     <row r="200" spans="1:4" x14ac:dyDescent="0.3">
@@ -3223,10 +3223,10 @@
         <v>7</v>
       </c>
       <c r="C200">
-        <v>109.09725098847071</v>
+        <v>109.00851561060909</v>
       </c>
       <c r="D200">
-        <v>108.73323945324799</v>
+        <v>108.61165664602973</v>
       </c>
     </row>
     <row r="201" spans="1:4" x14ac:dyDescent="0.3">
@@ -3237,10 +3237,10 @@
         <v>8</v>
       </c>
       <c r="C201">
-        <v>120.50127882954666</v>
+        <v>120.3839834935542</v>
       </c>
       <c r="D201">
-        <v>127.66430267638727</v>
+        <v>127.50349774990674</v>
       </c>
     </row>
     <row r="202" spans="1:4" x14ac:dyDescent="0.3">
@@ -3251,10 +3251,10 @@
         <v>9</v>
       </c>
       <c r="C202">
-        <v>139.74652110816331</v>
+        <v>139.62927512477324</v>
       </c>
       <c r="D202">
-        <v>141.63594997551567</v>
+        <v>141.47516874973721</v>
       </c>
     </row>
     <row r="203" spans="1:4" x14ac:dyDescent="0.3">
@@ -3265,10 +3265,10 @@
         <v>10</v>
       </c>
       <c r="C203">
-        <v>170.09708461097773</v>
+        <v>169.91904988025723</v>
       </c>
       <c r="D203">
-        <v>167.65911445735881</v>
+        <v>167.4150691586816</v>
       </c>
     </row>
     <row r="204" spans="1:4" x14ac:dyDescent="0.3">
@@ -3279,10 +3279,10 @@
         <v>11</v>
       </c>
       <c r="C204">
-        <v>105.03745540457595</v>
+        <v>104.8970581901048</v>
       </c>
       <c r="D204">
-        <v>108.31065508283851</v>
+        <v>108.11831756365788</v>
       </c>
     </row>
     <row r="205" spans="1:4" x14ac:dyDescent="0.3">
@@ -3293,10 +3293,10 @@
         <v>12</v>
       </c>
       <c r="C205">
-        <v>124.33466798631018</v>
+        <v>124.19044442491482</v>
       </c>
       <c r="D205">
-        <v>128.47376247649453</v>
+        <v>128.27598777106547</v>
       </c>
     </row>
     <row r="206" spans="1:4" x14ac:dyDescent="0.3">
@@ -3307,10 +3307,10 @@
         <v>1</v>
       </c>
       <c r="C206">
-        <v>116.29103785331415</v>
+        <v>116.16349921565681</v>
       </c>
       <c r="D206">
-        <v>119.89245168343595</v>
+        <v>119.72452692335156</v>
       </c>
     </row>
     <row r="207" spans="1:4" x14ac:dyDescent="0.3">
@@ -3321,10 +3321,10 @@
         <v>2</v>
       </c>
       <c r="C207">
-        <v>102.09728451186321</v>
+        <v>102.01047179707916</v>
       </c>
       <c r="D207">
-        <v>101.04014897477238</v>
+        <v>100.92578811408968</v>
       </c>
     </row>
     <row r="208" spans="1:4" x14ac:dyDescent="0.3">
@@ -3335,10 +3335,10 @@
         <v>3</v>
       </c>
       <c r="C208">
-        <v>115.95797488633711</v>
+        <v>115.83525645999038</v>
       </c>
       <c r="D208">
-        <v>114.78452366994939</v>
+        <v>114.62274172358721</v>
       </c>
     </row>
     <row r="209" spans="1:4" x14ac:dyDescent="0.3">
@@ -3349,10 +3349,10 @@
         <v>4</v>
       </c>
       <c r="C209">
-        <v>111.80882259599215</v>
+        <v>111.64955038345877</v>
       </c>
       <c r="D209">
-        <v>118.69549673877367</v>
+        <v>118.48565023588043</v>
       </c>
     </row>
     <row r="210" spans="1:4" x14ac:dyDescent="0.3">
@@ -3363,10 +3363,10 @@
         <v>5</v>
       </c>
       <c r="C210">
-        <v>107.82104756355945</v>
+        <v>107.72594660429303</v>
       </c>
       <c r="D210">
-        <v>111.16869316165112</v>
+        <v>111.04334557561116</v>
       </c>
     </row>
     <row r="211" spans="1:4" x14ac:dyDescent="0.3">
@@ -3377,10 +3377,10 @@
         <v>6</v>
       </c>
       <c r="C211">
-        <v>92.298959619292404</v>
+        <v>92.168190554978636</v>
       </c>
       <c r="D211">
-        <v>96.659065230506513</v>
+        <v>96.48710743626016</v>
       </c>
     </row>
     <row r="212" spans="1:4" x14ac:dyDescent="0.3">
@@ -3391,10 +3391,10 @@
         <v>7</v>
       </c>
       <c r="C212">
-        <v>95.430018382626855</v>
+        <v>95.313666940691959</v>
       </c>
       <c r="D212">
-        <v>100.073175695144</v>
+        <v>99.919899502723268</v>
       </c>
     </row>
     <row r="213" spans="1:4" x14ac:dyDescent="0.3">
@@ -3405,10 +3405,10 @@
         <v>8</v>
       </c>
       <c r="C213">
-        <v>97.840312727015089</v>
+        <v>97.744735801139569</v>
       </c>
       <c r="D213">
-        <v>105.24707763906315</v>
+        <v>105.12123500964519</v>
       </c>
     </row>
     <row r="214" spans="1:4" x14ac:dyDescent="0.3">
@@ -3419,10 +3419,10 @@
         <v>9</v>
       </c>
       <c r="C214">
-        <v>123.00543201777047</v>
+        <v>122.87243566128919</v>
       </c>
       <c r="D214">
-        <v>128.79451637816948</v>
+        <v>128.61944825900102</v>
       </c>
     </row>
     <row r="215" spans="1:4" x14ac:dyDescent="0.3">
@@ -3433,10 +3433,10 @@
         <v>10</v>
       </c>
       <c r="C215">
-        <v>113.48031107608809</v>
+        <v>113.357203494412</v>
       </c>
       <c r="D215">
-        <v>114.87934289053247</v>
+        <v>114.71733449991211</v>
       </c>
     </row>
     <row r="216" spans="1:4" x14ac:dyDescent="0.3">
@@ -3447,10 +3447,10 @@
         <v>11</v>
       </c>
       <c r="C216">
-        <v>120.71869686042098</v>
+        <v>120.57082688610555</v>
       </c>
       <c r="D216">
-        <v>128.76894802970023</v>
+        <v>128.57420697862889</v>
       </c>
     </row>
     <row r="217" spans="1:4" x14ac:dyDescent="0.3">
@@ -3461,10 +3461,10 @@
         <v>12</v>
       </c>
       <c r="C217">
-        <v>111.76323693590915</v>
+        <v>111.69069969203758</v>
       </c>
       <c r="D217">
-        <v>114.0162687994992</v>
+        <v>113.92075672241478</v>
       </c>
     </row>
     <row r="218" spans="1:4" x14ac:dyDescent="0.3">
@@ -3475,10 +3475,10 @@
         <v>1</v>
       </c>
       <c r="C218">
-        <v>130.24854846969785</v>
+        <v>130.11524710600563</v>
       </c>
       <c r="D218">
-        <v>135.30982019585232</v>
+        <v>135.14915785437597</v>
       </c>
     </row>
     <row r="219" spans="1:4" x14ac:dyDescent="0.3">
@@ -3489,10 +3489,10 @@
         <v>2</v>
       </c>
       <c r="C219">
-        <v>116.4518856799972</v>
+        <v>116.3223183697921</v>
       </c>
       <c r="D219">
-        <v>122.86659796792641</v>
+        <v>122.71051607592193</v>
       </c>
     </row>
     <row r="220" spans="1:4" x14ac:dyDescent="0.3">
@@ -3503,10 +3503,10 @@
         <v>3</v>
       </c>
       <c r="C220">
-        <v>113.41134485523457</v>
+        <v>113.25310510220275</v>
       </c>
       <c r="D220">
-        <v>118.07497270367075</v>
+        <v>117.88430392021309</v>
       </c>
     </row>
     <row r="221" spans="1:4" x14ac:dyDescent="0.3">
@@ -3517,10 +3517,10 @@
         <v>4</v>
       </c>
       <c r="C221">
-        <v>102.18254353002798</v>
+        <v>102.09562862998779</v>
       </c>
       <c r="D221">
-        <v>100.92988326162804</v>
+        <v>100.82511954923628</v>
       </c>
     </row>
     <row r="222" spans="1:4" x14ac:dyDescent="0.3">
@@ -3531,10 +3531,10 @@
         <v>5</v>
       </c>
       <c r="C222">
-        <v>105.14688925122555</v>
+        <v>105.05428636640566</v>
       </c>
       <c r="D222">
-        <v>101.61169178213926</v>
+        <v>101.50001533843437</v>
       </c>
     </row>
     <row r="223" spans="1:4" x14ac:dyDescent="0.3">
@@ -3545,10 +3545,10 @@
         <v>6</v>
       </c>
       <c r="C223">
-        <v>120.30934957300931</v>
+        <v>120.17907327503845</v>
       </c>
       <c r="D223">
-        <v>118.88235866770447</v>
+        <v>118.72546559374508</v>
       </c>
     </row>
     <row r="224" spans="1:4" x14ac:dyDescent="0.3">
@@ -3559,10 +3559,10 @@
         <v>7</v>
       </c>
       <c r="C224">
-        <v>124.54062010634929</v>
+        <v>124.35900311962672</v>
       </c>
       <c r="D224">
-        <v>123.16713960670498</v>
+        <v>122.94821553353027</v>
       </c>
     </row>
     <row r="225" spans="1:4" x14ac:dyDescent="0.3">
@@ -3573,10 +3573,10 @@
         <v>8</v>
       </c>
       <c r="C225">
-        <v>120.50670666002878</v>
+        <v>120.42455386176617</v>
       </c>
       <c r="D225">
-        <v>117.28865135957007</v>
+        <v>117.18973069198921</v>
       </c>
     </row>
     <row r="226" spans="1:4" x14ac:dyDescent="0.3">
@@ -3587,10 +3587,10 @@
         <v>9</v>
       </c>
       <c r="C226">
-        <v>154.49521023188797</v>
+        <v>154.3639527218765</v>
       </c>
       <c r="D226">
-        <v>153.99801352251413</v>
+        <v>153.83985991999424</v>
       </c>
     </row>
     <row r="227" spans="1:4" x14ac:dyDescent="0.3">
@@ -3601,10 +3601,10 @@
         <v>10</v>
       </c>
       <c r="C227">
-        <v>116.69119060067885</v>
+        <v>116.57229996191042</v>
       </c>
       <c r="D227">
-        <v>115.54192176193561</v>
+        <v>115.39867160722267</v>
       </c>
     </row>
     <row r="228" spans="1:4" x14ac:dyDescent="0.3">
@@ -3615,10 +3615,10 @@
         <v>11</v>
       </c>
       <c r="C228">
-        <v>106.51288492565962</v>
+        <v>106.38190444485974</v>
       </c>
       <c r="D228">
-        <v>106.21783277330299</v>
+        <v>106.06008017962027</v>
       </c>
     </row>
     <row r="229" spans="1:4" x14ac:dyDescent="0.3">
@@ -3629,10 +3629,10 @@
         <v>12</v>
       </c>
       <c r="C229">
-        <v>113.50201931239779</v>
+        <v>113.37340735762727</v>
       </c>
       <c r="D229">
-        <v>117.07873781228277</v>
+        <v>116.9237490628539</v>
       </c>
     </row>
     <row r="230" spans="1:4" x14ac:dyDescent="0.3">
@@ -3643,10 +3643,10 @@
         <v>1</v>
       </c>
       <c r="C230">
-        <v>145.37920230967987</v>
+        <v>145.20828759456197</v>
       </c>
       <c r="D230">
-        <v>141.19047095206878</v>
+        <v>140.98028114380421</v>
       </c>
     </row>
     <row r="231" spans="1:4" x14ac:dyDescent="0.3">
@@ -3657,10 +3657,10 @@
         <v>2</v>
       </c>
       <c r="C231">
-        <v>148.31181265936834</v>
+        <v>148.16671858416888</v>
       </c>
       <c r="D231">
-        <v>145.95507910881673</v>
+        <v>145.77674685802927</v>
       </c>
     </row>
     <row r="232" spans="1:4" x14ac:dyDescent="0.3">
@@ -3671,10 +3671,10 @@
         <v>3</v>
       </c>
       <c r="C232">
-        <v>160.78085179706758</v>
+        <v>160.57221680341146</v>
       </c>
       <c r="D232">
-        <v>162.60246569158912</v>
+        <v>162.34613364151207</v>
       </c>
     </row>
     <row r="233" spans="1:4" x14ac:dyDescent="0.3">
@@ -3685,10 +3685,10 @@
         <v>4</v>
       </c>
       <c r="C233">
-        <v>143.69237745572056</v>
+        <v>143.47075803180908</v>
       </c>
       <c r="D233">
-        <v>146.67188398372116</v>
+        <v>146.39938006134571</v>
       </c>
     </row>
     <row r="234" spans="1:4" x14ac:dyDescent="0.3">
@@ -3699,10 +3699,10 @@
         <v>5</v>
       </c>
       <c r="C234">
-        <v>127.34963855128508</v>
+        <v>127.19534335300986</v>
       </c>
       <c r="D234">
-        <v>123.96893835227262</v>
+        <v>123.77764021821704</v>
       </c>
     </row>
     <row r="235" spans="1:4" x14ac:dyDescent="0.3">
@@ -3713,10 +3713,10 @@
         <v>6</v>
       </c>
       <c r="C235">
-        <v>231.5786547742976</v>
+        <v>231.40098490517613</v>
       </c>
       <c r="D235">
-        <v>221.08016291016148</v>
+        <v>220.86233315580014</v>
       </c>
     </row>
     <row r="236" spans="1:4" x14ac:dyDescent="0.3">
@@ -3727,10 +3727,10 @@
         <v>7</v>
       </c>
       <c r="C236">
-        <v>204.93329827346255</v>
+        <v>204.78128542088467</v>
       </c>
       <c r="D236">
-        <v>189.21964952423232</v>
+        <v>189.03332279678318</v>
       </c>
     </row>
     <row r="237" spans="1:4" x14ac:dyDescent="0.3">
@@ -3741,10 +3741,10 @@
         <v>8</v>
       </c>
       <c r="C237">
-        <v>135.84187546090541</v>
+        <v>135.68519014445741</v>
       </c>
       <c r="D237">
-        <v>136.71528670390444</v>
+        <v>136.52293706387516</v>
       </c>
     </row>
     <row r="238" spans="1:4" x14ac:dyDescent="0.3">
@@ -3755,10 +3755,10 @@
         <v>9</v>
       </c>
       <c r="C238">
-        <v>137.04393565728878</v>
+        <v>136.84547874401932</v>
       </c>
       <c r="D238">
-        <v>139.40608799538697</v>
+        <v>139.16231812801496</v>
       </c>
     </row>
     <row r="239" spans="1:4" x14ac:dyDescent="0.3">
@@ -3769,10 +3769,10 @@
         <v>10</v>
       </c>
       <c r="C239">
-        <v>127.09036508753302</v>
+        <v>126.94637674855304</v>
       </c>
       <c r="D239">
-        <v>122.58815936098233</v>
+        <v>122.41145303991097</v>
       </c>
     </row>
     <row r="240" spans="1:4" x14ac:dyDescent="0.3">
@@ -3783,10 +3783,10 @@
         <v>11</v>
       </c>
       <c r="C240">
-        <v>229.99944598714194</v>
+        <v>229.82022596501565</v>
       </c>
       <c r="D240">
-        <v>215.42035190486612</v>
+        <v>215.20031347155745</v>
       </c>
     </row>
     <row r="241" spans="1:4" x14ac:dyDescent="0.3">
@@ -3797,10 +3797,10 @@
         <v>12</v>
       </c>
       <c r="C241">
-        <v>186.26373316420063</v>
+        <v>186.08800578367303</v>
       </c>
       <c r="D241">
-        <v>186.98870812761589</v>
+        <v>186.77291695314759</v>
       </c>
     </row>
     <row r="242" spans="1:4" x14ac:dyDescent="0.3">
@@ -3811,10 +3811,10 @@
         <v>1</v>
       </c>
       <c r="C242">
-        <v>249.90547064880647</v>
+        <v>249.48370754733381</v>
       </c>
       <c r="D242">
-        <v>255.9307409329231</v>
+        <v>255.42226394331243</v>
       </c>
     </row>
     <row r="243" spans="1:4" x14ac:dyDescent="0.3">
@@ -3825,10 +3825,10 @@
         <v>2</v>
       </c>
       <c r="C243">
-        <v>187.34628011736828</v>
+        <v>187.10329283151839</v>
       </c>
       <c r="D243">
-        <v>190.04857620818973</v>
+        <v>189.75558084888868</v>
       </c>
     </row>
     <row r="244" spans="1:4" x14ac:dyDescent="0.3">
@@ -3839,10 +3839,10 @@
         <v>3</v>
       </c>
       <c r="C244">
-        <v>239.6698350215654</v>
+        <v>239.18787214329279</v>
       </c>
       <c r="D244">
-        <v>250.82380329248235</v>
+        <v>250.24312859266627</v>
       </c>
     </row>
     <row r="245" spans="1:4" x14ac:dyDescent="0.3">
@@ -3853,10 +3853,10 @@
         <v>4</v>
       </c>
       <c r="C245">
-        <v>178.47117692420167</v>
+        <v>178.23111752982874</v>
       </c>
       <c r="D245">
-        <v>178.15871664219137</v>
+        <v>177.86929869118299</v>
       </c>
     </row>
     <row r="246" spans="1:4" x14ac:dyDescent="0.3">
@@ -3867,10 +3867,10 @@
         <v>5</v>
       </c>
       <c r="C246">
-        <v>145.68888244691274</v>
+        <v>145.512403915791</v>
       </c>
       <c r="D246">
-        <v>142.94797700848233</v>
+        <v>142.73368040790734</v>
       </c>
     </row>
     <row r="247" spans="1:4" x14ac:dyDescent="0.3">
@@ -3881,10 +3881,10 @@
         <v>6</v>
       </c>
       <c r="C247">
-        <v>174.03343301642514</v>
+        <v>173.71892359304385</v>
       </c>
       <c r="D247">
-        <v>175.98487805638771</v>
+        <v>175.60601807063787</v>
       </c>
     </row>
     <row r="248" spans="1:4" x14ac:dyDescent="0.3">
@@ -3895,10 +3895,10 @@
         <v>7</v>
       </c>
       <c r="C248">
-        <v>167.92057792029146</v>
+        <v>167.6048615571174</v>
       </c>
       <c r="D248">
-        <v>172.75917517256553</v>
+        <v>172.37902722802704</v>
       </c>
     </row>
     <row r="249" spans="1:4" x14ac:dyDescent="0.3">
@@ -3909,10 +3909,10 @@
         <v>8</v>
       </c>
       <c r="C249">
-        <v>141.89896514309876</v>
+        <v>141.67123050155007</v>
       </c>
       <c r="D249">
-        <v>142.11285453547455</v>
+        <v>141.83861671080984</v>
       </c>
     </row>
     <row r="250" spans="1:4" x14ac:dyDescent="0.3">
@@ -3923,10 +3923,10 @@
         <v>9</v>
       </c>
       <c r="C250">
-        <v>159.97501047541456</v>
+        <v>159.68989765733457</v>
       </c>
       <c r="D250">
-        <v>163.8820779579743</v>
+        <v>163.53862740693651</v>
       </c>
     </row>
     <row r="251" spans="1:4" x14ac:dyDescent="0.3">
@@ -3937,10 +3937,10 @@
         <v>10</v>
       </c>
       <c r="C251">
-        <v>145.84818462413446</v>
+        <v>145.65026167385273</v>
       </c>
       <c r="D251">
-        <v>150.11227440082453</v>
+        <v>149.87426585880743</v>
       </c>
     </row>
     <row r="252" spans="1:4" x14ac:dyDescent="0.3">
@@ -3951,10 +3951,10 @@
         <v>11</v>
       </c>
       <c r="C252">
-        <v>162.33184614241455</v>
+        <v>162.04753058013239</v>
       </c>
       <c r="D252">
-        <v>168.44268536550913</v>
+        <v>168.10006262308235</v>
       </c>
     </row>
     <row r="253" spans="1:4" x14ac:dyDescent="0.3">
@@ -3965,10 +3965,10 @@
         <v>12</v>
       </c>
       <c r="C253">
-        <v>150.35055060066691</v>
+        <v>150.11890215442429</v>
       </c>
       <c r="D253">
-        <v>155.89844806900106</v>
+        <v>155.61939820513842</v>
       </c>
     </row>
     <row r="254" spans="1:4" x14ac:dyDescent="0.3">
@@ -3979,10 +3979,10 @@
         <v>1</v>
       </c>
       <c r="C254">
-        <v>180.86849849488374</v>
+        <v>180.48141870546138</v>
       </c>
       <c r="D254">
-        <v>180.65872953862902</v>
+        <v>180.20591695454513</v>
       </c>
     </row>
     <row r="255" spans="1:4" x14ac:dyDescent="0.3">
@@ -3993,10 +3993,10 @@
         <v>2</v>
       </c>
       <c r="C255">
-        <v>128.23570433311107</v>
+        <v>128.01718389909237</v>
       </c>
       <c r="D255">
-        <v>131.08920991724941</v>
+        <v>130.83360315712056</v>
       </c>
     </row>
     <row r="256" spans="1:4" x14ac:dyDescent="0.3">
@@ -4007,10 +4007,10 @@
         <v>3</v>
       </c>
       <c r="C256">
-        <v>184.80405608075677</v>
+        <v>184.43191124502565</v>
       </c>
       <c r="D256">
-        <v>181.99727795930602</v>
+        <v>181.56232165874425</v>
       </c>
     </row>
     <row r="257" spans="1:4" x14ac:dyDescent="0.3">
@@ -4021,10 +4021,10 @@
         <v>4</v>
       </c>
       <c r="C257">
-        <v>167.90213578096532</v>
+        <v>167.54926890136545</v>
       </c>
       <c r="D257">
-        <v>173.99474325260817</v>
+        <v>173.5819054444155</v>
       </c>
     </row>
     <row r="258" spans="1:4" x14ac:dyDescent="0.3">
@@ -4035,10 +4035,10 @@
         <v>5</v>
       </c>
       <c r="C258">
-        <v>173.78663148442953</v>
+        <v>173.4820116083192</v>
       </c>
       <c r="D258">
-        <v>172.97871642027658</v>
+        <v>172.62118812581292</v>
       </c>
     </row>
     <row r="259" spans="1:4" x14ac:dyDescent="0.3">
@@ -4049,10 +4049,10 @@
         <v>6</v>
       </c>
       <c r="C259">
-        <v>166.71315283862742</v>
+        <v>166.41611630501833</v>
       </c>
       <c r="D259">
-        <v>163.93265911172239</v>
+        <v>163.58535428065198</v>
       </c>
     </row>
     <row r="260" spans="1:4" x14ac:dyDescent="0.3">
@@ -4063,10 +4063,10 @@
         <v>7</v>
       </c>
       <c r="C260">
-        <v>232.72863728591119</v>
+        <v>232.14825629415978</v>
       </c>
       <c r="D260">
-        <v>239.29823978518209</v>
+        <v>238.62026183298073</v>
       </c>
     </row>
     <row r="261" spans="1:4" x14ac:dyDescent="0.3">
@@ -4077,10 +4077,10 @@
         <v>8</v>
       </c>
       <c r="C261">
-        <v>175.13856537292881</v>
+        <v>174.74392420984989</v>
       </c>
       <c r="D261">
-        <v>182.69316584845899</v>
+        <v>182.23192923553509</v>
       </c>
     </row>
     <row r="262" spans="1:4" x14ac:dyDescent="0.3">
@@ -4091,10 +4091,10 @@
         <v>9</v>
       </c>
       <c r="C262">
-        <v>196.63746484642607</v>
+        <v>196.17743634752517</v>
       </c>
       <c r="D262">
-        <v>206.38561209516359</v>
+        <v>205.84797358840544</v>
       </c>
     </row>
     <row r="263" spans="1:4" x14ac:dyDescent="0.3">
@@ -4105,10 +4105,10 @@
         <v>10</v>
       </c>
       <c r="C263">
-        <v>217.31615305449512</v>
+        <v>216.8102887432153</v>
       </c>
       <c r="D263">
-        <v>226.54948126494</v>
+        <v>225.95935388896473</v>
       </c>
     </row>
     <row r="264" spans="1:4" x14ac:dyDescent="0.3">
@@ -4119,10 +4119,10 @@
         <v>11</v>
       </c>
       <c r="C264">
-        <v>252.19056473178105</v>
+        <v>251.5484923617006</v>
       </c>
       <c r="D264">
-        <v>266.11917564083205</v>
+        <v>265.36885900799149</v>
       </c>
     </row>
     <row r="265" spans="1:4" x14ac:dyDescent="0.3">
@@ -4133,10 +4133,10 @@
         <v>12</v>
       </c>
       <c r="C265">
-        <v>223.12230029331994</v>
+        <v>222.76299285405602</v>
       </c>
       <c r="D265">
-        <v>218.77690900182324</v>
+        <v>218.35528990905249</v>
       </c>
     </row>
     <row r="266" spans="1:4" x14ac:dyDescent="0.3">
@@ -4147,10 +4147,10 @@
         <v>1</v>
       </c>
       <c r="C266">
-        <v>247.05117293272218</v>
+        <v>246.62372742958269</v>
       </c>
       <c r="D266">
-        <v>244.22146357676081</v>
+        <v>243.71587174201119</v>
       </c>
     </row>
     <row r="267" spans="1:4" x14ac:dyDescent="0.3">
@@ -4161,10 +4161,10 @@
         <v>2</v>
       </c>
       <c r="C267">
-        <v>175.84204770229255</v>
+        <v>175.48518048075968</v>
       </c>
       <c r="D267">
-        <v>178.28993257167937</v>
+        <v>177.86814789992968</v>
       </c>
     </row>
     <row r="268" spans="1:4" x14ac:dyDescent="0.3">
@@ -4175,10 +4175,10 @@
         <v>3</v>
       </c>
       <c r="C268">
-        <v>244.73080166888073</v>
+        <v>244.11788255599978</v>
       </c>
       <c r="D268">
-        <v>252.58262092839368</v>
+        <v>251.85882987638382</v>
       </c>
     </row>
     <row r="269" spans="1:4" x14ac:dyDescent="0.3">
@@ -4189,10 +4189,10 @@
         <v>4</v>
       </c>
       <c r="C269">
-        <v>194.37360131474179</v>
+        <v>193.89965683312334</v>
       </c>
       <c r="D269">
-        <v>205.48074475217291</v>
+        <v>204.92016884478554</v>
       </c>
     </row>
     <row r="270" spans="1:4" x14ac:dyDescent="0.3">
@@ -4203,10 +4203,10 @@
         <v>5</v>
       </c>
       <c r="C270">
-        <v>227.32490649001639</v>
+        <v>226.78967437213407</v>
       </c>
       <c r="D270">
-        <v>238.91021259031805</v>
+        <v>238.27451033946343</v>
       </c>
     </row>
     <row r="271" spans="1:4" x14ac:dyDescent="0.3">
@@ -4217,10 +4217,10 @@
         <v>6</v>
       </c>
       <c r="C271">
-        <v>327.99994373586088</v>
+        <v>327.03523606883186</v>
       </c>
       <c r="D271">
-        <v>351.1708384074168</v>
+        <v>350.03045891586095</v>
       </c>
     </row>
     <row r="272" spans="1:4" x14ac:dyDescent="0.3">
@@ -4231,10 +4231,10 @@
         <v>7</v>
       </c>
       <c r="C272">
-        <v>253.20206876061607</v>
+        <v>252.63888368057439</v>
       </c>
       <c r="D272">
-        <v>260.52012112601784</v>
+        <v>259.85619420747571</v>
       </c>
     </row>
     <row r="273" spans="1:4" x14ac:dyDescent="0.3">
@@ -4245,10 +4245,10 @@
         <v>8</v>
       </c>
       <c r="C273">
-        <v>294.98898696279264</v>
+        <v>294.39700116164812</v>
       </c>
       <c r="D273">
-        <v>293.89657686184836</v>
+        <v>293.19818026548529</v>
       </c>
     </row>
     <row r="274" spans="1:4" x14ac:dyDescent="0.3">
@@ -4259,10 +4259,10 @@
         <v>9</v>
       </c>
       <c r="C274">
-        <v>240.75323832092093</v>
+        <v>240.23526250901344</v>
       </c>
       <c r="D274">
-        <v>251.11609263197568</v>
+        <v>250.50445589675445</v>
       </c>
     </row>
     <row r="275" spans="1:4" x14ac:dyDescent="0.3">
@@ -4273,10 +4273,10 @@
         <v>10</v>
       </c>
       <c r="C275">
-        <v>204.28415774403234</v>
+        <v>203.92827165911427</v>
       </c>
       <c r="D275">
-        <v>209.37194271634667</v>
+        <v>208.95446486857173</v>
       </c>
     </row>
     <row r="276" spans="1:4" x14ac:dyDescent="0.3">
@@ -4287,10 +4287,10 @@
         <v>11</v>
       </c>
       <c r="C276">
-        <v>247.35763491445007</v>
+        <v>246.76265599512021</v>
       </c>
       <c r="D276">
-        <v>260.07058600419725</v>
+        <v>259.36974506762999</v>
       </c>
     </row>
     <row r="277" spans="1:4" x14ac:dyDescent="0.3">
@@ -4301,10 +4301,10 @@
         <v>12</v>
       </c>
       <c r="C277">
-        <v>235.18487734075856</v>
+        <v>234.68649485166162</v>
       </c>
       <c r="D277">
-        <v>245.21209363846179</v>
+        <v>244.62138653328199</v>
       </c>
     </row>
     <row r="278" spans="1:4" x14ac:dyDescent="0.3">
@@ -4315,10 +4315,10 @@
         <v>1</v>
       </c>
       <c r="C278">
-        <v>194.75234600357371</v>
+        <v>194.35931956728533</v>
       </c>
       <c r="D278">
-        <v>199.88896123200593</v>
+        <v>199.42663643617422</v>
       </c>
     </row>
     <row r="279" spans="1:4" x14ac:dyDescent="0.3">
@@ -4329,10 +4329,10 @@
         <v>2</v>
       </c>
       <c r="C279">
-        <v>198.96309256190844</v>
+        <v>198.65659597512538</v>
       </c>
       <c r="D279">
-        <v>198.45743598107808</v>
+        <v>198.09657304117113</v>
       </c>
     </row>
     <row r="280" spans="1:4" x14ac:dyDescent="0.3">
@@ -4343,10 +4343,10 @@
         <v>3</v>
       </c>
       <c r="C280">
-        <v>320.60580447712516</v>
+        <v>320.25775855449734</v>
       </c>
       <c r="D280">
-        <v>311.97583850746054</v>
+        <v>311.56790130141098</v>
       </c>
     </row>
     <row r="281" spans="1:4" x14ac:dyDescent="0.3">
@@ -4357,10 +4357,10 @@
         <v>4</v>
       </c>
       <c r="C281">
-        <v>332.06267084473586</v>
+        <v>331.55608303731066</v>
       </c>
       <c r="D281">
-        <v>335.57658988022098</v>
+        <v>334.97665943936892</v>
       </c>
     </row>
     <row r="282" spans="1:4" x14ac:dyDescent="0.3">
@@ -4371,10 +4371,10 @@
         <v>5</v>
       </c>
       <c r="C282">
-        <v>421.50885868942237</v>
+        <v>420.74178132771971</v>
       </c>
       <c r="D282">
-        <v>425.02321189833759</v>
+        <v>424.1125449663939</v>
       </c>
     </row>
     <row r="283" spans="1:4" x14ac:dyDescent="0.3">
@@ -4385,10 +4385,10 @@
         <v>6</v>
       </c>
       <c r="C283">
-        <v>314.92170414929086</v>
+        <v>314.26848288666866</v>
       </c>
       <c r="D283">
-        <v>325.90556348156531</v>
+        <v>325.13351340712103</v>
       </c>
     </row>
     <row r="284" spans="1:4" x14ac:dyDescent="0.3">
@@ -4399,10 +4399,10 @@
         <v>7</v>
       </c>
       <c r="C284">
-        <v>317.45809960293161</v>
+        <v>316.94937274021834</v>
       </c>
       <c r="D284">
-        <v>309.30381434110024</v>
+        <v>308.70496463984534</v>
       </c>
     </row>
     <row r="285" spans="1:4" x14ac:dyDescent="0.3">
@@ -4413,10 +4413,10 @@
         <v>8</v>
       </c>
       <c r="C285">
-        <v>294.93607517430445</v>
+        <v>294.22599297265356</v>
       </c>
       <c r="D285">
-        <v>305.26781303475025</v>
+        <v>304.4329421174711</v>
       </c>
     </row>
     <row r="286" spans="1:4" x14ac:dyDescent="0.3">
@@ -4427,10 +4427,10 @@
         <v>9</v>
       </c>
       <c r="C286">
-        <v>315.58050783374978</v>
+        <v>314.81730891139438</v>
       </c>
       <c r="D286">
-        <v>328.90586601501792</v>
+        <v>328.00333062977825</v>
       </c>
     </row>
     <row r="287" spans="1:4" x14ac:dyDescent="0.3">
@@ -4441,10 +4441,10 @@
         <v>10</v>
       </c>
       <c r="C287">
-        <v>310.72365324566243</v>
+        <v>310.06682621958123</v>
       </c>
       <c r="D287">
-        <v>313.94323343152337</v>
+        <v>313.18465651012497</v>
       </c>
     </row>
     <row r="288" spans="1:4" x14ac:dyDescent="0.3">
@@ -4455,10 +4455,10 @@
         <v>11</v>
       </c>
       <c r="C288">
-        <v>405.93904467406549</v>
+        <v>404.88362010605658</v>
       </c>
       <c r="D288">
-        <v>422.87876484736404</v>
+        <v>421.64403409906873</v>
       </c>
     </row>
     <row r="289" spans="1:4" x14ac:dyDescent="0.3">
@@ -4469,10 +4469,10 @@
         <v>12</v>
       </c>
       <c r="C289">
-        <v>308.05790202889614</v>
+        <v>307.36724934943396</v>
       </c>
       <c r="D289">
-        <v>315.92576926846226</v>
+        <v>315.11383979727316</v>
       </c>
     </row>
     <row r="290" spans="1:4" x14ac:dyDescent="0.3">
@@ -4483,10 +4483,10 @@
         <v>1</v>
       </c>
       <c r="C290">
-        <v>277.09725421638399</v>
+        <v>276.47805036665352</v>
       </c>
       <c r="D290">
-        <v>284.02349086262097</v>
+        <v>283.31878145527418</v>
       </c>
     </row>
     <row r="291" spans="1:4" x14ac:dyDescent="0.3">
@@ -4497,10 +4497,10 @@
         <v>2</v>
       </c>
       <c r="C291">
-        <v>197.82407412842264</v>
+        <v>197.43269227664675</v>
       </c>
       <c r="D291">
-        <v>200.61254936694937</v>
+        <v>200.16798918569179</v>
       </c>
     </row>
     <row r="292" spans="1:4" x14ac:dyDescent="0.3">
@@ -4511,10 +4511,10 @@
         <v>3</v>
       </c>
       <c r="C292">
-        <v>216.36902066617213</v>
+        <v>215.87111120794535</v>
       </c>
       <c r="D292">
-        <v>222.09831227965185</v>
+        <v>221.53261501859527</v>
       </c>
     </row>
     <row r="293" spans="1:4" x14ac:dyDescent="0.3">
@@ -4525,10 +4525,10 @@
         <v>4</v>
       </c>
       <c r="C293">
-        <v>198.70956853858135</v>
+        <v>198.23460321243005</v>
       </c>
       <c r="D293">
-        <v>207.0239541429045</v>
+        <v>206.48369580672235</v>
       </c>
     </row>
     <row r="294" spans="1:4" x14ac:dyDescent="0.3">
@@ -4539,10 +4539,10 @@
         <v>5</v>
       </c>
       <c r="C294">
-        <v>176.54403078475795</v>
+        <v>176.19199724303462</v>
       </c>
       <c r="D294">
-        <v>180.30036684389026</v>
+        <v>179.89884290197725</v>
       </c>
     </row>
     <row r="295" spans="1:4" x14ac:dyDescent="0.3">
@@ -4553,10 +4553,10 @@
         <v>6</v>
       </c>
       <c r="C295">
-        <v>174.02100611018989</v>
+        <v>173.66680625587492</v>
       </c>
       <c r="D295">
-        <v>181.63906190658599</v>
+        <v>181.23428421323726</v>
       </c>
     </row>
     <row r="296" spans="1:4" x14ac:dyDescent="0.3">
@@ -4567,10 +4567,10 @@
         <v>7</v>
       </c>
       <c r="C296">
-        <v>192.491695508742</v>
+        <v>192.115411161683</v>
       </c>
       <c r="D296">
-        <v>191.08561132730622</v>
+        <v>190.65836251606945</v>
       </c>
     </row>
     <row r="297" spans="1:4" x14ac:dyDescent="0.3">
@@ -4581,10 +4581,10 @@
         <v>8</v>
       </c>
       <c r="C297">
-        <v>205.9261328729086</v>
+        <v>205.43640095535491</v>
       </c>
       <c r="D297">
-        <v>210.78926991378827</v>
+        <v>210.23411722809971</v>
       </c>
     </row>
     <row r="298" spans="1:4" x14ac:dyDescent="0.3">
@@ -4595,10 +4595,10 @@
         <v>9</v>
       </c>
       <c r="C298">
-        <v>216.10833278656173</v>
+        <v>215.6718122403102</v>
       </c>
       <c r="D298">
-        <v>220.55357403557014</v>
+        <v>220.05266910688033</v>
       </c>
     </row>
     <row r="299" spans="1:4" x14ac:dyDescent="0.3">
@@ -4609,10 +4609,10 @@
         <v>10</v>
       </c>
       <c r="C299">
-        <v>191.34995444829494</v>
+        <v>190.87943818953735</v>
       </c>
       <c r="D299">
-        <v>196.04673649097171</v>
+        <v>195.53073812288125</v>
       </c>
     </row>
     <row r="300" spans="1:4" x14ac:dyDescent="0.3">
@@ -4623,10 +4623,10 @@
         <v>11</v>
       </c>
       <c r="C300">
-        <v>234.01104343606406</v>
+        <v>233.44966912494121</v>
       </c>
       <c r="D300">
-        <v>235.54847159650816</v>
+        <v>234.91654455772948</v>
       </c>
     </row>
     <row r="301" spans="1:4" x14ac:dyDescent="0.3">
@@ -4637,10 +4637,10 @@
         <v>12</v>
       </c>
       <c r="C301">
-        <v>264.45682047423071</v>
+        <v>263.88593707362116</v>
       </c>
       <c r="D301">
-        <v>268.4616988956613</v>
+        <v>267.81439306043461</v>
       </c>
     </row>
     <row r="302" spans="1:4" x14ac:dyDescent="0.3">
@@ -4651,10 +4651,10 @@
         <v>1</v>
       </c>
       <c r="C302">
-        <v>226.96891400964307</v>
+        <v>226.45670542820747</v>
       </c>
       <c r="D302">
-        <v>234.45925355920116</v>
+        <v>233.86611032758714</v>
       </c>
     </row>
     <row r="303" spans="1:4" x14ac:dyDescent="0.3">
@@ -4665,10 +4665,10 @@
         <v>2</v>
       </c>
       <c r="C303">
-        <v>178.83372859445495</v>
+        <v>178.5644403903801</v>
       </c>
       <c r="D303">
-        <v>186.82651551688826</v>
+        <v>186.51485304517678</v>
       </c>
     </row>
     <row r="304" spans="1:4" x14ac:dyDescent="0.3">
@@ -4679,10 +4679,10 @@
         <v>3</v>
       </c>
       <c r="C304">
-        <v>302.99930541266559</v>
+        <v>302.42345510638739</v>
       </c>
       <c r="D304">
-        <v>306.59568499367873</v>
+        <v>305.92876637859626</v>
       </c>
     </row>
     <row r="305" spans="1:4" x14ac:dyDescent="0.3">
@@ -4693,10 +4693,10 @@
         <v>4</v>
       </c>
       <c r="C305">
-        <v>273.97223975254053</v>
+        <v>273.42980674046532</v>
       </c>
       <c r="D305">
-        <v>288.96710957763543</v>
+        <v>288.33916396727528</v>
       </c>
     </row>
     <row r="306" spans="1:4" x14ac:dyDescent="0.3">
@@ -4707,10 +4707,10 @@
         <v>5</v>
       </c>
       <c r="C306">
-        <v>281.74743731147765</v>
+        <v>281.12795372087572</v>
       </c>
       <c r="D306">
-        <v>291.5508821770336</v>
+        <v>290.83328593730448</v>
       </c>
     </row>
     <row r="307" spans="1:4" x14ac:dyDescent="0.3">
@@ -4721,10 +4721,10 @@
         <v>6</v>
       </c>
       <c r="C307">
-        <v>253.30670977856278</v>
+        <v>252.80778671715754</v>
       </c>
       <c r="D307">
-        <v>266.2320802190257</v>
+        <v>265.64971282286695</v>
       </c>
     </row>
     <row r="308" spans="1:4" x14ac:dyDescent="0.3">
@@ -4735,10 +4735,10 @@
         <v>7</v>
       </c>
       <c r="C308">
-        <v>298.90264447182597</v>
+        <v>298.31313276205225</v>
       </c>
       <c r="D308">
-        <v>306.49098948042547</v>
+        <v>305.81025857980325</v>
       </c>
     </row>
     <row r="309" spans="1:4" x14ac:dyDescent="0.3">
@@ -4749,10 +4749,10 @@
         <v>8</v>
       </c>
       <c r="C309">
-        <v>240.03169198330377</v>
+        <v>239.61456649887785</v>
       </c>
       <c r="D309">
-        <v>242.563560941931</v>
+        <v>242.08024728261972</v>
       </c>
     </row>
     <row r="310" spans="1:4" x14ac:dyDescent="0.3">
@@ -4763,10 +4763,10 @@
         <v>9</v>
       </c>
       <c r="C310">
-        <v>252.98001900987583</v>
+        <v>252.61450778808256</v>
       </c>
       <c r="D310">
-        <v>254.74969002399541</v>
+        <v>254.32246218163783</v>
       </c>
     </row>
     <row r="311" spans="1:4" x14ac:dyDescent="0.3">
@@ -4777,10 +4777,10 @@
         <v>10</v>
       </c>
       <c r="C311">
-        <v>269.5576916546932</v>
+        <v>269.05464705747062</v>
       </c>
       <c r="D311">
-        <v>269.94973781523379</v>
+        <v>269.38167308003312</v>
       </c>
     </row>
     <row r="312" spans="1:4" x14ac:dyDescent="0.3">
@@ -4791,10 +4791,10 @@
         <v>11</v>
       </c>
       <c r="C312">
-        <v>317.71710554921054</v>
+        <v>316.95929795087574</v>
       </c>
       <c r="D312">
-        <v>328.29761586117729</v>
+        <v>327.42631946284712</v>
       </c>
     </row>
     <row r="313" spans="1:4" x14ac:dyDescent="0.3">
@@ -4805,10 +4805,10 @@
         <v>12</v>
       </c>
       <c r="C313">
-        <v>244.86427508862499</v>
+        <v>244.35662154604373</v>
       </c>
       <c r="D313">
-        <v>256.71220950155976</v>
+        <v>256.12586888296181</v>
       </c>
     </row>
     <row r="314" spans="1:4" x14ac:dyDescent="0.3">
@@ -4819,10 +4819,10 @@
         <v>1</v>
       </c>
       <c r="C314">
-        <v>221.26600178887702</v>
+        <v>220.85253806352262</v>
       </c>
       <c r="D314">
-        <v>229.9478413661854</v>
+        <v>229.43470907073205</v>
       </c>
     </row>
     <row r="315" spans="1:4" x14ac:dyDescent="0.3">
@@ -4833,10 +4833,10 @@
         <v>2</v>
       </c>
       <c r="C315">
-        <v>246.63108578842946</v>
+        <v>246.0730616199894</v>
       </c>
       <c r="D315">
-        <v>264.2695590895259</v>
+        <v>263.5794920922101</v>
       </c>
     </row>
     <row r="316" spans="1:4" x14ac:dyDescent="0.3">
@@ -4847,10 +4847,10 @@
         <v>3</v>
       </c>
       <c r="C316">
-        <v>320.95409558863645</v>
+        <v>320.16716632020103</v>
       </c>
       <c r="D316">
-        <v>340.95673959388978</v>
+        <v>339.98251718731456</v>
       </c>
     </row>
     <row r="317" spans="1:4" x14ac:dyDescent="0.3">
@@ -4861,10 +4861,10 @@
         <v>4</v>
       </c>
       <c r="C317">
-        <v>260.43906613767416</v>
+        <v>259.84356673092952</v>
       </c>
       <c r="D317">
-        <v>285.21951030653582</v>
+        <v>284.48181610332347</v>
       </c>
     </row>
     <row r="318" spans="1:4" x14ac:dyDescent="0.3">
@@ -4875,10 +4875,10 @@
         <v>5</v>
       </c>
       <c r="C318">
-        <v>215.11254656471712</v>
+        <v>214.75975620400095</v>
       </c>
       <c r="D318">
-        <v>214.49991156462869</v>
+        <v>214.06243660530828</v>
       </c>
     </row>
     <row r="319" spans="1:4" x14ac:dyDescent="0.3">
@@ -4889,10 +4889,10 @@
         <v>6</v>
       </c>
       <c r="C319">
-        <v>225.98622140603393</v>
+        <v>225.56617001966492</v>
       </c>
       <c r="D319">
-        <v>239.01659342224175</v>
+        <v>238.49183581826145</v>
       </c>
     </row>
     <row r="320" spans="1:4" x14ac:dyDescent="0.3">
@@ -4903,10 +4903,10 @@
         <v>7</v>
       </c>
       <c r="C320">
-        <v>195.58813001308849</v>
+        <v>195.2059297359298</v>
       </c>
       <c r="D320">
-        <v>203.7424290637706</v>
+        <v>203.27500104337264</v>
       </c>
     </row>
     <row r="321" spans="1:4" x14ac:dyDescent="0.3">
@@ -4917,10 +4917,10 @@
         <v>8</v>
       </c>
       <c r="C321">
-        <v>178.84707900083797</v>
+        <v>178.50173248162628</v>
       </c>
       <c r="D321">
-        <v>189.04821747516422</v>
+        <v>188.62060206145676</v>
       </c>
     </row>
     <row r="322" spans="1:4" x14ac:dyDescent="0.3">
@@ -4931,10 +4931,10 @@
         <v>9</v>
       </c>
       <c r="C322">
-        <v>204.82686539781875</v>
+        <v>204.47967522082536</v>
       </c>
       <c r="D322">
-        <v>213.85829750902445</v>
+        <v>213.42144221891957</v>
       </c>
     </row>
     <row r="323" spans="1:4" x14ac:dyDescent="0.3">
@@ -4945,10 +4945,10 @@
         <v>10</v>
       </c>
       <c r="C323">
-        <v>193.41911024688079</v>
+        <v>193.08905907205227</v>
       </c>
       <c r="D323">
-        <v>199.84918679111294</v>
+        <v>199.45899664045706</v>
       </c>
     </row>
     <row r="324" spans="1:4" x14ac:dyDescent="0.3">
@@ -4959,10 +4959,10 @@
         <v>11</v>
       </c>
       <c r="C324">
-        <v>211.63040001006149</v>
+        <v>211.23745638540998</v>
       </c>
       <c r="D324">
-        <v>221.71643019146018</v>
+        <v>221.23947372757539</v>
       </c>
     </row>
     <row r="325" spans="1:4" x14ac:dyDescent="0.3">
@@ -4973,10 +4973,10 @@
         <v>12</v>
       </c>
       <c r="C325">
-        <v>227.86503313474938</v>
+        <v>227.3862800587525</v>
       </c>
       <c r="D325">
-        <v>250.6849982388583</v>
+        <v>250.09286943195727</v>
       </c>
     </row>
     <row r="326" spans="1:4" x14ac:dyDescent="0.3">
@@ -4987,10 +4987,10 @@
         <v>1</v>
       </c>
       <c r="C326">
-        <v>245.0900914283761</v>
+        <v>244.54239744865757</v>
       </c>
       <c r="D326">
-        <v>263.93076571993646</v>
+        <v>263.24541202160128</v>
       </c>
     </row>
     <row r="327" spans="1:4" x14ac:dyDescent="0.3">
@@ -5001,10 +5001,10 @@
         <v>2</v>
       </c>
       <c r="C327">
-        <v>170.67391596914027</v>
+        <v>170.41360779469005</v>
       </c>
       <c r="D327">
-        <v>182.33397287735565</v>
+        <v>182.00786071904193</v>
       </c>
     </row>
     <row r="328" spans="1:4" x14ac:dyDescent="0.3">
@@ -5015,10 +5015,10 @@
         <v>3</v>
       </c>
       <c r="C328">
-        <v>182.75468222114586</v>
+        <v>182.39498135733737</v>
       </c>
       <c r="D328">
-        <v>190.35040012838181</v>
+        <v>189.89753721535533</v>
       </c>
     </row>
     <row r="329" spans="1:4" x14ac:dyDescent="0.3">
@@ -5029,10 +5029,10 @@
         <v>4</v>
       </c>
       <c r="C329">
-        <v>174.16575420015351</v>
+        <v>173.91542382619409</v>
       </c>
       <c r="D329">
-        <v>178.46006789004423</v>
+        <v>178.14568033070077</v>
       </c>
     </row>
     <row r="330" spans="1:4" x14ac:dyDescent="0.3">
@@ -5043,10 +5043,10 @@
         <v>5</v>
       </c>
       <c r="C330">
-        <v>187.67452172292718</v>
+        <v>187.36681591320436</v>
       </c>
       <c r="D330">
-        <v>191.7909143576972</v>
+        <v>191.40401142926817</v>
       </c>
     </row>
     <row r="331" spans="1:4" x14ac:dyDescent="0.3">
@@ -5057,10 +5057,10 @@
         <v>6</v>
       </c>
       <c r="C331">
-        <v>175.69562532542903</v>
+        <v>175.53900858089676</v>
       </c>
       <c r="D331">
-        <v>175.81511519472281</v>
+        <v>175.6118807949544</v>
       </c>
     </row>
     <row r="332" spans="1:4" x14ac:dyDescent="0.3">
@@ -5071,10 +5071,10 @@
         <v>7</v>
       </c>
       <c r="C332">
-        <v>233.73497508796581</v>
+        <v>233.2874927222027</v>
       </c>
       <c r="D332">
-        <v>245.42028142979427</v>
+        <v>244.8646092924179</v>
       </c>
     </row>
     <row r="333" spans="1:4" x14ac:dyDescent="0.3">
@@ -5085,10 +5085,10 @@
         <v>8</v>
       </c>
       <c r="C333">
-        <v>194.88700385623156</v>
+        <v>194.5871068045075</v>
       </c>
       <c r="D333">
-        <v>202.57627138181851</v>
+        <v>202.19846658538549</v>
       </c>
     </row>
     <row r="334" spans="1:4" x14ac:dyDescent="0.3">
@@ -5099,10 +5099,10 @@
         <v>9</v>
       </c>
       <c r="C334">
-        <v>206.06839623165021</v>
+        <v>205.76488066628005</v>
       </c>
       <c r="D334">
-        <v>212.01406586256172</v>
+        <v>211.62606641729235</v>
       </c>
     </row>
     <row r="335" spans="1:4" x14ac:dyDescent="0.3">
@@ -5113,10 +5113,10 @@
         <v>10</v>
       </c>
       <c r="C335">
-        <v>209.04188689302484</v>
+        <v>208.60713973687507</v>
       </c>
       <c r="D335">
-        <v>215.82757297890333</v>
+        <v>215.30477819474424</v>
       </c>
     </row>
     <row r="336" spans="1:4" x14ac:dyDescent="0.3">
@@ -5127,10 +5127,10 @@
         <v>11</v>
       </c>
       <c r="C336">
-        <v>286.60025612047684</v>
+        <v>286.1715654702279</v>
       </c>
       <c r="D336">
-        <v>282.51316665393438</v>
+        <v>281.98094916909332</v>
       </c>
     </row>
     <row r="337" spans="1:4" x14ac:dyDescent="0.3">
@@ -5141,10 +5141,10 @@
         <v>12</v>
       </c>
       <c r="C337">
-        <v>332.45858266227816</v>
+        <v>331.88483601953277</v>
       </c>
       <c r="D337">
-        <v>337.5859169100238</v>
+        <v>336.72508880396026</v>
       </c>
     </row>
     <row r="338" spans="1:4" x14ac:dyDescent="0.3">
@@ -5155,10 +5155,10 @@
         <v>1</v>
       </c>
       <c r="C338">
-        <v>313.37481995372525</v>
+        <v>312.89797654305369</v>
       </c>
       <c r="D338">
-        <v>310.51677155956963</v>
+        <v>309.68000775827858</v>
       </c>
     </row>
     <row r="339" spans="1:4" x14ac:dyDescent="0.3">
@@ -5169,10 +5169,10 @@
         <v>2</v>
       </c>
       <c r="C339">
-        <v>331.12887063282432</v>
+        <v>330.80587857445784</v>
       </c>
       <c r="D339">
-        <v>320.83451104800366</v>
+        <v>319.9595703778059</v>
       </c>
     </row>
     <row r="340" spans="1:4" x14ac:dyDescent="0.3">
@@ -5183,10 +5183,10 @@
         <v>3</v>
       </c>
       <c r="C340">
-        <v>473.87762492917579</v>
+        <v>473.86809065435637</v>
       </c>
       <c r="D340">
-        <v>460.00608862166638</v>
+        <v>459.37896184566586</v>
       </c>
     </row>
     <row r="341" spans="1:4" x14ac:dyDescent="0.3">
@@ -5197,10 +5197,10 @@
         <v>4</v>
       </c>
       <c r="C341">
-        <v>629.10734632561309</v>
+        <v>628.11525280876424</v>
       </c>
       <c r="D341">
-        <v>586.1978822275637</v>
+        <v>584.65212754255742</v>
       </c>
     </row>
     <row r="342" spans="1:4" x14ac:dyDescent="0.3">
@@ -5211,10 +5211,10 @@
         <v>5</v>
       </c>
       <c r="C342">
-        <v>518.30578992573055</v>
+        <v>517.2872310382146</v>
       </c>
       <c r="D342">
-        <v>486.33346173725903</v>
+        <v>484.71578432716711</v>
       </c>
     </row>
     <row r="343" spans="1:4" x14ac:dyDescent="0.3">
@@ -5225,10 +5225,10 @@
         <v>6</v>
       </c>
       <c r="C343">
-        <v>372.2638063309941</v>
+        <v>371.66034760749568</v>
       </c>
       <c r="D343">
-        <v>359.44422579993574</v>
+        <v>358.55888236939552</v>
       </c>
     </row>
     <row r="344" spans="1:4" x14ac:dyDescent="0.3">
@@ -5239,10 +5239,10 @@
         <v>7</v>
       </c>
       <c r="C344">
-        <v>412.66240265870243</v>
+        <v>412.35583625732295</v>
       </c>
       <c r="D344">
-        <v>396.01465039549845</v>
+        <v>395.34453389485452</v>
       </c>
     </row>
     <row r="345" spans="1:4" x14ac:dyDescent="0.3">
@@ -5253,10 +5253,10 @@
         <v>8</v>
       </c>
       <c r="C345">
-        <v>340.89051998494881</v>
+        <v>348.55903429722025</v>
       </c>
       <c r="D345">
-        <v>326.83528866439542</v>
+        <v>332.07479705017988</v>
       </c>
     </row>
     <row r="346" spans="1:4" x14ac:dyDescent="0.3">
@@ -5267,14 +5267,28 @@
         <v>9</v>
       </c>
       <c r="C346">
-        <v>302.70154021403499</v>
+        <v>311.53140085687312</v>
       </c>
       <c r="D346">
-        <v>291.05219047736955</v>
-      </c>
-    </row>
-    <row r="348" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A348" t="s">
+        <v>297.6189053615164</v>
+      </c>
+    </row>
+    <row r="347" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A347">
+        <v>2025</v>
+      </c>
+      <c r="B347">
+        <v>10</v>
+      </c>
+      <c r="C347">
+        <v>389.43001518245899</v>
+      </c>
+      <c r="D347">
+        <v>404.56293470540879</v>
+      </c>
+    </row>
+    <row r="349" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A349" t="s">
         <v>4</v>
       </c>
     </row>

--- a/00.data/01.incertezas/Global_Policy_Uncertainty_Data.xlsx
+++ b/00.data/01.incertezas/Global_Policy_Uncertainty_Data.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29426"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kms12\Documents\R\EPU\Monthly Files\2025-11-17\Submission 2025-11-21\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kms12\Documents\R\EPU\Monthly Files\2025-12-16\Submission 2025-12-30\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6FA747CA-6362-453B-801B-D1A06A97AA11}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2AEE60D6-2964-406D-9352-E4311B0BF9EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -426,7 +426,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D349"/>
+  <dimension ref="A1:D350"/>
   <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.3">
@@ -451,10 +451,10 @@
         <v>1</v>
       </c>
       <c r="C2">
-        <v>75.741271974917922</v>
+        <v>76.059427308815501</v>
       </c>
       <c r="D2">
-        <v>78.956962338546234</v>
+        <v>79.856772116595351</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.3">
@@ -465,10 +465,10 @@
         <v>2</v>
       </c>
       <c r="C3">
-        <v>76.076042743994904</v>
+        <v>76.286022725961487</v>
       </c>
       <c r="D3">
-        <v>75.59514446381327</v>
+        <v>75.828219584804401</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.3">
@@ -479,10 +479,10 @@
         <v>3</v>
       </c>
       <c r="C4">
-        <v>66.713953414947468</v>
+        <v>66.810541023810302</v>
       </c>
       <c r="D4">
-        <v>64.571995448278926</v>
+        <v>64.850547128999608</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.3">
@@ -493,10 +493,10 @@
         <v>4</v>
       </c>
       <c r="C5">
-        <v>71.674360425624855</v>
+        <v>71.716550770602723</v>
       </c>
       <c r="D5">
-        <v>71.665830735704347</v>
+        <v>71.855862852473109</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.3">
@@ -507,10 +507,10 @@
         <v>5</v>
       </c>
       <c r="C6">
-        <v>75.49898252954236</v>
+        <v>75.229731446306516</v>
       </c>
       <c r="D6">
-        <v>82.644865614066916</v>
+        <v>82.058364990486098</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.3">
@@ -521,10 +521,10 @@
         <v>6</v>
       </c>
       <c r="C7">
-        <v>79.464736680604275</v>
+        <v>79.30427370431282</v>
       </c>
       <c r="D7">
-        <v>82.923131972643333</v>
+        <v>82.500800657829259</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.3">
@@ -535,10 +535,10 @@
         <v>7</v>
       </c>
       <c r="C8">
-        <v>66.059779564206423</v>
+        <v>66.132049524870581</v>
       </c>
       <c r="D8">
-        <v>66.468540431614869</v>
+        <v>66.695377054512136</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.3">
@@ -549,10 +549,10 @@
         <v>8</v>
       </c>
       <c r="C9">
-        <v>62.882588072218006</v>
+        <v>63.428782663780389</v>
       </c>
       <c r="D9">
-        <v>58.197200450363866</v>
+        <v>59.475917489419281</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.3">
@@ -563,10 +563,10 @@
         <v>9</v>
       </c>
       <c r="C10">
-        <v>66.022761864324622</v>
+        <v>66.871417913628022</v>
       </c>
       <c r="D10">
-        <v>61.058892961155038</v>
+        <v>63.038297189349983</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.3">
@@ -577,10 +577,10 @@
         <v>10</v>
       </c>
       <c r="C11">
-        <v>81.711155273417205</v>
+        <v>82.35544771105728</v>
       </c>
       <c r="D11">
-        <v>76.079478789908848</v>
+        <v>77.7616262046798</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.3">
@@ -591,10 +591,10 @@
         <v>11</v>
       </c>
       <c r="C12">
-        <v>93.562786052259213</v>
+        <v>95.76485893019192</v>
       </c>
       <c r="D12">
-        <v>84.848888510154637</v>
+        <v>90.141538837605992</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.3">
@@ -605,10 +605,10 @@
         <v>12</v>
       </c>
       <c r="C13">
-        <v>104.86962521486274</v>
+        <v>107.06244802382213</v>
       </c>
       <c r="D13">
-        <v>93.288841785802319</v>
+        <v>98.93286306015311</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.3">
@@ -619,10 +619,10 @@
         <v>1</v>
       </c>
       <c r="C14">
-        <v>95.486482633788128</v>
+        <v>97.507329014474678</v>
       </c>
       <c r="D14">
-        <v>89.091089046791879</v>
+        <v>94.046515552952087</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.3">
@@ -633,10 +633,10 @@
         <v>2</v>
       </c>
       <c r="C15">
-        <v>82.305402880717622</v>
+        <v>83.565447221457674</v>
       </c>
       <c r="D15">
-        <v>76.394379378260453</v>
+        <v>79.588620930384593</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.3">
@@ -647,10 +647,10 @@
         <v>3</v>
       </c>
       <c r="C16">
-        <v>83.904021815981707</v>
+        <v>85.551147883106864</v>
       </c>
       <c r="D16">
-        <v>76.678629226405391</v>
+        <v>80.689812472196465</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.3">
@@ -661,10 +661,10 @@
         <v>4</v>
       </c>
       <c r="C17">
-        <v>78.404300080683782</v>
+        <v>80.031156789039173</v>
       </c>
       <c r="D17">
-        <v>72.315120241281676</v>
+        <v>76.423556109348638</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.3">
@@ -675,10 +675,10 @@
         <v>5</v>
       </c>
       <c r="C18">
-        <v>84.88282871996428</v>
+        <v>86.598931006241159</v>
       </c>
       <c r="D18">
-        <v>78.74670606033294</v>
+        <v>82.745962530973316</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.3">
@@ -689,10 +689,10 @@
         <v>6</v>
       </c>
       <c r="C19">
-        <v>82.59879531237199</v>
+        <v>84.207331121679616</v>
       </c>
       <c r="D19">
-        <v>76.913655011295972</v>
+        <v>80.893326486840877</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.3">
@@ -703,10 +703,10 @@
         <v>7</v>
       </c>
       <c r="C20">
-        <v>99.661022668137235</v>
+        <v>101.87812393889836</v>
       </c>
       <c r="D20">
-        <v>92.634730937769731</v>
+        <v>97.954434597259009</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.3">
@@ -717,10 +717,10 @@
         <v>8</v>
       </c>
       <c r="C21">
-        <v>112.88676109434741</v>
+        <v>115.2810019054193</v>
       </c>
       <c r="D21">
-        <v>104.03405217450583</v>
+        <v>109.47525986764889</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.3">
@@ -731,10 +731,10 @@
         <v>9</v>
       </c>
       <c r="C22">
-        <v>143.43068625949803</v>
+        <v>144.60407151025601</v>
       </c>
       <c r="D22">
-        <v>142.45621416166168</v>
+        <v>145.15702517256341</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.3">
@@ -745,10 +745,10 @@
         <v>10</v>
       </c>
       <c r="C23">
-        <v>117.28978490824011</v>
+        <v>119.13000585377694</v>
       </c>
       <c r="D23">
-        <v>108.8959631388216</v>
+        <v>113.21635375184974</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.3">
@@ -759,10 +759,10 @@
         <v>11</v>
       </c>
       <c r="C24">
-        <v>96.897584529865966</v>
+        <v>97.500811291270082</v>
       </c>
       <c r="D24">
-        <v>90.270998857486489</v>
+        <v>91.807127193986375</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.3">
@@ -773,10 +773,10 @@
         <v>12</v>
       </c>
       <c r="C25">
-        <v>91.497155512588549</v>
+        <v>92.32681946400362</v>
       </c>
       <c r="D25">
-        <v>89.142614723016663</v>
+        <v>90.799677860718319</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.3">
@@ -787,10 +787,10 @@
         <v>1</v>
       </c>
       <c r="C26">
-        <v>94.613555897534269</v>
+        <v>95.155116163418342</v>
       </c>
       <c r="D26">
-        <v>91.292705367495302</v>
+        <v>92.331235068822494</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.3">
@@ -801,10 +801,10 @@
         <v>2</v>
       </c>
       <c r="C27">
-        <v>78.375353224557017</v>
+        <v>78.800036571351853</v>
       </c>
       <c r="D27">
-        <v>74.581348825718038</v>
+        <v>75.774288599104878</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.3">
@@ -815,10 +815,10 @@
         <v>3</v>
       </c>
       <c r="C28">
-        <v>61.848730858458445</v>
+        <v>62.356786639999761</v>
       </c>
       <c r="D28">
-        <v>56.437649029044834</v>
+        <v>57.548676021393582</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.3">
@@ -829,10 +829,10 @@
         <v>4</v>
       </c>
       <c r="C29">
-        <v>65.0666578411807</v>
+        <v>65.402097271664701</v>
       </c>
       <c r="D29">
-        <v>63.263372900847777</v>
+        <v>64.03573239636394</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.3">
@@ -843,10 +843,10 @@
         <v>5</v>
       </c>
       <c r="C30">
-        <v>68.581072312852143</v>
+        <v>69.413250965001467</v>
       </c>
       <c r="D30">
-        <v>67.442301378869828</v>
+        <v>69.413358963645905</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.3">
@@ -857,10 +857,10 @@
         <v>6</v>
       </c>
       <c r="C31">
-        <v>69.730600844356886</v>
+        <v>70.090584606597034</v>
       </c>
       <c r="D31">
-        <v>66.828817347899331</v>
+        <v>67.60325367294196</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.3">
@@ -871,10 +871,10 @@
         <v>7</v>
       </c>
       <c r="C32">
-        <v>71.759326676688787</v>
+        <v>71.877411573209699</v>
       </c>
       <c r="D32">
-        <v>69.911706624109186</v>
+        <v>70.336576218004154</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.3">
@@ -885,10 +885,10 @@
         <v>8</v>
       </c>
       <c r="C33">
-        <v>64.838825179004175</v>
+        <v>64.991248680877177</v>
       </c>
       <c r="D33">
-        <v>67.58128577468824</v>
+        <v>67.952090020034404</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.3">
@@ -899,10 +899,10 @@
         <v>9</v>
       </c>
       <c r="C34">
-        <v>65.664987011020742</v>
+        <v>65.990342830105561</v>
       </c>
       <c r="D34">
-        <v>61.436560592437942</v>
+        <v>62.111644015007251</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.3">
@@ -913,10 +913,10 @@
         <v>10</v>
       </c>
       <c r="C35">
-        <v>65.329385570292928</v>
+        <v>65.465529075929695</v>
       </c>
       <c r="D35">
-        <v>65.961620630961846</v>
+        <v>66.516596572864657</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.3">
@@ -927,10 +927,10 @@
         <v>11</v>
       </c>
       <c r="C36">
-        <v>67.988962847201478</v>
+        <v>68.000994152029008</v>
       </c>
       <c r="D36">
-        <v>64.880002960339056</v>
+        <v>64.913213753296404</v>
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.3">
@@ -941,10 +941,10 @@
         <v>12</v>
       </c>
       <c r="C37">
-        <v>60.791443824699634</v>
+        <v>60.744667671197206</v>
       </c>
       <c r="D37">
-        <v>57.849748743464836</v>
+        <v>57.968837470831929</v>
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.3">
@@ -955,10 +955,10 @@
         <v>1</v>
       </c>
       <c r="C38">
-        <v>65.26429532311559</v>
+        <v>65.061983114608452</v>
       </c>
       <c r="D38">
-        <v>66.361770280124475</v>
+        <v>65.994709160160212</v>
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.3">
@@ -969,10 +969,10 @@
         <v>2</v>
       </c>
       <c r="C39">
-        <v>59.302564206118653</v>
+        <v>59.25342264879275</v>
       </c>
       <c r="D39">
-        <v>55.56510488772031</v>
+        <v>55.471225459091478</v>
       </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.3">
@@ -983,10 +983,10 @@
         <v>3</v>
       </c>
       <c r="C40">
-        <v>61.953916818540655</v>
+        <v>61.726901696838702</v>
       </c>
       <c r="D40">
-        <v>60.524437341035785</v>
+        <v>60.170193355054302</v>
       </c>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.3">
@@ -997,10 +997,10 @@
         <v>4</v>
       </c>
       <c r="C41">
-        <v>64.579859732348737</v>
+        <v>64.590236302328762</v>
       </c>
       <c r="D41">
-        <v>61.609651227572165</v>
+        <v>61.536708001736422</v>
       </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.3">
@@ -1011,10 +1011,10 @@
         <v>5</v>
       </c>
       <c r="C42">
-        <v>85.828628393036183</v>
+        <v>85.762418733647678</v>
       </c>
       <c r="D42">
-        <v>81.413188620036493</v>
+        <v>81.257569828792256</v>
       </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.3">
@@ -1025,10 +1025,10 @@
         <v>6</v>
       </c>
       <c r="C43">
-        <v>89.195279047981586</v>
+        <v>89.099354730367693</v>
       </c>
       <c r="D43">
-        <v>85.187133087690512</v>
+        <v>84.968549194598367</v>
       </c>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.3">
@@ -1039,10 +1039,10 @@
         <v>7</v>
       </c>
       <c r="C44">
-        <v>67.335125022949626</v>
+        <v>67.232284447092439</v>
       </c>
       <c r="D44">
-        <v>63.40839146880375</v>
+        <v>63.184661405746958</v>
       </c>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.3">
@@ -1053,10 +1053,10 @@
         <v>8</v>
       </c>
       <c r="C45">
-        <v>54.464186431620753</v>
+        <v>54.394553558506523</v>
       </c>
       <c r="D45">
-        <v>52.789840192965059</v>
+        <v>52.642683081232207</v>
       </c>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.3">
@@ -1067,10 +1067,10 @@
         <v>9</v>
       </c>
       <c r="C46">
-        <v>60.727859792997876</v>
+        <v>60.644905323563457</v>
       </c>
       <c r="D46">
-        <v>61.660764538394368</v>
+        <v>61.488889952438257</v>
       </c>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.3">
@@ -1081,10 +1081,10 @@
         <v>10</v>
       </c>
       <c r="C47">
-        <v>68.818372297765009</v>
+        <v>68.777394662756706</v>
       </c>
       <c r="D47">
-        <v>67.715651680325394</v>
+        <v>67.552424525351981</v>
       </c>
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.3">
@@ -1095,10 +1095,10 @@
         <v>11</v>
       </c>
       <c r="C48">
-        <v>104.55919709819041</v>
+        <v>104.66426511469963</v>
       </c>
       <c r="D48">
-        <v>93.834101541392684</v>
+        <v>93.905352810263892</v>
       </c>
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.3">
@@ -1109,10 +1109,10 @@
         <v>12</v>
       </c>
       <c r="C49">
-        <v>100.80643184348025</v>
+        <v>100.70875911967444</v>
       </c>
       <c r="D49">
-        <v>94.655840948819758</v>
+        <v>94.420084417078641</v>
       </c>
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.3">
@@ -1123,10 +1123,10 @@
         <v>1</v>
       </c>
       <c r="C50">
-        <v>99.216299060737285</v>
+        <v>99.186506650929957</v>
       </c>
       <c r="D50">
-        <v>93.348563200213178</v>
+        <v>93.157645270872408</v>
       </c>
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.3">
@@ -1137,10 +1137,10 @@
         <v>2</v>
       </c>
       <c r="C51">
-        <v>99.95321108586576</v>
+        <v>99.910593950261315</v>
       </c>
       <c r="D51">
-        <v>93.5879803245857</v>
+        <v>93.422706211243352</v>
       </c>
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.3">
@@ -1151,10 +1151,10 @@
         <v>3</v>
       </c>
       <c r="C52">
-        <v>112.15196178453434</v>
+        <v>112.25207210717883</v>
       </c>
       <c r="D52">
-        <v>104.08670423544652</v>
+        <v>103.9950236587611</v>
       </c>
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.3">
@@ -1165,10 +1165,10 @@
         <v>4</v>
       </c>
       <c r="C53">
-        <v>107.02347144131578</v>
+        <v>107.28232107945647</v>
       </c>
       <c r="D53">
-        <v>95.959881268817881</v>
+        <v>96.110790743930608</v>
       </c>
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.3">
@@ -1179,10 +1179,10 @@
         <v>5</v>
       </c>
       <c r="C54">
-        <v>82.950789716204781</v>
+        <v>82.96555886443798</v>
       </c>
       <c r="D54">
-        <v>76.227253937215011</v>
+        <v>76.153901858458227</v>
       </c>
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.3">
@@ -1193,10 +1193,10 @@
         <v>6</v>
       </c>
       <c r="C55">
-        <v>74.085197568082762</v>
+        <v>74.133524437651175</v>
       </c>
       <c r="D55">
-        <v>70.382551445700969</v>
+        <v>70.297222521175527</v>
       </c>
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.3">
@@ -1207,10 +1207,10 @@
         <v>7</v>
       </c>
       <c r="C56">
-        <v>97.386014075993316</v>
+        <v>97.407200966202538</v>
       </c>
       <c r="D56">
-        <v>89.315377227686312</v>
+        <v>89.239644602902189</v>
       </c>
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.3">
@@ -1221,10 +1221,10 @@
         <v>8</v>
       </c>
       <c r="C57">
-        <v>82.594543443486856</v>
+        <v>82.717511999580225</v>
       </c>
       <c r="D57">
-        <v>78.625569002556261</v>
+        <v>78.614857288217507</v>
       </c>
     </row>
     <row r="58" spans="1:4" x14ac:dyDescent="0.3">
@@ -1235,10 +1235,10 @@
         <v>9</v>
       </c>
       <c r="C58">
-        <v>174.97706150021304</v>
+        <v>175.33068016298623</v>
       </c>
       <c r="D58">
-        <v>157.86632351885626</v>
+        <v>158.04783413346399</v>
       </c>
     </row>
     <row r="59" spans="1:4" x14ac:dyDescent="0.3">
@@ -1249,10 +1249,10 @@
         <v>10</v>
       </c>
       <c r="C59">
-        <v>163.6873969752921</v>
+        <v>164.15051766032843</v>
       </c>
       <c r="D59">
-        <v>149.65525801828673</v>
+        <v>149.91126841448838</v>
       </c>
     </row>
     <row r="60" spans="1:4" x14ac:dyDescent="0.3">
@@ -1263,10 +1263,10 @@
         <v>11</v>
       </c>
       <c r="C60">
-        <v>123.74895249709455</v>
+        <v>123.95523138435773</v>
       </c>
       <c r="D60">
-        <v>116.18126533469467</v>
+        <v>116.20001217828741</v>
       </c>
     </row>
     <row r="61" spans="1:4" x14ac:dyDescent="0.3">
@@ -1277,10 +1277,10 @@
         <v>12</v>
       </c>
       <c r="C61">
-        <v>106.24967153560777</v>
+        <v>106.10798671700023</v>
       </c>
       <c r="D61">
-        <v>100.57844336403146</v>
+        <v>100.26182156174477</v>
       </c>
     </row>
     <row r="62" spans="1:4" x14ac:dyDescent="0.3">
@@ -1291,10 +1291,10 @@
         <v>1</v>
       </c>
       <c r="C62">
-        <v>104.10876727013027</v>
+        <v>103.72241664433486</v>
       </c>
       <c r="D62">
-        <v>99.519537095862063</v>
+        <v>98.984058054084102</v>
       </c>
     </row>
     <row r="63" spans="1:4" x14ac:dyDescent="0.3">
@@ -1305,10 +1305,10 @@
         <v>2</v>
       </c>
       <c r="C63">
-        <v>86.314764573232793</v>
+        <v>86.269673047196207</v>
       </c>
       <c r="D63">
-        <v>80.760350683622733</v>
+        <v>80.579714213326042</v>
       </c>
     </row>
     <row r="64" spans="1:4" x14ac:dyDescent="0.3">
@@ -1319,10 +1319,10 @@
         <v>3</v>
       </c>
       <c r="C64">
-        <v>76.823632845254565</v>
+        <v>76.763801466547591</v>
       </c>
       <c r="D64">
-        <v>74.591100086801347</v>
+        <v>74.351857114299975</v>
       </c>
     </row>
     <row r="65" spans="1:4" x14ac:dyDescent="0.3">
@@ -1333,10 +1333,10 @@
         <v>4</v>
       </c>
       <c r="C65">
-        <v>81.825405387532726</v>
+        <v>81.805006355699945</v>
       </c>
       <c r="D65">
-        <v>79.131244989375872</v>
+        <v>78.953321697940069</v>
       </c>
     </row>
     <row r="66" spans="1:4" x14ac:dyDescent="0.3">
@@ -1347,10 +1347,10 @@
         <v>5</v>
       </c>
       <c r="C66">
-        <v>80.083482714086387</v>
+        <v>79.810733864934591</v>
       </c>
       <c r="D66">
-        <v>77.966731288645846</v>
+        <v>77.578393909750758</v>
       </c>
     </row>
     <row r="67" spans="1:4" x14ac:dyDescent="0.3">
@@ -1361,10 +1361,10 @@
         <v>6</v>
       </c>
       <c r="C67">
-        <v>91.957544118240477</v>
+        <v>91.818173150487098</v>
       </c>
       <c r="D67">
-        <v>88.840467065699883</v>
+        <v>88.619706146497961</v>
       </c>
     </row>
     <row r="68" spans="1:4" x14ac:dyDescent="0.3">
@@ -1375,10 +1375,10 @@
         <v>7</v>
       </c>
       <c r="C68">
-        <v>99.851642861998101</v>
+        <v>99.912982620034455</v>
       </c>
       <c r="D68">
-        <v>94.055731628433648</v>
+        <v>93.914924223185864</v>
       </c>
     </row>
     <row r="69" spans="1:4" x14ac:dyDescent="0.3">
@@ -1389,10 +1389,10 @@
         <v>8</v>
       </c>
       <c r="C69">
-        <v>104.36415652958401</v>
+        <v>104.25400295956025</v>
       </c>
       <c r="D69">
-        <v>98.658565473958234</v>
+        <v>98.413319026719719</v>
       </c>
     </row>
     <row r="70" spans="1:4" x14ac:dyDescent="0.3">
@@ -1403,10 +1403,10 @@
         <v>9</v>
       </c>
       <c r="C70">
-        <v>119.30208016201752</v>
+        <v>119.53578555617999</v>
       </c>
       <c r="D70">
-        <v>113.83021082902694</v>
+        <v>113.82648075764507</v>
       </c>
     </row>
     <row r="71" spans="1:4" x14ac:dyDescent="0.3">
@@ -1417,10 +1417,10 @@
         <v>10</v>
       </c>
       <c r="C71">
-        <v>115.09632039492662</v>
+        <v>114.92770325277006</v>
       </c>
       <c r="D71">
-        <v>113.14112637942536</v>
+        <v>112.80397290289957</v>
       </c>
     </row>
     <row r="72" spans="1:4" x14ac:dyDescent="0.3">
@@ -1431,10 +1431,10 @@
         <v>11</v>
       </c>
       <c r="C72">
-        <v>121.2803413704422</v>
+        <v>121.40470623249051</v>
       </c>
       <c r="D72">
-        <v>114.38480041804431</v>
+        <v>114.27612691613383</v>
       </c>
     </row>
     <row r="73" spans="1:4" x14ac:dyDescent="0.3">
@@ -1445,10 +1445,10 @@
         <v>12</v>
       </c>
       <c r="C73">
-        <v>119.61762104177213</v>
+        <v>119.86164868173495</v>
       </c>
       <c r="D73">
-        <v>115.91450090188592</v>
+        <v>115.79431140340903</v>
       </c>
     </row>
     <row r="74" spans="1:4" x14ac:dyDescent="0.3">
@@ -1459,10 +1459,10 @@
         <v>1</v>
       </c>
       <c r="C74">
-        <v>125.72825392086349</v>
+        <v>125.66857028404685</v>
       </c>
       <c r="D74">
-        <v>113.23760649377601</v>
+        <v>113.00595908670235</v>
       </c>
     </row>
     <row r="75" spans="1:4" x14ac:dyDescent="0.3">
@@ -1473,10 +1473,10 @@
         <v>2</v>
       </c>
       <c r="C75">
-        <v>134.78164906361948</v>
+        <v>134.84995327598929</v>
       </c>
       <c r="D75">
-        <v>122.67165175404271</v>
+        <v>122.60543051622091</v>
       </c>
     </row>
     <row r="76" spans="1:4" x14ac:dyDescent="0.3">
@@ -1487,10 +1487,10 @@
         <v>3</v>
       </c>
       <c r="C76">
-        <v>167.64179719519376</v>
+        <v>168.03674846321312</v>
       </c>
       <c r="D76">
-        <v>154.94883124591124</v>
+        <v>154.93760726698741</v>
       </c>
     </row>
     <row r="77" spans="1:4" x14ac:dyDescent="0.3">
@@ -1501,10 +1501,10 @@
         <v>4</v>
       </c>
       <c r="C77">
-        <v>136.17379935542564</v>
+        <v>136.08248207201012</v>
       </c>
       <c r="D77">
-        <v>130.40963813715462</v>
+        <v>129.92848184466357</v>
       </c>
     </row>
     <row r="78" spans="1:4" x14ac:dyDescent="0.3">
@@ -1515,10 +1515,10 @@
         <v>5</v>
       </c>
       <c r="C78">
-        <v>106.35312377094233</v>
+        <v>106.29012576027846</v>
       </c>
       <c r="D78">
-        <v>101.67527236480038</v>
+        <v>101.34842225399132</v>
       </c>
     </row>
     <row r="79" spans="1:4" x14ac:dyDescent="0.3">
@@ -1529,10 +1529,10 @@
         <v>6</v>
       </c>
       <c r="C79">
-        <v>88.874366577549821</v>
+        <v>88.699561876682353</v>
       </c>
       <c r="D79">
-        <v>82.512261577475172</v>
+        <v>82.162754630235767</v>
       </c>
     </row>
     <row r="80" spans="1:4" x14ac:dyDescent="0.3">
@@ -1543,10 +1543,10 @@
         <v>7</v>
       </c>
       <c r="C80">
-        <v>80.6042365435015</v>
+        <v>80.370097727342952</v>
       </c>
       <c r="D80">
-        <v>82.56268589989422</v>
+        <v>82.046655165179146</v>
       </c>
     </row>
     <row r="81" spans="1:4" x14ac:dyDescent="0.3">
@@ -1557,10 +1557,10 @@
         <v>8</v>
       </c>
       <c r="C81">
-        <v>69.264723904202555</v>
+        <v>69.143348515409187</v>
       </c>
       <c r="D81">
-        <v>71.224510445060901</v>
+        <v>70.887878125274071</v>
       </c>
     </row>
     <row r="82" spans="1:4" x14ac:dyDescent="0.3">
@@ -1571,10 +1571,10 @@
         <v>9</v>
       </c>
       <c r="C82">
-        <v>80.180830002876036</v>
+        <v>80.016381331897577</v>
       </c>
       <c r="D82">
-        <v>76.204235513587733</v>
+        <v>75.883664168830677</v>
       </c>
     </row>
     <row r="83" spans="1:4" x14ac:dyDescent="0.3">
@@ -1585,10 +1585,10 @@
         <v>10</v>
       </c>
       <c r="C83">
-        <v>76.342662612994701</v>
+        <v>76.154453451865734</v>
       </c>
       <c r="D83">
-        <v>78.332028901963767</v>
+        <v>77.940702341927178</v>
       </c>
     </row>
     <row r="84" spans="1:4" x14ac:dyDescent="0.3">
@@ -1599,10 +1599,10 @@
         <v>11</v>
       </c>
       <c r="C84">
-        <v>73.756235787073308</v>
+        <v>73.510210200243918</v>
       </c>
       <c r="D84">
-        <v>75.207438526504106</v>
+        <v>74.873459480385009</v>
       </c>
     </row>
     <row r="85" spans="1:4" x14ac:dyDescent="0.3">
@@ -1613,10 +1613,10 @@
         <v>12</v>
       </c>
       <c r="C85">
-        <v>70.246752894268894</v>
+        <v>69.970888638480631</v>
       </c>
       <c r="D85">
-        <v>69.900595219219753</v>
+        <v>69.486897522681247</v>
       </c>
     </row>
     <row r="86" spans="1:4" x14ac:dyDescent="0.3">
@@ -1627,10 +1627,10 @@
         <v>1</v>
       </c>
       <c r="C86">
-        <v>72.306003728001912</v>
+        <v>72.17751999944025</v>
       </c>
       <c r="D86">
-        <v>76.729604645015513</v>
+        <v>76.397167664503598</v>
       </c>
     </row>
     <row r="87" spans="1:4" x14ac:dyDescent="0.3">
@@ -1641,10 +1641,10 @@
         <v>2</v>
       </c>
       <c r="C87">
-        <v>72.52157832623783</v>
+        <v>72.265654751538378</v>
       </c>
       <c r="D87">
-        <v>79.574678355574065</v>
+        <v>79.147474342932682</v>
       </c>
     </row>
     <row r="88" spans="1:4" x14ac:dyDescent="0.3">
@@ -1655,10 +1655,10 @@
         <v>3</v>
       </c>
       <c r="C88">
-        <v>77.923399752810198</v>
+        <v>77.764477668048414</v>
       </c>
       <c r="D88">
-        <v>74.991797178746992</v>
+        <v>74.673338931655962</v>
       </c>
     </row>
     <row r="89" spans="1:4" x14ac:dyDescent="0.3">
@@ -1669,10 +1669,10 @@
         <v>4</v>
       </c>
       <c r="C89">
-        <v>77.694399210345324</v>
+        <v>77.478198235014219</v>
       </c>
       <c r="D89">
-        <v>79.71451570607465</v>
+        <v>79.308576040126326</v>
       </c>
     </row>
     <row r="90" spans="1:4" x14ac:dyDescent="0.3">
@@ -1683,10 +1683,10 @@
         <v>5</v>
       </c>
       <c r="C90">
-        <v>89.312722630667608</v>
+        <v>89.332375006571951</v>
       </c>
       <c r="D90">
-        <v>94.404070347978134</v>
+        <v>94.255204567805507</v>
       </c>
     </row>
     <row r="91" spans="1:4" x14ac:dyDescent="0.3">
@@ -1697,10 +1697,10 @@
         <v>6</v>
       </c>
       <c r="C91">
-        <v>77.400231302055545</v>
+        <v>77.306814525187875</v>
       </c>
       <c r="D91">
-        <v>77.949313547690139</v>
+        <v>77.661897829273443</v>
       </c>
     </row>
     <row r="92" spans="1:4" x14ac:dyDescent="0.3">
@@ -1711,10 +1711,10 @@
         <v>7</v>
       </c>
       <c r="C92">
-        <v>74.67048544760739</v>
+        <v>74.246224487447805</v>
       </c>
       <c r="D92">
-        <v>71.895974191386699</v>
+        <v>71.397867842220379</v>
       </c>
     </row>
     <row r="93" spans="1:4" x14ac:dyDescent="0.3">
@@ -1725,10 +1725,10 @@
         <v>8</v>
       </c>
       <c r="C93">
-        <v>68.73517108160722</v>
+        <v>68.46489394103746</v>
       </c>
       <c r="D93">
-        <v>67.769108892345301</v>
+        <v>67.389902852231472</v>
       </c>
     </row>
     <row r="94" spans="1:4" x14ac:dyDescent="0.3">
@@ -1739,10 +1739,10 @@
         <v>9</v>
       </c>
       <c r="C94">
-        <v>78.016656002505911</v>
+        <v>78.099538767035298</v>
       </c>
       <c r="D94">
-        <v>73.991043208792789</v>
+        <v>73.896548881405565</v>
       </c>
     </row>
     <row r="95" spans="1:4" x14ac:dyDescent="0.3">
@@ -1753,10 +1753,10 @@
         <v>10</v>
       </c>
       <c r="C95">
-        <v>89.01513790143153</v>
+        <v>88.65505671078175</v>
       </c>
       <c r="D95">
-        <v>88.914887543513629</v>
+        <v>88.397257173125951</v>
       </c>
     </row>
     <row r="96" spans="1:4" x14ac:dyDescent="0.3">
@@ -1767,10 +1767,10 @@
         <v>11</v>
       </c>
       <c r="C96">
-        <v>84.084835377592427</v>
+        <v>83.779416446346303</v>
       </c>
       <c r="D96">
-        <v>80.410519724177746</v>
+        <v>79.988303381503513</v>
       </c>
     </row>
     <row r="97" spans="1:4" x14ac:dyDescent="0.3">
@@ -1781,10 +1781,10 @@
         <v>12</v>
       </c>
       <c r="C97">
-        <v>65.529927145519721</v>
+        <v>65.450891746942219</v>
       </c>
       <c r="D97">
-        <v>67.818390775672285</v>
+        <v>67.443932509834866</v>
       </c>
     </row>
     <row r="98" spans="1:4" x14ac:dyDescent="0.3">
@@ -1795,10 +1795,10 @@
         <v>1</v>
       </c>
       <c r="C98">
-        <v>57.928471982838623</v>
+        <v>57.844692989238609</v>
       </c>
       <c r="D98">
-        <v>64.158296141692304</v>
+        <v>63.875961018486983</v>
       </c>
     </row>
     <row r="99" spans="1:4" x14ac:dyDescent="0.3">
@@ -1809,10 +1809,10 @@
         <v>2</v>
       </c>
       <c r="C99">
-        <v>55.187655537309354</v>
+        <v>54.688886386025459</v>
       </c>
       <c r="D99">
-        <v>58.049763571554614</v>
+        <v>57.52738431418949</v>
       </c>
     </row>
     <row r="100" spans="1:4" x14ac:dyDescent="0.3">
@@ -1823,10 +1823,10 @@
         <v>3</v>
       </c>
       <c r="C100">
-        <v>53.226919907999473</v>
+        <v>53.142543223884033</v>
       </c>
       <c r="D100">
-        <v>56.262886237224464</v>
+        <v>56.01542760682149</v>
       </c>
     </row>
     <row r="101" spans="1:4" x14ac:dyDescent="0.3">
@@ -1837,10 +1837,10 @@
         <v>4</v>
       </c>
       <c r="C101">
-        <v>70.842665439278235</v>
+        <v>70.405008195430653</v>
       </c>
       <c r="D101">
-        <v>76.227136955251396</v>
+        <v>75.562484918720116</v>
       </c>
     </row>
     <row r="102" spans="1:4" x14ac:dyDescent="0.3">
@@ -1851,10 +1851,10 @@
         <v>5</v>
       </c>
       <c r="C102">
-        <v>67.560138267198965</v>
+        <v>67.430884367173846</v>
       </c>
       <c r="D102">
-        <v>63.968503658058665</v>
+        <v>63.771070348227894</v>
       </c>
     </row>
     <row r="103" spans="1:4" x14ac:dyDescent="0.3">
@@ -1865,10 +1865,10 @@
         <v>6</v>
       </c>
       <c r="C103">
-        <v>70.884755955470524</v>
+        <v>70.805484571313841</v>
       </c>
       <c r="D103">
-        <v>71.540138273339082</v>
+        <v>71.270166380816718</v>
       </c>
     </row>
     <row r="104" spans="1:4" x14ac:dyDescent="0.3">
@@ -1879,10 +1879,10 @@
         <v>7</v>
       </c>
       <c r="C104">
-        <v>63.156059400822762</v>
+        <v>62.919556791616188</v>
       </c>
       <c r="D104">
-        <v>64.828271432721664</v>
+        <v>64.383069011599858</v>
       </c>
     </row>
     <row r="105" spans="1:4" x14ac:dyDescent="0.3">
@@ -1893,10 +1893,10 @@
         <v>8</v>
       </c>
       <c r="C105">
-        <v>61.602579998646398</v>
+        <v>61.39265753421536</v>
       </c>
       <c r="D105">
-        <v>63.037839434542462</v>
+        <v>62.620649936229746</v>
       </c>
     </row>
     <row r="106" spans="1:4" x14ac:dyDescent="0.3">
@@ -1907,10 +1907,10 @@
         <v>9</v>
       </c>
       <c r="C106">
-        <v>94.119182407570918</v>
+        <v>93.761277848129907</v>
       </c>
       <c r="D106">
-        <v>92.156031063569827</v>
+        <v>91.58950895700282</v>
       </c>
     </row>
     <row r="107" spans="1:4" x14ac:dyDescent="0.3">
@@ -1921,10 +1921,10 @@
         <v>10</v>
       </c>
       <c r="C107">
-        <v>66.097850049160272</v>
+        <v>66.039997109162329</v>
       </c>
       <c r="D107">
-        <v>68.552573636736895</v>
+        <v>68.270839193151701</v>
       </c>
     </row>
     <row r="108" spans="1:4" x14ac:dyDescent="0.3">
@@ -1935,10 +1935,10 @@
         <v>11</v>
       </c>
       <c r="C108">
-        <v>66.613204119469458</v>
+        <v>66.226634644060184</v>
       </c>
       <c r="D108">
-        <v>64.41922156653618</v>
+        <v>63.99226536830357</v>
       </c>
     </row>
     <row r="109" spans="1:4" x14ac:dyDescent="0.3">
@@ -1949,10 +1949,10 @@
         <v>12</v>
       </c>
       <c r="C109">
-        <v>61.915390934351123</v>
+        <v>61.582985010512509</v>
       </c>
       <c r="D109">
-        <v>66.693136483989193</v>
+        <v>66.170832359859872</v>
       </c>
     </row>
     <row r="110" spans="1:4" x14ac:dyDescent="0.3">
@@ -1963,10 +1963,10 @@
         <v>1</v>
       </c>
       <c r="C110">
-        <v>71.034827910902749</v>
+        <v>70.52274860163142</v>
       </c>
       <c r="D110">
-        <v>78.193822760742066</v>
+        <v>77.373296819014129</v>
       </c>
     </row>
     <row r="111" spans="1:4" x14ac:dyDescent="0.3">
@@ -1977,10 +1977,10 @@
         <v>2</v>
       </c>
       <c r="C111">
-        <v>59.399210435757844</v>
+        <v>58.947864929648283</v>
       </c>
       <c r="D111">
-        <v>61.175646762355058</v>
+        <v>60.563846277619859</v>
       </c>
     </row>
     <row r="112" spans="1:4" x14ac:dyDescent="0.3">
@@ -1991,10 +1991,10 @@
         <v>3</v>
       </c>
       <c r="C112">
-        <v>58.545748350794497</v>
+        <v>58.258757759219932</v>
       </c>
       <c r="D112">
-        <v>61.387590105134528</v>
+        <v>60.926033618627088</v>
       </c>
     </row>
     <row r="113" spans="1:4" x14ac:dyDescent="0.3">
@@ -2005,10 +2005,10 @@
         <v>4</v>
       </c>
       <c r="C113">
-        <v>71.832899123677961</v>
+        <v>71.351896101922591</v>
       </c>
       <c r="D113">
-        <v>73.972998077200529</v>
+        <v>73.361786815431955</v>
       </c>
     </row>
     <row r="114" spans="1:4" x14ac:dyDescent="0.3">
@@ -2019,10 +2019,10 @@
         <v>5</v>
       </c>
       <c r="C114">
-        <v>63.009013231846588</v>
+        <v>63.048925396226345</v>
       </c>
       <c r="D114">
-        <v>62.929691555249654</v>
+        <v>62.770324339105493</v>
       </c>
     </row>
     <row r="115" spans="1:4" x14ac:dyDescent="0.3">
@@ -2033,10 +2033,10 @@
         <v>6</v>
       </c>
       <c r="C115">
-        <v>72.469081422108232</v>
+        <v>72.238229471464606</v>
       </c>
       <c r="D115">
-        <v>72.605461192089834</v>
+        <v>72.221394792774817</v>
       </c>
     </row>
     <row r="116" spans="1:4" x14ac:dyDescent="0.3">
@@ -2047,10 +2047,10 @@
         <v>7</v>
       </c>
       <c r="C116">
-        <v>69.501950165844534</v>
+        <v>69.327710577493164</v>
       </c>
       <c r="D116">
-        <v>71.107835154440679</v>
+        <v>70.717790232389234</v>
       </c>
     </row>
     <row r="117" spans="1:4" x14ac:dyDescent="0.3">
@@ -2061,10 +2061,10 @@
         <v>8</v>
       </c>
       <c r="C117">
-        <v>60.581174960935883</v>
+        <v>60.124612703918189</v>
       </c>
       <c r="D117">
-        <v>64.521915290767367</v>
+        <v>63.928500297438831</v>
       </c>
     </row>
     <row r="118" spans="1:4" x14ac:dyDescent="0.3">
@@ -2075,10 +2075,10 @@
         <v>9</v>
       </c>
       <c r="C118">
-        <v>58.343876175420192</v>
+        <v>58.189343527202823</v>
       </c>
       <c r="D118">
-        <v>57.068721001145555</v>
+        <v>56.843834952354683</v>
       </c>
     </row>
     <row r="119" spans="1:4" x14ac:dyDescent="0.3">
@@ -2089,10 +2089,10 @@
         <v>10</v>
       </c>
       <c r="C119">
-        <v>61.310714292824635</v>
+        <v>61.06836574420236</v>
       </c>
       <c r="D119">
-        <v>66.813134666119197</v>
+        <v>66.304641815593371</v>
       </c>
     </row>
     <row r="120" spans="1:4" x14ac:dyDescent="0.3">
@@ -2103,10 +2103,10 @@
         <v>11</v>
       </c>
       <c r="C120">
-        <v>58.800429309634971</v>
+        <v>58.259307250278198</v>
       </c>
       <c r="D120">
-        <v>64.197817726037997</v>
+        <v>63.548116789317056</v>
       </c>
     </row>
     <row r="121" spans="1:4" x14ac:dyDescent="0.3">
@@ -2117,10 +2117,10 @@
         <v>12</v>
       </c>
       <c r="C121">
-        <v>58.004377266198993</v>
+        <v>57.415119226692589</v>
       </c>
       <c r="D121">
-        <v>61.834027131581443</v>
+        <v>61.127270398173074</v>
       </c>
     </row>
     <row r="122" spans="1:4" x14ac:dyDescent="0.3">
@@ -2131,10 +2131,10 @@
         <v>1</v>
       </c>
       <c r="C122">
-        <v>64.411734916868653</v>
+        <v>64.46652923998974</v>
       </c>
       <c r="D122">
-        <v>65.102754764795407</v>
+        <v>64.984751209353249</v>
       </c>
     </row>
     <row r="123" spans="1:4" x14ac:dyDescent="0.3">
@@ -2145,10 +2145,10 @@
         <v>2</v>
       </c>
       <c r="C123">
-        <v>54.670458876511475</v>
+        <v>54.743006166322537</v>
       </c>
       <c r="D123">
-        <v>57.815821932646344</v>
+        <v>57.652385488051998</v>
       </c>
     </row>
     <row r="124" spans="1:4" x14ac:dyDescent="0.3">
@@ -2159,10 +2159,10 @@
         <v>3</v>
       </c>
       <c r="C124">
-        <v>65.01010984404968</v>
+        <v>64.727108079480985</v>
       </c>
       <c r="D124">
-        <v>67.46203687893771</v>
+        <v>66.963832363970951</v>
       </c>
     </row>
     <row r="125" spans="1:4" x14ac:dyDescent="0.3">
@@ -2173,10 +2173,10 @@
         <v>4</v>
       </c>
       <c r="C125">
-        <v>60.49784118077531</v>
+        <v>60.557197569193278</v>
       </c>
       <c r="D125">
-        <v>64.475155351281458</v>
+        <v>64.296420623783504</v>
       </c>
     </row>
     <row r="126" spans="1:4" x14ac:dyDescent="0.3">
@@ -2187,10 +2187,10 @@
         <v>5</v>
       </c>
       <c r="C126">
-        <v>57.167739618079054</v>
+        <v>57.153401744199002</v>
       </c>
       <c r="D126">
-        <v>57.167881809554288</v>
+        <v>56.963498151870859</v>
       </c>
     </row>
     <row r="127" spans="1:4" x14ac:dyDescent="0.3">
@@ -2201,10 +2201,10 @@
         <v>6</v>
       </c>
       <c r="C127">
-        <v>56.791507307845656</v>
+        <v>56.368568178793666</v>
       </c>
       <c r="D127">
-        <v>57.422152938489603</v>
+        <v>56.918112780467574</v>
       </c>
     </row>
     <row r="128" spans="1:4" x14ac:dyDescent="0.3">
@@ -2215,10 +2215,10 @@
         <v>7</v>
       </c>
       <c r="C128">
-        <v>47.856428285814843</v>
+        <v>47.588486288361146</v>
       </c>
       <c r="D128">
-        <v>52.307810272909428</v>
+        <v>51.826653905143779</v>
       </c>
     </row>
     <row r="129" spans="1:4" x14ac:dyDescent="0.3">
@@ -2229,10 +2229,10 @@
         <v>8</v>
       </c>
       <c r="C129">
-        <v>78.435149664217477</v>
+        <v>78.347843116697589</v>
       </c>
       <c r="D129">
-        <v>76.530487118929642</v>
+        <v>76.210386725037694</v>
       </c>
     </row>
     <row r="130" spans="1:4" x14ac:dyDescent="0.3">
@@ -2243,10 +2243,10 @@
         <v>9</v>
       </c>
       <c r="C130">
-        <v>100.1027954086818</v>
+        <v>99.766425255833497</v>
       </c>
       <c r="D130">
-        <v>94.276442963390735</v>
+        <v>93.750604098490982</v>
       </c>
     </row>
     <row r="131" spans="1:4" x14ac:dyDescent="0.3">
@@ -2257,10 +2257,10 @@
         <v>10</v>
       </c>
       <c r="C131">
-        <v>79.819488322885633</v>
+        <v>79.311864359228309</v>
       </c>
       <c r="D131">
-        <v>79.054579642079915</v>
+        <v>78.440355729092119</v>
       </c>
     </row>
     <row r="132" spans="1:4" x14ac:dyDescent="0.3">
@@ -2271,10 +2271,10 @@
         <v>11</v>
       </c>
       <c r="C132">
-        <v>83.512107860190241</v>
+        <v>82.915552203291099</v>
       </c>
       <c r="D132">
-        <v>79.240565703151674</v>
+        <v>78.614008502794661</v>
       </c>
     </row>
     <row r="133" spans="1:4" x14ac:dyDescent="0.3">
@@ -2285,10 +2285,10 @@
         <v>12</v>
       </c>
       <c r="C133">
-        <v>97.070141851370479</v>
+        <v>96.765607743454154</v>
       </c>
       <c r="D133">
-        <v>99.497646246992133</v>
+        <v>98.860143039392923</v>
       </c>
     </row>
     <row r="134" spans="1:4" x14ac:dyDescent="0.3">
@@ -2299,10 +2299,10 @@
         <v>1</v>
       </c>
       <c r="C134">
-        <v>134.77515414054008</v>
+        <v>134.64482218286452</v>
       </c>
       <c r="D134">
-        <v>132.66898606166689</v>
+        <v>132.14548510453147</v>
       </c>
     </row>
     <row r="135" spans="1:4" x14ac:dyDescent="0.3">
@@ -2313,10 +2313,10 @@
         <v>2</v>
       </c>
       <c r="C135">
-        <v>99.338493453900668</v>
+        <v>99.414594080004505</v>
       </c>
       <c r="D135">
-        <v>97.691320536507092</v>
+        <v>97.44637425242199</v>
       </c>
     </row>
     <row r="136" spans="1:4" x14ac:dyDescent="0.3">
@@ -2327,10 +2327,10 @@
         <v>3</v>
       </c>
       <c r="C136">
-        <v>120.27834070222642</v>
+        <v>119.60275977856372</v>
       </c>
       <c r="D136">
-        <v>129.4850567162087</v>
+        <v>128.32890809503039</v>
       </c>
     </row>
     <row r="137" spans="1:4" x14ac:dyDescent="0.3">
@@ -2341,10 +2341,10 @@
         <v>4</v>
       </c>
       <c r="C137">
-        <v>92.250734739189483</v>
+        <v>91.66161896115814</v>
       </c>
       <c r="D137">
-        <v>98.841048787499489</v>
+        <v>97.977941167477866</v>
       </c>
     </row>
     <row r="138" spans="1:4" x14ac:dyDescent="0.3">
@@ -2355,10 +2355,10 @@
         <v>5</v>
       </c>
       <c r="C138">
-        <v>78.577100598634146</v>
+        <v>78.034049710214475</v>
       </c>
       <c r="D138">
-        <v>81.647949053082414</v>
+        <v>80.942988136164715</v>
       </c>
     </row>
     <row r="139" spans="1:4" x14ac:dyDescent="0.3">
@@ -2369,10 +2369,10 @@
         <v>6</v>
       </c>
       <c r="C139">
-        <v>86.389794661552557</v>
+        <v>87.020717348324823</v>
       </c>
       <c r="D139">
-        <v>90.882326039109643</v>
+        <v>90.939751321245424</v>
       </c>
     </row>
     <row r="140" spans="1:4" x14ac:dyDescent="0.3">
@@ -2383,10 +2383,10 @@
         <v>7</v>
       </c>
       <c r="C140">
-        <v>96.848888398427235</v>
+        <v>96.362753792134015</v>
       </c>
       <c r="D140">
-        <v>108.03765492218241</v>
+        <v>107.05381560669827</v>
       </c>
     </row>
     <row r="141" spans="1:4" x14ac:dyDescent="0.3">
@@ -2397,10 +2397,10 @@
         <v>8</v>
       </c>
       <c r="C141">
-        <v>90.502000110391975</v>
+        <v>90.248500652133202</v>
       </c>
       <c r="D141">
-        <v>98.950066651527948</v>
+        <v>98.099567210481624</v>
       </c>
     </row>
     <row r="142" spans="1:4" x14ac:dyDescent="0.3">
@@ -2411,10 +2411,10 @@
         <v>9</v>
       </c>
       <c r="C142">
-        <v>162.48119206840639</v>
+        <v>162.48055542344935</v>
       </c>
       <c r="D142">
-        <v>159.37768378815611</v>
+        <v>158.81780411265737</v>
       </c>
     </row>
     <row r="143" spans="1:4" x14ac:dyDescent="0.3">
@@ -2425,10 +2425,10 @@
         <v>10</v>
       </c>
       <c r="C143">
-        <v>208.41027406746682</v>
+        <v>208.55935525706138</v>
       </c>
       <c r="D143">
-        <v>209.10172236225122</v>
+        <v>208.38503760185466</v>
       </c>
     </row>
     <row r="144" spans="1:4" x14ac:dyDescent="0.3">
@@ -2439,10 +2439,10 @@
         <v>11</v>
       </c>
       <c r="C144">
-        <v>143.96182891276595</v>
+        <v>143.53505579370659</v>
       </c>
       <c r="D144">
-        <v>146.34789749835605</v>
+        <v>145.40116805809475</v>
       </c>
     </row>
     <row r="145" spans="1:4" x14ac:dyDescent="0.3">
@@ -2453,10 +2453,10 @@
         <v>12</v>
       </c>
       <c r="C145">
-        <v>144.72867735615071</v>
+        <v>144.60486321999096</v>
       </c>
       <c r="D145">
-        <v>148.57080577500147</v>
+        <v>147.81937534217158</v>
       </c>
     </row>
     <row r="146" spans="1:4" x14ac:dyDescent="0.3">
@@ -2467,10 +2467,10 @@
         <v>1</v>
       </c>
       <c r="C146">
-        <v>146.11124849470096</v>
+        <v>145.30676023297832</v>
       </c>
       <c r="D146">
-        <v>146.4392207254933</v>
+        <v>145.15955717590919</v>
       </c>
     </row>
     <row r="147" spans="1:4" x14ac:dyDescent="0.3">
@@ -2481,10 +2481,10 @@
         <v>2</v>
       </c>
       <c r="C147">
-        <v>147.70314387306672</v>
+        <v>147.44491738946704</v>
       </c>
       <c r="D147">
-        <v>144.31469084392114</v>
+        <v>143.57280999966935</v>
       </c>
     </row>
     <row r="148" spans="1:4" x14ac:dyDescent="0.3">
@@ -2495,10 +2495,10 @@
         <v>3</v>
       </c>
       <c r="C148">
-        <v>132.58174913289</v>
+        <v>132.28776741479626</v>
       </c>
       <c r="D148">
-        <v>136.37799488741189</v>
+        <v>135.53929158744319</v>
       </c>
     </row>
     <row r="149" spans="1:4" x14ac:dyDescent="0.3">
@@ -2509,10 +2509,10 @@
         <v>4</v>
       </c>
       <c r="C149">
-        <v>102.62313480280388</v>
+        <v>102.29239178025952</v>
       </c>
       <c r="D149">
-        <v>104.745746029674</v>
+        <v>104.07567247518271</v>
       </c>
     </row>
     <row r="150" spans="1:4" x14ac:dyDescent="0.3">
@@ -2523,10 +2523,10 @@
         <v>5</v>
       </c>
       <c r="C150">
-        <v>103.7335007984622</v>
+        <v>103.91299609212474</v>
       </c>
       <c r="D150">
-        <v>100.52189852815273</v>
+        <v>100.32550474457216</v>
       </c>
     </row>
     <row r="151" spans="1:4" x14ac:dyDescent="0.3">
@@ -2537,10 +2537,10 @@
         <v>6</v>
       </c>
       <c r="C151">
-        <v>117.71767536856736</v>
+        <v>116.62711109185173</v>
       </c>
       <c r="D151">
-        <v>130.58030763815603</v>
+        <v>128.8551785432665</v>
       </c>
     </row>
     <row r="152" spans="1:4" x14ac:dyDescent="0.3">
@@ -2551,10 +2551,10 @@
         <v>7</v>
       </c>
       <c r="C152">
-        <v>106.89572722047274</v>
+        <v>106.25893991265355</v>
       </c>
       <c r="D152">
-        <v>117.79920388662993</v>
+        <v>116.62725595658566</v>
       </c>
     </row>
     <row r="153" spans="1:4" x14ac:dyDescent="0.3">
@@ -2565,10 +2565,10 @@
         <v>8</v>
       </c>
       <c r="C153">
-        <v>103.4630222944608</v>
+        <v>103.04966252756878</v>
       </c>
       <c r="D153">
-        <v>109.27559248451905</v>
+        <v>108.32437921500832</v>
       </c>
     </row>
     <row r="154" spans="1:4" x14ac:dyDescent="0.3">
@@ -2579,10 +2579,10 @@
         <v>9</v>
       </c>
       <c r="C154">
-        <v>106.7308047259959</v>
+        <v>105.98612316655009</v>
       </c>
       <c r="D154">
-        <v>119.5786353129479</v>
+        <v>118.02732200413207</v>
       </c>
     </row>
     <row r="155" spans="1:4" x14ac:dyDescent="0.3">
@@ -2593,10 +2593,10 @@
         <v>10</v>
       </c>
       <c r="C155">
-        <v>92.278554370963391</v>
+        <v>92.067707508628445</v>
       </c>
       <c r="D155">
-        <v>98.052842841680786</v>
+        <v>97.241058503556459</v>
       </c>
     </row>
     <row r="156" spans="1:4" x14ac:dyDescent="0.3">
@@ -2607,10 +2607,10 @@
         <v>11</v>
       </c>
       <c r="C156">
-        <v>105.84607192905921</v>
+        <v>104.98010791148249</v>
       </c>
       <c r="D156">
-        <v>109.34600522650734</v>
+        <v>108.08536829745618</v>
       </c>
     </row>
     <row r="157" spans="1:4" x14ac:dyDescent="0.3">
@@ -2621,10 +2621,10 @@
         <v>12</v>
       </c>
       <c r="C157">
-        <v>102.98740772532891</v>
+        <v>102.37380537219239</v>
       </c>
       <c r="D157">
-        <v>105.68220373236775</v>
+        <v>104.69834373789205</v>
       </c>
     </row>
     <row r="158" spans="1:4" x14ac:dyDescent="0.3">
@@ -2635,10 +2635,10 @@
         <v>1</v>
       </c>
       <c r="C158">
-        <v>118.30959251807451</v>
+        <v>117.67233394351534</v>
       </c>
       <c r="D158">
-        <v>120.6541925646326</v>
+        <v>119.55521675950101</v>
       </c>
     </row>
     <row r="159" spans="1:4" x14ac:dyDescent="0.3">
@@ -2649,10 +2649,10 @@
         <v>2</v>
       </c>
       <c r="C159">
-        <v>115.05661675702144</v>
+        <v>114.12997789513584</v>
       </c>
       <c r="D159">
-        <v>120.4738756830882</v>
+        <v>119.22801364179459</v>
       </c>
     </row>
     <row r="160" spans="1:4" x14ac:dyDescent="0.3">
@@ -2663,10 +2663,10 @@
         <v>3</v>
       </c>
       <c r="C160">
-        <v>115.25458490062186</v>
+        <v>114.16618394477351</v>
       </c>
       <c r="D160">
-        <v>121.44864991675993</v>
+        <v>119.88387068597675</v>
       </c>
     </row>
     <row r="161" spans="1:4" x14ac:dyDescent="0.3">
@@ -2677,10 +2677,10 @@
         <v>4</v>
       </c>
       <c r="C161">
-        <v>109.54859358290922</v>
+        <v>108.80332595303653</v>
       </c>
       <c r="D161">
-        <v>109.2899844711115</v>
+        <v>108.2369043268468</v>
       </c>
     </row>
     <row r="162" spans="1:4" x14ac:dyDescent="0.3">
@@ -2691,10 +2691,10 @@
         <v>5</v>
       </c>
       <c r="C162">
-        <v>147.84150852003191</v>
+        <v>147.35271747551585</v>
       </c>
       <c r="D162">
-        <v>143.24957781356943</v>
+        <v>142.32532283577024</v>
       </c>
     </row>
     <row r="163" spans="1:4" x14ac:dyDescent="0.3">
@@ -2705,10 +2705,10 @@
         <v>6</v>
       </c>
       <c r="C163">
-        <v>138.93798811972377</v>
+        <v>138.05363589359015</v>
       </c>
       <c r="D163">
-        <v>142.0473363347887</v>
+        <v>140.66300375034325</v>
       </c>
     </row>
     <row r="164" spans="1:4" x14ac:dyDescent="0.3">
@@ -2719,10 +2719,10 @@
         <v>7</v>
       </c>
       <c r="C164">
-        <v>149.21505375128004</v>
+        <v>148.44795299764223</v>
       </c>
       <c r="D164">
-        <v>146.88945589613454</v>
+        <v>145.65005350677586</v>
       </c>
     </row>
     <row r="165" spans="1:4" x14ac:dyDescent="0.3">
@@ -2733,10 +2733,10 @@
         <v>8</v>
       </c>
       <c r="C165">
-        <v>123.82712516722994</v>
+        <v>123.34952702944828</v>
       </c>
       <c r="D165">
-        <v>121.89059236448537</v>
+        <v>121.03626699808483</v>
       </c>
     </row>
     <row r="166" spans="1:4" x14ac:dyDescent="0.3">
@@ -2747,10 +2747,10 @@
         <v>9</v>
       </c>
       <c r="C166">
-        <v>133.31452141086339</v>
+        <v>133.2687605714103</v>
       </c>
       <c r="D166">
-        <v>127.39682959466751</v>
+        <v>126.93253026563934</v>
       </c>
     </row>
     <row r="167" spans="1:4" x14ac:dyDescent="0.3">
@@ -2761,10 +2761,10 @@
         <v>10</v>
       </c>
       <c r="C167">
-        <v>127.35779814017353</v>
+        <v>126.83336865932203</v>
       </c>
       <c r="D167">
-        <v>123.38713121942504</v>
+        <v>122.48358527690344</v>
       </c>
     </row>
     <row r="168" spans="1:4" x14ac:dyDescent="0.3">
@@ -2775,10 +2775,10 @@
         <v>11</v>
       </c>
       <c r="C168">
-        <v>131.22173687914412</v>
+        <v>131.48753550780665</v>
       </c>
       <c r="D168">
-        <v>127.68749403835716</v>
+        <v>127.39674124445305</v>
       </c>
     </row>
     <row r="169" spans="1:4" x14ac:dyDescent="0.3">
@@ -2789,10 +2789,10 @@
         <v>12</v>
       </c>
       <c r="C169">
-        <v>135.41963436562136</v>
+        <v>134.76192624958907</v>
       </c>
       <c r="D169">
-        <v>139.85416432526088</v>
+        <v>138.70534201306188</v>
       </c>
     </row>
     <row r="170" spans="1:4" x14ac:dyDescent="0.3">
@@ -2803,10 +2803,10 @@
         <v>1</v>
       </c>
       <c r="C170">
-        <v>115.38021090456377</v>
+        <v>114.31861704313937</v>
       </c>
       <c r="D170">
-        <v>124.42186230123907</v>
+        <v>122.82209145509555</v>
       </c>
     </row>
     <row r="171" spans="1:4" x14ac:dyDescent="0.3">
@@ -2817,10 +2817,10 @@
         <v>2</v>
       </c>
       <c r="C171">
-        <v>96.909062688281139</v>
+        <v>96.579076863296649</v>
       </c>
       <c r="D171">
-        <v>97.593801926649249</v>
+        <v>97.039942033494455</v>
       </c>
     </row>
     <row r="172" spans="1:4" x14ac:dyDescent="0.3">
@@ -2831,10 +2831,10 @@
         <v>3</v>
       </c>
       <c r="C172">
-        <v>131.24021257844836</v>
+        <v>130.36071276295712</v>
       </c>
       <c r="D172">
-        <v>132.04265241427061</v>
+        <v>130.75748189533013</v>
       </c>
     </row>
     <row r="173" spans="1:4" x14ac:dyDescent="0.3">
@@ -2845,10 +2845,10 @@
         <v>4</v>
       </c>
       <c r="C173">
-        <v>119.99429139631967</v>
+        <v>118.82751569774082</v>
       </c>
       <c r="D173">
-        <v>124.28837725370009</v>
+        <v>122.71455457999423</v>
       </c>
     </row>
     <row r="174" spans="1:4" x14ac:dyDescent="0.3">
@@ -2859,10 +2859,10 @@
         <v>5</v>
       </c>
       <c r="C174">
-        <v>94.753682188479971</v>
+        <v>93.959265479274436</v>
       </c>
       <c r="D174">
-        <v>94.709584346828038</v>
+        <v>93.73179639503762</v>
       </c>
     </row>
     <row r="175" spans="1:4" x14ac:dyDescent="0.3">
@@ -2873,10 +2873,10 @@
         <v>6</v>
       </c>
       <c r="C175">
-        <v>125.01542788786777</v>
+        <v>124.52442225987642</v>
       </c>
       <c r="D175">
-        <v>124.30942851034966</v>
+        <v>123.40750193952779</v>
       </c>
     </row>
     <row r="176" spans="1:4" x14ac:dyDescent="0.3">
@@ -2887,10 +2887,10 @@
         <v>7</v>
       </c>
       <c r="C176">
-        <v>154.14254867495367</v>
+        <v>153.82885984326128</v>
       </c>
       <c r="D176">
-        <v>151.24522723383021</v>
+        <v>150.48970853348305</v>
       </c>
     </row>
     <row r="177" spans="1:4" x14ac:dyDescent="0.3">
@@ -2901,10 +2901,10 @@
         <v>8</v>
       </c>
       <c r="C177">
-        <v>217.55313259953877</v>
+        <v>216.75711838429405</v>
       </c>
       <c r="D177">
-        <v>215.6544495486055</v>
+        <v>214.32923266780404</v>
       </c>
     </row>
     <row r="178" spans="1:4" x14ac:dyDescent="0.3">
@@ -2915,10 +2915,10 @@
         <v>9</v>
       </c>
       <c r="C178">
-        <v>194.95863798422059</v>
+        <v>194.41022780761008</v>
       </c>
       <c r="D178">
-        <v>194.65878153918371</v>
+        <v>193.50561378918334</v>
       </c>
     </row>
     <row r="179" spans="1:4" x14ac:dyDescent="0.3">
@@ -2929,10 +2929,10 @@
         <v>10</v>
       </c>
       <c r="C179">
-        <v>167.5341554010823</v>
+        <v>166.33759690386063</v>
       </c>
       <c r="D179">
-        <v>173.32363643136401</v>
+        <v>171.60965888880105</v>
       </c>
     </row>
     <row r="180" spans="1:4" x14ac:dyDescent="0.3">
@@ -2943,10 +2943,10 @@
         <v>11</v>
       </c>
       <c r="C180">
-        <v>192.25005987697205</v>
+        <v>191.77611142045239</v>
       </c>
       <c r="D180">
-        <v>195.31919839452877</v>
+        <v>194.12008869598847</v>
       </c>
     </row>
     <row r="181" spans="1:4" x14ac:dyDescent="0.3">
@@ -2957,10 +2957,10 @@
         <v>12</v>
       </c>
       <c r="C181">
-        <v>178.97791106415752</v>
+        <v>178.07909760261643</v>
       </c>
       <c r="D181">
-        <v>186.36615866290614</v>
+        <v>184.86332236770855</v>
       </c>
     </row>
     <row r="182" spans="1:4" x14ac:dyDescent="0.3">
@@ -2971,10 +2971,10 @@
         <v>1</v>
       </c>
       <c r="C182">
-        <v>155.22841912913435</v>
+        <v>154.60602395879906</v>
       </c>
       <c r="D182">
-        <v>158.48274509811742</v>
+        <v>157.41036451550957</v>
       </c>
     </row>
     <row r="183" spans="1:4" x14ac:dyDescent="0.3">
@@ -2985,10 +2985,10 @@
         <v>2</v>
       </c>
       <c r="C183">
-        <v>142.05671042941958</v>
+        <v>141.12412244454075</v>
       </c>
       <c r="D183">
-        <v>148.33616981716602</v>
+        <v>146.9292622417652</v>
       </c>
     </row>
     <row r="184" spans="1:4" x14ac:dyDescent="0.3">
@@ -2999,10 +2999,10 @@
         <v>3</v>
       </c>
       <c r="C184">
-        <v>133.42707057269976</v>
+        <v>132.41014631139356</v>
       </c>
       <c r="D184">
-        <v>146.86629413299869</v>
+        <v>145.40453329613123</v>
       </c>
     </row>
     <row r="185" spans="1:4" x14ac:dyDescent="0.3">
@@ -3013,10 +3013,10 @@
         <v>4</v>
       </c>
       <c r="C185">
-        <v>130.88523693433663</v>
+        <v>129.83842375850958</v>
       </c>
       <c r="D185">
-        <v>136.50267736600006</v>
+        <v>135.06799687824955</v>
       </c>
     </row>
     <row r="186" spans="1:4" x14ac:dyDescent="0.3">
@@ -3027,10 +3027,10 @@
         <v>5</v>
       </c>
       <c r="C186">
-        <v>160.47509910769094</v>
+        <v>159.69718380001015</v>
       </c>
       <c r="D186">
-        <v>165.57251078982361</v>
+        <v>164.31634818928904</v>
       </c>
     </row>
     <row r="187" spans="1:4" x14ac:dyDescent="0.3">
@@ -3041,10 +3041,10 @@
         <v>6</v>
       </c>
       <c r="C187">
-        <v>184.00226936645751</v>
+        <v>183.18487261203407</v>
       </c>
       <c r="D187">
-        <v>188.31049549704892</v>
+        <v>186.99475499314059</v>
       </c>
     </row>
     <row r="188" spans="1:4" x14ac:dyDescent="0.3">
@@ -3055,10 +3055,10 @@
         <v>7</v>
       </c>
       <c r="C188">
-        <v>153.30700667004788</v>
+        <v>152.08521244525861</v>
       </c>
       <c r="D188">
-        <v>152.99256430944016</v>
+        <v>151.44882456052207</v>
       </c>
     </row>
     <row r="189" spans="1:4" x14ac:dyDescent="0.3">
@@ -3069,10 +3069,10 @@
         <v>8</v>
       </c>
       <c r="C189">
-        <v>117.36385982738729</v>
+        <v>116.96839694186473</v>
       </c>
       <c r="D189">
-        <v>118.63401845140011</v>
+        <v>117.94182245880837</v>
       </c>
     </row>
     <row r="190" spans="1:4" x14ac:dyDescent="0.3">
@@ -3083,10 +3083,10 @@
         <v>9</v>
       </c>
       <c r="C190">
-        <v>154.41709628193945</v>
+        <v>153.5869384600671</v>
       </c>
       <c r="D190">
-        <v>156.10490579691134</v>
+        <v>154.86900426346949</v>
       </c>
     </row>
     <row r="191" spans="1:4" x14ac:dyDescent="0.3">
@@ -3097,10 +3097,10 @@
         <v>10</v>
       </c>
       <c r="C191">
-        <v>151.89991378511874</v>
+        <v>151.12166580863942</v>
       </c>
       <c r="D191">
-        <v>151.65634429573933</v>
+        <v>150.49687911210751</v>
       </c>
     </row>
     <row r="192" spans="1:4" x14ac:dyDescent="0.3">
@@ -3111,10 +3111,10 @@
         <v>11</v>
       </c>
       <c r="C192">
-        <v>166.73184187001465</v>
+        <v>165.75635341180524</v>
       </c>
       <c r="D192">
-        <v>161.03700011000601</v>
+        <v>159.67779711634202</v>
       </c>
     </row>
     <row r="193" spans="1:4" x14ac:dyDescent="0.3">
@@ -3125,10 +3125,10 @@
         <v>12</v>
       </c>
       <c r="C193">
-        <v>171.16874994689618</v>
+        <v>170.16380835460885</v>
       </c>
       <c r="D193">
-        <v>170.04450512292792</v>
+        <v>168.56653532364655</v>
       </c>
     </row>
     <row r="194" spans="1:4" x14ac:dyDescent="0.3">
@@ -3139,10 +3139,10 @@
         <v>1</v>
       </c>
       <c r="C194">
-        <v>168.2642680709402</v>
+        <v>167.12465300401243</v>
       </c>
       <c r="D194">
-        <v>165.96021311857433</v>
+        <v>164.48001517058722</v>
       </c>
     </row>
     <row r="195" spans="1:4" x14ac:dyDescent="0.3">
@@ -3153,10 +3153,10 @@
         <v>2</v>
       </c>
       <c r="C195">
-        <v>123.77125161209148</v>
+        <v>122.75716917827998</v>
       </c>
       <c r="D195">
-        <v>123.41635968507401</v>
+        <v>122.25008606337573</v>
       </c>
     </row>
     <row r="196" spans="1:4" x14ac:dyDescent="0.3">
@@ -3167,10 +3167,10 @@
         <v>3</v>
       </c>
       <c r="C196">
-        <v>146.22625713675311</v>
+        <v>145.56859862171578</v>
       </c>
       <c r="D196">
-        <v>145.26603936169289</v>
+        <v>144.33817859085846</v>
       </c>
     </row>
     <row r="197" spans="1:4" x14ac:dyDescent="0.3">
@@ -3181,10 +3181,10 @@
         <v>4</v>
       </c>
       <c r="C197">
-        <v>137.09818401956534</v>
+        <v>136.20573390160476</v>
       </c>
       <c r="D197">
-        <v>139.81218788794314</v>
+        <v>138.56817522432905</v>
       </c>
     </row>
     <row r="198" spans="1:4" x14ac:dyDescent="0.3">
@@ -3195,10 +3195,10 @@
         <v>5</v>
       </c>
       <c r="C198">
-        <v>108.73915324764916</v>
+        <v>107.75691938636902</v>
       </c>
       <c r="D198">
-        <v>108.45492731936986</v>
+        <v>107.37360099719862</v>
       </c>
     </row>
     <row r="199" spans="1:4" x14ac:dyDescent="0.3">
@@ -3209,10 +3209,10 @@
         <v>6</v>
       </c>
       <c r="C199">
-        <v>128.71741720497738</v>
+        <v>127.51606137664947</v>
       </c>
       <c r="D199">
-        <v>130.33402461196374</v>
+        <v>128.93859711665405</v>
       </c>
     </row>
     <row r="200" spans="1:4" x14ac:dyDescent="0.3">
@@ -3223,10 +3223,10 @@
         <v>7</v>
       </c>
       <c r="C200">
-        <v>109.00851561060909</v>
+        <v>107.95890058768815</v>
       </c>
       <c r="D200">
-        <v>108.61165664602973</v>
+        <v>107.45704648926161</v>
       </c>
     </row>
     <row r="201" spans="1:4" x14ac:dyDescent="0.3">
@@ -3237,10 +3237,10 @@
         <v>8</v>
       </c>
       <c r="C201">
-        <v>120.3839834935542</v>
+        <v>119.31401795530486</v>
       </c>
       <c r="D201">
-        <v>127.50349774990674</v>
+        <v>126.21558707279809</v>
       </c>
     </row>
     <row r="202" spans="1:4" x14ac:dyDescent="0.3">
@@ -3251,10 +3251,10 @@
         <v>9</v>
       </c>
       <c r="C202">
-        <v>139.62927512477324</v>
+        <v>138.62338970215609</v>
       </c>
       <c r="D202">
-        <v>141.47516874973721</v>
+        <v>140.23538522349253</v>
       </c>
     </row>
     <row r="203" spans="1:4" x14ac:dyDescent="0.3">
@@ -3265,10 +3265,10 @@
         <v>10</v>
       </c>
       <c r="C203">
-        <v>169.91904988025723</v>
+        <v>168.48061820680076</v>
       </c>
       <c r="D203">
-        <v>167.4150691586816</v>
+        <v>165.60012509333902</v>
       </c>
     </row>
     <row r="204" spans="1:4" x14ac:dyDescent="0.3">
@@ -3279,10 +3279,10 @@
         <v>11</v>
       </c>
       <c r="C204">
-        <v>104.8970581901048</v>
+        <v>103.83916646198959</v>
       </c>
       <c r="D204">
-        <v>108.11831756365788</v>
+        <v>106.74541520446978</v>
       </c>
     </row>
     <row r="205" spans="1:4" x14ac:dyDescent="0.3">
@@ -3293,10 +3293,10 @@
         <v>12</v>
       </c>
       <c r="C205">
-        <v>124.19044442491482</v>
+        <v>122.64177002804905</v>
       </c>
       <c r="D205">
-        <v>128.27598777106547</v>
+        <v>126.51660223516559</v>
       </c>
     </row>
     <row r="206" spans="1:4" x14ac:dyDescent="0.3">
@@ -3307,10 +3307,10 @@
         <v>1</v>
       </c>
       <c r="C206">
-        <v>116.16349921565681</v>
+        <v>115.25755875656071</v>
       </c>
       <c r="D206">
-        <v>119.72452692335156</v>
+        <v>118.56467656247958</v>
       </c>
     </row>
     <row r="207" spans="1:4" x14ac:dyDescent="0.3">
@@ -3321,10 +3321,10 @@
         <v>2</v>
       </c>
       <c r="C207">
-        <v>102.01047179707916</v>
+        <v>101.14727336265942</v>
       </c>
       <c r="D207">
-        <v>100.92578811408968</v>
+        <v>99.953353407067624</v>
       </c>
     </row>
     <row r="208" spans="1:4" x14ac:dyDescent="0.3">
@@ -3335,10 +3335,10 @@
         <v>3</v>
       </c>
       <c r="C208">
-        <v>115.83525645999038</v>
+        <v>114.65237885062528</v>
       </c>
       <c r="D208">
-        <v>114.62274172358721</v>
+        <v>113.27478695135211</v>
       </c>
     </row>
     <row r="209" spans="1:4" x14ac:dyDescent="0.3">
@@ -3349,10 +3349,10 @@
         <v>4</v>
       </c>
       <c r="C209">
-        <v>111.64955038345877</v>
+        <v>110.45015023216153</v>
       </c>
       <c r="D209">
-        <v>118.48565023588043</v>
+        <v>116.98574032886097</v>
       </c>
     </row>
     <row r="210" spans="1:4" x14ac:dyDescent="0.3">
@@ -3363,10 +3363,10 @@
         <v>5</v>
       </c>
       <c r="C210">
-        <v>107.72594660429303</v>
+        <v>106.83907357078779</v>
       </c>
       <c r="D210">
-        <v>111.04334557561116</v>
+        <v>110.02100710684959</v>
       </c>
     </row>
     <row r="211" spans="1:4" x14ac:dyDescent="0.3">
@@ -3377,10 +3377,10 @@
         <v>6</v>
       </c>
       <c r="C211">
-        <v>92.168190554978636</v>
+        <v>91.148211408258604</v>
       </c>
       <c r="D211">
-        <v>96.48710743626016</v>
+        <v>95.232221354936669</v>
       </c>
     </row>
     <row r="212" spans="1:4" x14ac:dyDescent="0.3">
@@ -3391,10 +3391,10 @@
         <v>7</v>
       </c>
       <c r="C212">
-        <v>95.313666940691959</v>
+        <v>94.179985645290941</v>
       </c>
       <c r="D212">
-        <v>99.919899502723268</v>
+        <v>98.633762845583689</v>
       </c>
     </row>
     <row r="213" spans="1:4" x14ac:dyDescent="0.3">
@@ -3405,10 +3405,10 @@
         <v>8</v>
       </c>
       <c r="C213">
-        <v>97.744735801139569</v>
+        <v>96.850719703444369</v>
       </c>
       <c r="D213">
-        <v>105.12123500964519</v>
+        <v>104.0928313313606</v>
       </c>
     </row>
     <row r="214" spans="1:4" x14ac:dyDescent="0.3">
@@ -3419,10 +3419,10 @@
         <v>9</v>
       </c>
       <c r="C214">
-        <v>122.87243566128919</v>
+        <v>121.73330987420927</v>
       </c>
       <c r="D214">
-        <v>128.61944825900102</v>
+        <v>127.26640354177155</v>
       </c>
     </row>
     <row r="215" spans="1:4" x14ac:dyDescent="0.3">
@@ -3433,10 +3433,10 @@
         <v>10</v>
       </c>
       <c r="C215">
-        <v>113.357203494412</v>
+        <v>112.59083773760791</v>
       </c>
       <c r="D215">
-        <v>114.71733449991211</v>
+        <v>113.67844709301887</v>
       </c>
     </row>
     <row r="216" spans="1:4" x14ac:dyDescent="0.3">
@@ -3447,10 +3447,10 @@
         <v>11</v>
       </c>
       <c r="C216">
-        <v>120.57082688610555</v>
+        <v>119.36406517732429</v>
       </c>
       <c r="D216">
-        <v>128.57420697862889</v>
+        <v>127.11332372486578</v>
       </c>
     </row>
     <row r="217" spans="1:4" x14ac:dyDescent="0.3">
@@ -3461,10 +3461,10 @@
         <v>12</v>
       </c>
       <c r="C217">
-        <v>111.69069969203758</v>
+        <v>111.29673945685165</v>
       </c>
       <c r="D217">
-        <v>113.92075672241478</v>
+        <v>113.35084067163022</v>
       </c>
     </row>
     <row r="218" spans="1:4" x14ac:dyDescent="0.3">
@@ -3475,10 +3475,10 @@
         <v>1</v>
       </c>
       <c r="C218">
-        <v>130.11524710600563</v>
+        <v>129.05862693182343</v>
       </c>
       <c r="D218">
-        <v>135.14915785437597</v>
+        <v>133.93860884872547</v>
       </c>
     </row>
     <row r="219" spans="1:4" x14ac:dyDescent="0.3">
@@ -3489,10 +3489,10 @@
         <v>2</v>
       </c>
       <c r="C219">
-        <v>116.3223183697921</v>
+        <v>115.61559524982279</v>
       </c>
       <c r="D219">
-        <v>122.71051607592193</v>
+        <v>121.80158926844791</v>
       </c>
     </row>
     <row r="220" spans="1:4" x14ac:dyDescent="0.3">
@@ -3503,10 +3503,10 @@
         <v>3</v>
       </c>
       <c r="C220">
-        <v>113.25310510220275</v>
+        <v>111.37814484347381</v>
       </c>
       <c r="D220">
-        <v>117.88430392021309</v>
+        <v>115.93005412238342</v>
       </c>
     </row>
     <row r="221" spans="1:4" x14ac:dyDescent="0.3">
@@ -3517,10 +3517,10 @@
         <v>4</v>
       </c>
       <c r="C221">
-        <v>102.09562862998779</v>
+        <v>100.97814202399941</v>
       </c>
       <c r="D221">
-        <v>100.82511954923628</v>
+        <v>99.67836720920404</v>
       </c>
     </row>
     <row r="222" spans="1:4" x14ac:dyDescent="0.3">
@@ -3531,10 +3531,10 @@
         <v>5</v>
       </c>
       <c r="C222">
-        <v>105.05428636640566</v>
+        <v>104.46210434787858</v>
       </c>
       <c r="D222">
-        <v>101.50001533843437</v>
+        <v>100.77685785367923</v>
       </c>
     </row>
     <row r="223" spans="1:4" x14ac:dyDescent="0.3">
@@ -3545,10 +3545,10 @@
         <v>6</v>
       </c>
       <c r="C223">
-        <v>120.17907327503845</v>
+        <v>119.21169438298865</v>
       </c>
       <c r="D223">
-        <v>118.72546559374508</v>
+        <v>117.59775289669153</v>
       </c>
     </row>
     <row r="224" spans="1:4" x14ac:dyDescent="0.3">
@@ -3559,10 +3559,10 @@
         <v>7</v>
       </c>
       <c r="C224">
-        <v>124.35900311962672</v>
+        <v>123.09581595749549</v>
       </c>
       <c r="D224">
-        <v>122.94821553353027</v>
+        <v>121.44577530782651</v>
       </c>
     </row>
     <row r="225" spans="1:4" x14ac:dyDescent="0.3">
@@ -3573,10 +3573,10 @@
         <v>8</v>
       </c>
       <c r="C225">
-        <v>120.42455386176617</v>
+        <v>119.81714603791028</v>
       </c>
       <c r="D225">
-        <v>117.18973069198921</v>
+        <v>116.48090418861899</v>
       </c>
     </row>
     <row r="226" spans="1:4" x14ac:dyDescent="0.3">
@@ -3587,10 +3587,10 @@
         <v>9</v>
       </c>
       <c r="C226">
-        <v>154.3639527218765</v>
+        <v>153.68748113179885</v>
       </c>
       <c r="D226">
-        <v>153.83985991999424</v>
+        <v>152.95172370833561</v>
       </c>
     </row>
     <row r="227" spans="1:4" x14ac:dyDescent="0.3">
@@ -3601,10 +3601,10 @@
         <v>10</v>
       </c>
       <c r="C227">
-        <v>116.57229996191042</v>
+        <v>115.96898203730355</v>
       </c>
       <c r="D227">
-        <v>115.39867160722267</v>
+        <v>114.60209501050156</v>
       </c>
     </row>
     <row r="228" spans="1:4" x14ac:dyDescent="0.3">
@@ -3615,10 +3615,10 @@
         <v>11</v>
       </c>
       <c r="C228">
-        <v>106.38190444485974</v>
+        <v>105.3314587780463</v>
       </c>
       <c r="D228">
-        <v>106.06008017962027</v>
+        <v>104.86125856606864</v>
       </c>
     </row>
     <row r="229" spans="1:4" x14ac:dyDescent="0.3">
@@ -3629,10 +3629,10 @@
         <v>12</v>
       </c>
       <c r="C229">
-        <v>113.37340735762727</v>
+        <v>112.56950499373438</v>
       </c>
       <c r="D229">
-        <v>116.9237490628539</v>
+        <v>115.93570752151057</v>
       </c>
     </row>
     <row r="230" spans="1:4" x14ac:dyDescent="0.3">
@@ -3643,10 +3643,10 @@
         <v>1</v>
       </c>
       <c r="C230">
-        <v>145.20828759456197</v>
+        <v>144.52665766496807</v>
       </c>
       <c r="D230">
-        <v>140.98028114380421</v>
+        <v>139.96425403713414</v>
       </c>
     </row>
     <row r="231" spans="1:4" x14ac:dyDescent="0.3">
@@ -3657,10 +3657,10 @@
         <v>2</v>
       </c>
       <c r="C231">
-        <v>148.16671858416888</v>
+        <v>147.48300213264932</v>
       </c>
       <c r="D231">
-        <v>145.77674685802927</v>
+        <v>144.82661745529299</v>
       </c>
     </row>
     <row r="232" spans="1:4" x14ac:dyDescent="0.3">
@@ -3671,10 +3671,10 @@
         <v>3</v>
       </c>
       <c r="C232">
-        <v>160.57221680341146</v>
+        <v>159.28977291016236</v>
       </c>
       <c r="D232">
-        <v>162.34613364151207</v>
+        <v>160.72915062379769</v>
       </c>
     </row>
     <row r="233" spans="1:4" x14ac:dyDescent="0.3">
@@ -3685,10 +3685,10 @@
         <v>4</v>
       </c>
       <c r="C233">
-        <v>143.47075803180908</v>
+        <v>142.29600124441353</v>
       </c>
       <c r="D233">
-        <v>146.39938006134571</v>
+        <v>144.8379381031954</v>
       </c>
     </row>
     <row r="234" spans="1:4" x14ac:dyDescent="0.3">
@@ -3699,10 +3699,10 @@
         <v>5</v>
       </c>
       <c r="C234">
-        <v>127.19534335300986</v>
+        <v>125.81350028030027</v>
       </c>
       <c r="D234">
-        <v>123.77764021821704</v>
+        <v>122.20841082088944</v>
       </c>
     </row>
     <row r="235" spans="1:4" x14ac:dyDescent="0.3">
@@ -3713,10 +3713,10 @@
         <v>6</v>
       </c>
       <c r="C235">
-        <v>231.40098490517613</v>
+        <v>231.05573344420372</v>
       </c>
       <c r="D235">
-        <v>220.86233315580014</v>
+        <v>220.1147415136731</v>
       </c>
     </row>
     <row r="236" spans="1:4" x14ac:dyDescent="0.3">
@@ -3727,10 +3727,10 @@
         <v>7</v>
       </c>
       <c r="C236">
-        <v>204.78128542088467</v>
+        <v>204.9228587156837</v>
       </c>
       <c r="D236">
-        <v>189.03332279678318</v>
+        <v>188.7607739232181</v>
       </c>
     </row>
     <row r="237" spans="1:4" x14ac:dyDescent="0.3">
@@ -3741,10 +3741,10 @@
         <v>8</v>
       </c>
       <c r="C237">
-        <v>135.68519014445741</v>
+        <v>134.74163051003325</v>
       </c>
       <c r="D237">
-        <v>136.52293706387516</v>
+        <v>135.32588036274123</v>
       </c>
     </row>
     <row r="238" spans="1:4" x14ac:dyDescent="0.3">
@@ -3755,10 +3755,10 @@
         <v>9</v>
       </c>
       <c r="C238">
-        <v>136.84547874401932</v>
+        <v>135.50843354811593</v>
       </c>
       <c r="D238">
-        <v>139.16231812801496</v>
+        <v>137.52613762559957</v>
       </c>
     </row>
     <row r="239" spans="1:4" x14ac:dyDescent="0.3">
@@ -3769,10 +3769,10 @@
         <v>10</v>
       </c>
       <c r="C239">
-        <v>126.94637674855304</v>
+        <v>126.4360770997193</v>
       </c>
       <c r="D239">
-        <v>122.41145303991097</v>
+        <v>121.611165183971</v>
       </c>
     </row>
     <row r="240" spans="1:4" x14ac:dyDescent="0.3">
@@ -3783,10 +3783,10 @@
         <v>11</v>
       </c>
       <c r="C240">
-        <v>229.82022596501565</v>
+        <v>228.72571947461651</v>
       </c>
       <c r="D240">
-        <v>215.20031347155745</v>
+        <v>213.81809898891979</v>
       </c>
     </row>
     <row r="241" spans="1:4" x14ac:dyDescent="0.3">
@@ -3797,10 +3797,10 @@
         <v>12</v>
       </c>
       <c r="C241">
-        <v>186.08800578367303</v>
+        <v>184.98364258927208</v>
       </c>
       <c r="D241">
-        <v>186.77291695314759</v>
+        <v>185.39123727212629</v>
       </c>
     </row>
     <row r="242" spans="1:4" x14ac:dyDescent="0.3">
@@ -3811,10 +3811,10 @@
         <v>1</v>
       </c>
       <c r="C242">
-        <v>249.48370754733381</v>
+        <v>247.29754147936166</v>
       </c>
       <c r="D242">
-        <v>255.42226394331243</v>
+        <v>252.55679302620661</v>
       </c>
     </row>
     <row r="243" spans="1:4" x14ac:dyDescent="0.3">
@@ -3825,10 +3825,10 @@
         <v>2</v>
       </c>
       <c r="C243">
-        <v>187.10329283151839</v>
+        <v>186.28732769294118</v>
       </c>
       <c r="D243">
-        <v>189.75558084888868</v>
+        <v>188.47482115803516</v>
       </c>
     </row>
     <row r="244" spans="1:4" x14ac:dyDescent="0.3">
@@ -3839,10 +3839,10 @@
         <v>3</v>
       </c>
       <c r="C244">
-        <v>239.18787214329279</v>
+        <v>236.02181683318673</v>
       </c>
       <c r="D244">
-        <v>250.24312859266627</v>
+        <v>246.41324331698056</v>
       </c>
     </row>
     <row r="245" spans="1:4" x14ac:dyDescent="0.3">
@@ -3853,10 +3853,10 @@
         <v>4</v>
       </c>
       <c r="C245">
-        <v>178.23111752982874</v>
+        <v>176.40003710496936</v>
       </c>
       <c r="D245">
-        <v>177.86929869118299</v>
+        <v>175.74835492035791</v>
       </c>
     </row>
     <row r="246" spans="1:4" x14ac:dyDescent="0.3">
@@ -3867,10 +3867,10 @@
         <v>5</v>
       </c>
       <c r="C246">
-        <v>145.512403915791</v>
+        <v>144.09811272073168</v>
       </c>
       <c r="D246">
-        <v>142.73368040790734</v>
+        <v>141.1083830098967</v>
       </c>
     </row>
     <row r="247" spans="1:4" x14ac:dyDescent="0.3">
@@ -3881,10 +3881,10 @@
         <v>6</v>
       </c>
       <c r="C247">
-        <v>173.71892359304385</v>
+        <v>171.71627059966727</v>
       </c>
       <c r="D247">
-        <v>175.60601807063787</v>
+        <v>173.16011188512874</v>
       </c>
     </row>
     <row r="248" spans="1:4" x14ac:dyDescent="0.3">
@@ -3895,10 +3895,10 @@
         <v>7</v>
       </c>
       <c r="C248">
-        <v>167.6048615571174</v>
+        <v>164.9591009516385</v>
       </c>
       <c r="D248">
-        <v>172.37902722802704</v>
+        <v>169.39409745402185</v>
       </c>
     </row>
     <row r="249" spans="1:4" x14ac:dyDescent="0.3">
@@ -3909,10 +3909,10 @@
         <v>8</v>
       </c>
       <c r="C249">
-        <v>141.67123050155007</v>
+        <v>140.62593065113481</v>
       </c>
       <c r="D249">
-        <v>141.83861671080984</v>
+        <v>140.40616251631815</v>
       </c>
     </row>
     <row r="250" spans="1:4" x14ac:dyDescent="0.3">
@@ -3923,10 +3923,10 @@
         <v>9</v>
       </c>
       <c r="C250">
-        <v>159.68989765733457</v>
+        <v>157.65407480504359</v>
       </c>
       <c r="D250">
-        <v>163.53862740693651</v>
+        <v>161.13732682183164</v>
       </c>
     </row>
     <row r="251" spans="1:4" x14ac:dyDescent="0.3">
@@ -3937,10 +3937,10 @@
         <v>10</v>
       </c>
       <c r="C251">
-        <v>145.65026167385273</v>
+        <v>144.50923773473738</v>
       </c>
       <c r="D251">
-        <v>149.87426585880743</v>
+        <v>148.43712882138308</v>
       </c>
     </row>
     <row r="252" spans="1:4" x14ac:dyDescent="0.3">
@@ -3951,10 +3951,10 @@
         <v>11</v>
       </c>
       <c r="C252">
-        <v>162.04753058013239</v>
+        <v>159.90805790363834</v>
       </c>
       <c r="D252">
-        <v>168.10006262308235</v>
+        <v>165.6133808546744</v>
       </c>
     </row>
     <row r="253" spans="1:4" x14ac:dyDescent="0.3">
@@ -3965,10 +3965,10 @@
         <v>12</v>
       </c>
       <c r="C253">
-        <v>150.11890215442429</v>
+        <v>148.16699621114816</v>
       </c>
       <c r="D253">
-        <v>155.61939820513842</v>
+        <v>153.41965253901739</v>
       </c>
     </row>
     <row r="254" spans="1:4" x14ac:dyDescent="0.3">
@@ -3979,10 +3979,10 @@
         <v>1</v>
       </c>
       <c r="C254">
-        <v>180.48141870546138</v>
+        <v>177.71403301677506</v>
       </c>
       <c r="D254">
-        <v>180.20591695454513</v>
+        <v>177.03756043991226</v>
       </c>
     </row>
     <row r="255" spans="1:4" x14ac:dyDescent="0.3">
@@ -3993,10 +3993,10 @@
         <v>2</v>
       </c>
       <c r="C255">
-        <v>128.01718389909237</v>
+        <v>125.99200449060847</v>
       </c>
       <c r="D255">
-        <v>130.83360315712056</v>
+        <v>128.67032390740039</v>
       </c>
     </row>
     <row r="256" spans="1:4" x14ac:dyDescent="0.3">
@@ -4007,10 +4007,10 @@
         <v>3</v>
       </c>
       <c r="C256">
-        <v>184.43191124502565</v>
+        <v>181.6901391229753</v>
       </c>
       <c r="D256">
-        <v>181.56232165874425</v>
+        <v>178.45300349120163</v>
       </c>
     </row>
     <row r="257" spans="1:4" x14ac:dyDescent="0.3">
@@ -4021,10 +4021,10 @@
         <v>4</v>
       </c>
       <c r="C257">
-        <v>167.54926890136545</v>
+        <v>165.02254913208111</v>
       </c>
       <c r="D257">
-        <v>173.5819054444155</v>
+        <v>170.69008989703849</v>
       </c>
     </row>
     <row r="258" spans="1:4" x14ac:dyDescent="0.3">
@@ -4035,10 +4035,10 @@
         <v>5</v>
       </c>
       <c r="C258">
-        <v>173.4820116083192</v>
+        <v>171.49932503519423</v>
       </c>
       <c r="D258">
-        <v>172.62118812581292</v>
+        <v>170.27814833451669</v>
       </c>
     </row>
     <row r="259" spans="1:4" x14ac:dyDescent="0.3">
@@ -4049,10 +4049,10 @@
         <v>6</v>
       </c>
       <c r="C259">
-        <v>166.41611630501833</v>
+        <v>164.91752705189032</v>
       </c>
       <c r="D259">
-        <v>163.58535428065198</v>
+        <v>161.66123999114399</v>
       </c>
     </row>
     <row r="260" spans="1:4" x14ac:dyDescent="0.3">
@@ -4063,10 +4063,10 @@
         <v>7</v>
       </c>
       <c r="C260">
-        <v>232.14825629415978</v>
+        <v>227.49118600017695</v>
       </c>
       <c r="D260">
-        <v>238.62026183298073</v>
+        <v>233.46485885926924</v>
       </c>
     </row>
     <row r="261" spans="1:4" x14ac:dyDescent="0.3">
@@ -4077,10 +4077,10 @@
         <v>8</v>
       </c>
       <c r="C261">
-        <v>174.74392420984989</v>
+        <v>172.16646480818656</v>
       </c>
       <c r="D261">
-        <v>182.23192923553509</v>
+        <v>179.20197418050259</v>
       </c>
     </row>
     <row r="262" spans="1:4" x14ac:dyDescent="0.3">
@@ -4091,10 +4091,10 @@
         <v>9</v>
       </c>
       <c r="C262">
-        <v>196.17743634752517</v>
+        <v>193.32195627597463</v>
       </c>
       <c r="D262">
-        <v>205.84797358840544</v>
+        <v>202.43677937495283</v>
       </c>
     </row>
     <row r="263" spans="1:4" x14ac:dyDescent="0.3">
@@ -4105,10 +4105,10 @@
         <v>10</v>
       </c>
       <c r="C263">
-        <v>216.8102887432153</v>
+        <v>213.58534986857518</v>
       </c>
       <c r="D263">
-        <v>225.95935388896473</v>
+        <v>222.14653979527162</v>
       </c>
     </row>
     <row r="264" spans="1:4" x14ac:dyDescent="0.3">
@@ -4119,10 +4119,10 @@
         <v>11</v>
       </c>
       <c r="C264">
-        <v>251.5484923617006</v>
+        <v>247.13327892405806</v>
       </c>
       <c r="D264">
-        <v>265.36885900799149</v>
+        <v>260.26032300336999</v>
       </c>
     </row>
     <row r="265" spans="1:4" x14ac:dyDescent="0.3">
@@ -4133,10 +4133,10 @@
         <v>12</v>
       </c>
       <c r="C265">
-        <v>222.76299285405602</v>
+        <v>220.3905672413882</v>
       </c>
       <c r="D265">
-        <v>218.35528990905249</v>
+        <v>215.56484341941081</v>
       </c>
     </row>
     <row r="266" spans="1:4" x14ac:dyDescent="0.3">
@@ -4147,10 +4147,10 @@
         <v>1</v>
       </c>
       <c r="C266">
-        <v>246.62372742958269</v>
+        <v>243.99054678658453</v>
       </c>
       <c r="D266">
-        <v>243.71587174201119</v>
+        <v>240.52425388299542</v>
       </c>
     </row>
     <row r="267" spans="1:4" x14ac:dyDescent="0.3">
@@ -4161,10 +4161,10 @@
         <v>2</v>
       </c>
       <c r="C267">
-        <v>175.48518048075968</v>
+        <v>173.79769550537634</v>
       </c>
       <c r="D267">
-        <v>177.86814789992968</v>
+        <v>175.62271910451054</v>
       </c>
     </row>
     <row r="268" spans="1:4" x14ac:dyDescent="0.3">
@@ -4175,10 +4175,10 @@
         <v>3</v>
       </c>
       <c r="C268">
-        <v>244.11788255599978</v>
+        <v>240.87607356546934</v>
       </c>
       <c r="D268">
-        <v>251.85882987638382</v>
+        <v>247.72551396729631</v>
       </c>
     </row>
     <row r="269" spans="1:4" x14ac:dyDescent="0.3">
@@ -4189,10 +4189,10 @@
         <v>4</v>
       </c>
       <c r="C269">
-        <v>193.89965683312334</v>
+        <v>191.28384853645807</v>
       </c>
       <c r="D269">
-        <v>204.92016884478554</v>
+        <v>201.62958381169673</v>
       </c>
     </row>
     <row r="270" spans="1:4" x14ac:dyDescent="0.3">
@@ -4203,10 +4203,10 @@
         <v>5</v>
       </c>
       <c r="C270">
-        <v>226.78967437213407</v>
+        <v>223.54791390088798</v>
       </c>
       <c r="D270">
-        <v>238.27451033946343</v>
+        <v>234.30780715921594</v>
       </c>
     </row>
     <row r="271" spans="1:4" x14ac:dyDescent="0.3">
@@ -4217,10 +4217,10 @@
         <v>6</v>
       </c>
       <c r="C271">
-        <v>327.03523606883186</v>
+        <v>320.4310665201146</v>
       </c>
       <c r="D271">
-        <v>350.03045891586095</v>
+        <v>342.29141784639637</v>
       </c>
     </row>
     <row r="272" spans="1:4" x14ac:dyDescent="0.3">
@@ -4231,10 +4231,10 @@
         <v>7</v>
       </c>
       <c r="C272">
-        <v>252.63888368057439</v>
+        <v>249.39605046668876</v>
       </c>
       <c r="D272">
-        <v>259.85619420747571</v>
+        <v>255.84941993206405</v>
       </c>
     </row>
     <row r="273" spans="1:4" x14ac:dyDescent="0.3">
@@ -4245,10 +4245,10 @@
         <v>8</v>
       </c>
       <c r="C273">
-        <v>294.39700116164812</v>
+        <v>290.65585871241694</v>
       </c>
       <c r="D273">
-        <v>293.19818026548529</v>
+        <v>288.71199422694059</v>
       </c>
     </row>
     <row r="274" spans="1:4" x14ac:dyDescent="0.3">
@@ -4259,10 +4259,10 @@
         <v>9</v>
       </c>
       <c r="C274">
-        <v>240.23526250901344</v>
+        <v>237.37555726286612</v>
       </c>
       <c r="D274">
-        <v>250.50445589675445</v>
+        <v>246.91369974039762</v>
       </c>
     </row>
     <row r="275" spans="1:4" x14ac:dyDescent="0.3">
@@ -4273,10 +4273,10 @@
         <v>10</v>
       </c>
       <c r="C275">
-        <v>203.92827165911427</v>
+        <v>202.25403568557496</v>
       </c>
       <c r="D275">
-        <v>208.95446486857173</v>
+        <v>206.74121446051177</v>
       </c>
     </row>
     <row r="276" spans="1:4" x14ac:dyDescent="0.3">
@@ -4287,10 +4287,10 @@
         <v>11</v>
       </c>
       <c r="C276">
-        <v>246.76265599512021</v>
+        <v>242.60260664166731</v>
       </c>
       <c r="D276">
-        <v>259.36974506762999</v>
+        <v>254.54054849802372</v>
       </c>
     </row>
     <row r="277" spans="1:4" x14ac:dyDescent="0.3">
@@ -4301,10 +4301,10 @@
         <v>12</v>
       </c>
       <c r="C277">
-        <v>234.68649485166162</v>
+        <v>232.09853032302175</v>
       </c>
       <c r="D277">
-        <v>244.62138653328199</v>
+        <v>241.28658052185546</v>
       </c>
     </row>
     <row r="278" spans="1:4" x14ac:dyDescent="0.3">
@@ -4315,10 +4315,10 @@
         <v>1</v>
       </c>
       <c r="C278">
-        <v>194.35931956728533</v>
+        <v>191.721791492481</v>
       </c>
       <c r="D278">
-        <v>199.42663643617422</v>
+        <v>196.33211752982746</v>
       </c>
     </row>
     <row r="279" spans="1:4" x14ac:dyDescent="0.3">
@@ -4329,10 +4329,10 @@
         <v>2</v>
       </c>
       <c r="C279">
-        <v>198.65659597512538</v>
+        <v>196.49325687323858</v>
       </c>
       <c r="D279">
-        <v>198.09657304117113</v>
+        <v>195.59433936842683</v>
       </c>
     </row>
     <row r="280" spans="1:4" x14ac:dyDescent="0.3">
@@ -4343,10 +4343,10 @@
         <v>3</v>
       </c>
       <c r="C280">
-        <v>320.25775855449734</v>
+        <v>318.46485911401209</v>
       </c>
       <c r="D280">
-        <v>311.56790130141098</v>
+        <v>309.28002701120806</v>
       </c>
     </row>
     <row r="281" spans="1:4" x14ac:dyDescent="0.3">
@@ -4357,10 +4357,10 @@
         <v>4</v>
       </c>
       <c r="C281">
-        <v>331.55608303731066</v>
+        <v>328.13263909267255</v>
       </c>
       <c r="D281">
-        <v>334.97665943936892</v>
+        <v>330.9455147178349</v>
       </c>
     </row>
     <row r="282" spans="1:4" x14ac:dyDescent="0.3">
@@ -4371,10 +4371,10 @@
         <v>5</v>
       </c>
       <c r="C282">
-        <v>420.74178132771971</v>
+        <v>415.74335133814083</v>
       </c>
       <c r="D282">
-        <v>424.1125449663939</v>
+        <v>418.14840903798756</v>
       </c>
     </row>
     <row r="283" spans="1:4" x14ac:dyDescent="0.3">
@@ -4385,10 +4385,10 @@
         <v>6</v>
       </c>
       <c r="C283">
-        <v>314.26848288666866</v>
+        <v>309.59230354743733</v>
       </c>
       <c r="D283">
-        <v>325.13351340712103</v>
+        <v>319.73024756513018</v>
       </c>
     </row>
     <row r="284" spans="1:4" x14ac:dyDescent="0.3">
@@ -4399,10 +4399,10 @@
         <v>7</v>
       </c>
       <c r="C284">
-        <v>316.94937274021834</v>
+        <v>313.14659009183742</v>
       </c>
       <c r="D284">
-        <v>308.70496463984534</v>
+        <v>304.37945264277766</v>
       </c>
     </row>
     <row r="285" spans="1:4" x14ac:dyDescent="0.3">
@@ -4413,10 +4413,10 @@
         <v>8</v>
       </c>
       <c r="C285">
-        <v>294.22599297265356</v>
+        <v>289.35592920994884</v>
       </c>
       <c r="D285">
-        <v>304.4329421174711</v>
+        <v>298.75931612051357</v>
       </c>
     </row>
     <row r="286" spans="1:4" x14ac:dyDescent="0.3">
@@ -4427,10 +4427,10 @@
         <v>9</v>
       </c>
       <c r="C286">
-        <v>314.81730891139438</v>
+        <v>309.3344640447869</v>
       </c>
       <c r="D286">
-        <v>328.00333062977825</v>
+        <v>321.67261747880428</v>
       </c>
     </row>
     <row r="287" spans="1:4" x14ac:dyDescent="0.3">
@@ -4441,10 +4441,10 @@
         <v>10</v>
       </c>
       <c r="C287">
-        <v>310.06682621958123</v>
+        <v>306.55527088787562</v>
       </c>
       <c r="D287">
-        <v>313.18465651012497</v>
+        <v>308.82752786407934</v>
       </c>
     </row>
     <row r="288" spans="1:4" x14ac:dyDescent="0.3">
@@ -4455,10 +4455,10 @@
         <v>11</v>
       </c>
       <c r="C288">
-        <v>404.88362010605658</v>
+        <v>397.37945265644953</v>
       </c>
       <c r="D288">
-        <v>421.64403409906873</v>
+        <v>413.02682776263413</v>
       </c>
     </row>
     <row r="289" spans="1:4" x14ac:dyDescent="0.3">
@@ -4469,10 +4469,10 @@
         <v>12</v>
       </c>
       <c r="C289">
-        <v>307.36724934943396</v>
+        <v>302.48026692951555</v>
       </c>
       <c r="D289">
-        <v>315.11383979727316</v>
+        <v>309.47215062685325</v>
       </c>
     </row>
     <row r="290" spans="1:4" x14ac:dyDescent="0.3">
@@ -4483,10 +4483,10 @@
         <v>1</v>
       </c>
       <c r="C290">
-        <v>276.47805036665352</v>
+        <v>271.75653651100254</v>
       </c>
       <c r="D290">
-        <v>283.31878145527418</v>
+        <v>278.12765315761487</v>
       </c>
     </row>
     <row r="291" spans="1:4" x14ac:dyDescent="0.3">
@@ -4497,10 +4497,10 @@
         <v>2</v>
       </c>
       <c r="C291">
-        <v>197.43269227664675</v>
+        <v>195.10681452695769</v>
       </c>
       <c r="D291">
-        <v>200.16798918569179</v>
+        <v>197.44219387975886</v>
       </c>
     </row>
     <row r="292" spans="1:4" x14ac:dyDescent="0.3">
@@ -4511,10 +4511,10 @@
         <v>3</v>
       </c>
       <c r="C292">
-        <v>215.87111120794535</v>
+        <v>212.04868951840004</v>
       </c>
       <c r="D292">
-        <v>221.53261501859527</v>
+        <v>217.3432453229355</v>
       </c>
     </row>
     <row r="293" spans="1:4" x14ac:dyDescent="0.3">
@@ -4525,10 +4525,10 @@
         <v>4</v>
       </c>
       <c r="C293">
-        <v>198.23460321243005</v>
+        <v>193.92232765436131</v>
       </c>
       <c r="D293">
-        <v>206.48369580672235</v>
+        <v>201.92731097465662</v>
       </c>
     </row>
     <row r="294" spans="1:4" x14ac:dyDescent="0.3">
@@ -4539,10 +4539,10 @@
         <v>5</v>
       </c>
       <c r="C294">
-        <v>176.19199724303462</v>
+        <v>173.12515293203327</v>
       </c>
       <c r="D294">
-        <v>179.89884290197725</v>
+        <v>176.62245329444613</v>
       </c>
     </row>
     <row r="295" spans="1:4" x14ac:dyDescent="0.3">
@@ -4553,10 +4553,10 @@
         <v>6</v>
       </c>
       <c r="C295">
-        <v>173.66680625587492</v>
+        <v>170.97337846011976</v>
       </c>
       <c r="D295">
-        <v>181.23428421323726</v>
+        <v>178.25999010709182</v>
       </c>
     </row>
     <row r="296" spans="1:4" x14ac:dyDescent="0.3">
@@ -4567,10 +4567,10 @@
         <v>7</v>
       </c>
       <c r="C296">
-        <v>192.115411161683</v>
+        <v>189.07865457809666</v>
       </c>
       <c r="D296">
-        <v>190.65836251606945</v>
+        <v>187.37054029943536</v>
       </c>
     </row>
     <row r="297" spans="1:4" x14ac:dyDescent="0.3">
@@ -4581,10 +4581,10 @@
         <v>8</v>
       </c>
       <c r="C297">
-        <v>205.43640095535491</v>
+        <v>201.28162501514726</v>
       </c>
       <c r="D297">
-        <v>210.23411722809971</v>
+        <v>205.79203839529433</v>
       </c>
     </row>
     <row r="298" spans="1:4" x14ac:dyDescent="0.3">
@@ -4595,10 +4595,10 @@
         <v>9</v>
       </c>
       <c r="C298">
-        <v>215.6718122403102</v>
+        <v>211.94786926470647</v>
       </c>
       <c r="D298">
-        <v>220.05266910688033</v>
+        <v>216.03591693102638</v>
       </c>
     </row>
     <row r="299" spans="1:4" x14ac:dyDescent="0.3">
@@ -4609,10 +4609,10 @@
         <v>10</v>
       </c>
       <c r="C299">
-        <v>190.87943818953735</v>
+        <v>187.2398433784515</v>
       </c>
       <c r="D299">
-        <v>195.53073812288125</v>
+        <v>191.67183643519695</v>
       </c>
     </row>
     <row r="300" spans="1:4" x14ac:dyDescent="0.3">
@@ -4623,10 +4623,10 @@
         <v>11</v>
       </c>
       <c r="C300">
-        <v>233.44966912494121</v>
+        <v>229.32187991367334</v>
       </c>
       <c r="D300">
-        <v>234.91654455772948</v>
+        <v>230.38378229584893</v>
       </c>
     </row>
     <row r="301" spans="1:4" x14ac:dyDescent="0.3">
@@ -4637,10 +4637,10 @@
         <v>12</v>
       </c>
       <c r="C301">
-        <v>263.88593707362116</v>
+        <v>258.40928353024697</v>
       </c>
       <c r="D301">
-        <v>267.81439306043461</v>
+        <v>262.10643072401189</v>
       </c>
     </row>
     <row r="302" spans="1:4" x14ac:dyDescent="0.3">
@@ -4651,10 +4651,10 @@
         <v>1</v>
       </c>
       <c r="C302">
-        <v>226.45670542820747</v>
+        <v>221.70366663726656</v>
       </c>
       <c r="D302">
-        <v>233.86611032758714</v>
+        <v>228.7356125041467</v>
       </c>
     </row>
     <row r="303" spans="1:4" x14ac:dyDescent="0.3">
@@ -4665,10 +4665,10 @@
         <v>2</v>
       </c>
       <c r="C303">
-        <v>178.5644403903801</v>
+        <v>175.82258801196468</v>
       </c>
       <c r="D303">
-        <v>186.51485304517678</v>
+        <v>183.60577274392165</v>
       </c>
     </row>
     <row r="304" spans="1:4" x14ac:dyDescent="0.3">
@@ -4679,10 +4679,10 @@
         <v>3</v>
       </c>
       <c r="C304">
-        <v>302.42345510638739</v>
+        <v>298.18836502477018</v>
       </c>
       <c r="D304">
-        <v>305.92876637859626</v>
+        <v>301.13148802649499</v>
       </c>
     </row>
     <row r="305" spans="1:4" x14ac:dyDescent="0.3">
@@ -4693,10 +4693,10 @@
         <v>4</v>
       </c>
       <c r="C305">
-        <v>273.42980674046532</v>
+        <v>269.50295954734969</v>
       </c>
       <c r="D305">
-        <v>288.33916396727528</v>
+        <v>283.87813635155572</v>
       </c>
     </row>
     <row r="306" spans="1:4" x14ac:dyDescent="0.3">
@@ -4707,10 +4707,10 @@
         <v>5</v>
       </c>
       <c r="C306">
-        <v>281.12795372087572</v>
+        <v>275.87421047554949</v>
       </c>
       <c r="D306">
-        <v>290.83328593730448</v>
+        <v>285.0584566904991</v>
       </c>
     </row>
     <row r="307" spans="1:4" x14ac:dyDescent="0.3">
@@ -4721,10 +4721,10 @@
         <v>6</v>
       </c>
       <c r="C307">
-        <v>252.80778671715754</v>
+        <v>248.01935491968658</v>
       </c>
       <c r="D307">
-        <v>265.64971282286695</v>
+        <v>260.46048676432588</v>
       </c>
     </row>
     <row r="308" spans="1:4" x14ac:dyDescent="0.3">
@@ -4735,10 +4735,10 @@
         <v>7</v>
       </c>
       <c r="C308">
-        <v>298.31313276205225</v>
+        <v>292.80632953196897</v>
       </c>
       <c r="D308">
-        <v>305.81025857980325</v>
+        <v>299.89352772004656</v>
       </c>
     </row>
     <row r="309" spans="1:4" x14ac:dyDescent="0.3">
@@ -4749,10 +4749,10 @@
         <v>8</v>
       </c>
       <c r="C309">
-        <v>239.61456649887785</v>
+        <v>235.83155122180185</v>
       </c>
       <c r="D309">
-        <v>242.08024728261972</v>
+        <v>237.97363473130594</v>
       </c>
     </row>
     <row r="310" spans="1:4" x14ac:dyDescent="0.3">
@@ -4763,10 +4763,10 @@
         <v>9</v>
       </c>
       <c r="C310">
-        <v>252.61450778808256</v>
+        <v>248.85490514799466</v>
       </c>
       <c r="D310">
-        <v>254.32246218163783</v>
+        <v>250.29016868488179</v>
       </c>
     </row>
     <row r="311" spans="1:4" x14ac:dyDescent="0.3">
@@ -4777,10 +4777,10 @@
         <v>10</v>
       </c>
       <c r="C311">
-        <v>269.05464705747062</v>
+        <v>265.08245600682665</v>
       </c>
       <c r="D311">
-        <v>269.38167308003312</v>
+        <v>265.11421714658564</v>
       </c>
     </row>
     <row r="312" spans="1:4" x14ac:dyDescent="0.3">
@@ -4791,10 +4791,10 @@
         <v>11</v>
       </c>
       <c r="C312">
-        <v>316.95929795087574</v>
+        <v>311.34886671932895</v>
       </c>
       <c r="D312">
-        <v>327.42631946284712</v>
+        <v>321.16088382891911</v>
       </c>
     </row>
     <row r="313" spans="1:4" x14ac:dyDescent="0.3">
@@ -4805,10 +4805,10 @@
         <v>12</v>
       </c>
       <c r="C313">
-        <v>244.35662154604373</v>
+        <v>239.85428870142027</v>
       </c>
       <c r="D313">
-        <v>256.12586888296181</v>
+        <v>251.24348258672131</v>
       </c>
     </row>
     <row r="314" spans="1:4" x14ac:dyDescent="0.3">
@@ -4819,10 +4819,10 @@
         <v>1</v>
       </c>
       <c r="C314">
-        <v>220.85253806352262</v>
+        <v>217.19917934501004</v>
       </c>
       <c r="D314">
-        <v>229.43470907073205</v>
+        <v>225.26656526378653</v>
       </c>
     </row>
     <row r="315" spans="1:4" x14ac:dyDescent="0.3">
@@ -4833,10 +4833,10 @@
         <v>2</v>
       </c>
       <c r="C315">
-        <v>246.0730616199894</v>
+        <v>242.14083289899528</v>
       </c>
       <c r="D315">
-        <v>263.5794920922101</v>
+        <v>258.79599600111817</v>
       </c>
     </row>
     <row r="316" spans="1:4" x14ac:dyDescent="0.3">
@@ -4847,10 +4847,10 @@
         <v>3</v>
       </c>
       <c r="C316">
-        <v>320.16716632020103</v>
+        <v>313.65303642877439</v>
       </c>
       <c r="D316">
-        <v>339.98251718731456</v>
+        <v>332.43815207051563</v>
       </c>
     </row>
     <row r="317" spans="1:4" x14ac:dyDescent="0.3">
@@ -4861,10 +4861,10 @@
         <v>4</v>
       </c>
       <c r="C317">
-        <v>259.84356673092952</v>
+        <v>255.37935006332191</v>
       </c>
       <c r="D317">
-        <v>284.48181610332347</v>
+        <v>279.14671652092602</v>
       </c>
     </row>
     <row r="318" spans="1:4" x14ac:dyDescent="0.3">
@@ -4875,10 +4875,10 @@
         <v>5</v>
       </c>
       <c r="C318">
-        <v>214.75975620400095</v>
+        <v>211.34613104174466</v>
       </c>
       <c r="D318">
-        <v>214.06243660530828</v>
+        <v>210.26862995939837</v>
       </c>
     </row>
     <row r="319" spans="1:4" x14ac:dyDescent="0.3">
@@ -4889,10 +4889,10 @@
         <v>6</v>
       </c>
       <c r="C319">
-        <v>225.56617001966492</v>
+        <v>221.45846707536063</v>
       </c>
       <c r="D319">
-        <v>238.49183581826145</v>
+        <v>233.88805610467941</v>
       </c>
     </row>
     <row r="320" spans="1:4" x14ac:dyDescent="0.3">
@@ -4903,10 +4903,10 @@
         <v>7</v>
       </c>
       <c r="C320">
-        <v>195.2059297359298</v>
+        <v>191.73126185560224</v>
       </c>
       <c r="D320">
-        <v>203.27500104337264</v>
+        <v>199.42975382805719</v>
       </c>
     </row>
     <row r="321" spans="1:4" x14ac:dyDescent="0.3">
@@ -4917,10 +4917,10 @@
         <v>8</v>
       </c>
       <c r="C321">
-        <v>178.50173248162628</v>
+        <v>175.50515471617388</v>
       </c>
       <c r="D321">
-        <v>188.62060206145676</v>
+        <v>185.19143087835747</v>
       </c>
     </row>
     <row r="322" spans="1:4" x14ac:dyDescent="0.3">
@@ -4931,10 +4931,10 @@
         <v>9</v>
       </c>
       <c r="C322">
-        <v>204.47967522082536</v>
+        <v>200.63847820558766</v>
       </c>
       <c r="D322">
-        <v>213.42144221891957</v>
+        <v>209.20313504978304</v>
       </c>
     </row>
     <row r="323" spans="1:4" x14ac:dyDescent="0.3">
@@ -4945,10 +4945,10 @@
         <v>10</v>
       </c>
       <c r="C323">
-        <v>193.08905907205227</v>
+        <v>190.44380861220509</v>
       </c>
       <c r="D323">
-        <v>199.45899664045706</v>
+        <v>196.60018930585051</v>
       </c>
     </row>
     <row r="324" spans="1:4" x14ac:dyDescent="0.3">
@@ -4959,10 +4959,10 @@
         <v>11</v>
       </c>
       <c r="C324">
-        <v>211.23745638540998</v>
+        <v>207.97210385954006</v>
       </c>
       <c r="D324">
-        <v>221.23947372757539</v>
+        <v>217.60537964071216</v>
       </c>
     </row>
     <row r="325" spans="1:4" x14ac:dyDescent="0.3">
@@ -4973,10 +4973,10 @@
         <v>12</v>
       </c>
       <c r="C325">
-        <v>227.3862800587525</v>
+        <v>223.02369978288257</v>
       </c>
       <c r="D325">
-        <v>250.09286943195727</v>
+        <v>245.19148693755091</v>
       </c>
     </row>
     <row r="326" spans="1:4" x14ac:dyDescent="0.3">
@@ -4987,10 +4987,10 @@
         <v>1</v>
       </c>
       <c r="C326">
-        <v>244.54239744865757</v>
+        <v>239.69746810159759</v>
       </c>
       <c r="D326">
-        <v>263.24541202160128</v>
+        <v>257.70930704259808</v>
       </c>
     </row>
     <row r="327" spans="1:4" x14ac:dyDescent="0.3">
@@ -5001,10 +5001,10 @@
         <v>2</v>
       </c>
       <c r="C327">
-        <v>170.41360779469005</v>
+        <v>167.97191002157467</v>
       </c>
       <c r="D327">
-        <v>182.00786071904193</v>
+        <v>179.2567291827761</v>
       </c>
     </row>
     <row r="328" spans="1:4" x14ac:dyDescent="0.3">
@@ -5015,10 +5015,10 @@
         <v>3</v>
       </c>
       <c r="C328">
-        <v>182.39498135733737</v>
+        <v>179.48343979338063</v>
       </c>
       <c r="D328">
-        <v>189.89753721535533</v>
+        <v>186.43984252319487</v>
       </c>
     </row>
     <row r="329" spans="1:4" x14ac:dyDescent="0.3">
@@ -5029,10 +5029,10 @@
         <v>4</v>
       </c>
       <c r="C329">
-        <v>173.91542382619409</v>
+        <v>171.26273444832714</v>
       </c>
       <c r="D329">
-        <v>178.14568033070077</v>
+        <v>175.24803318902559</v>
       </c>
     </row>
     <row r="330" spans="1:4" x14ac:dyDescent="0.3">
@@ -5043,10 +5043,10 @@
         <v>5</v>
       </c>
       <c r="C330">
-        <v>187.36681591320436</v>
+        <v>184.16442051498547</v>
       </c>
       <c r="D330">
-        <v>191.40401142926817</v>
+        <v>187.8818622780019</v>
       </c>
     </row>
     <row r="331" spans="1:4" x14ac:dyDescent="0.3">
@@ -5057,10 +5057,10 @@
         <v>6</v>
       </c>
       <c r="C331">
-        <v>175.53900858089676</v>
+        <v>173.4343793636483</v>
       </c>
       <c r="D331">
-        <v>175.6118807949544</v>
+        <v>173.34831850534741</v>
       </c>
     </row>
     <row r="332" spans="1:4" x14ac:dyDescent="0.3">
@@ -5071,10 +5071,10 @@
         <v>7</v>
       </c>
       <c r="C332">
-        <v>233.2874927222027</v>
+        <v>229.01164085374731</v>
       </c>
       <c r="D332">
-        <v>244.8646092924179</v>
+        <v>240.14298761173242</v>
       </c>
     </row>
     <row r="333" spans="1:4" x14ac:dyDescent="0.3">
@@ -5085,10 +5085,10 @@
         <v>8</v>
       </c>
       <c r="C333">
-        <v>194.5871068045075</v>
+        <v>191.11852025074197</v>
       </c>
       <c r="D333">
-        <v>202.19846658538549</v>
+        <v>198.43875142744884</v>
       </c>
     </row>
     <row r="334" spans="1:4" x14ac:dyDescent="0.3">
@@ -5099,10 +5099,10 @@
         <v>9</v>
       </c>
       <c r="C334">
-        <v>205.76488066628005</v>
+        <v>202.17762371454685</v>
       </c>
       <c r="D334">
-        <v>211.62606641729235</v>
+        <v>207.69401952965862</v>
       </c>
     </row>
     <row r="335" spans="1:4" x14ac:dyDescent="0.3">
@@ -5113,10 +5113,10 @@
         <v>10</v>
       </c>
       <c r="C335">
-        <v>208.60713973687507</v>
+        <v>204.92841907731767</v>
       </c>
       <c r="D335">
-        <v>215.30477819474424</v>
+        <v>211.2685233870294</v>
       </c>
     </row>
     <row r="336" spans="1:4" x14ac:dyDescent="0.3">
@@ -5127,10 +5127,10 @@
         <v>11</v>
       </c>
       <c r="C336">
-        <v>286.1715654702279</v>
+        <v>282.59265973990313</v>
       </c>
       <c r="D336">
-        <v>281.98094916909332</v>
+        <v>278.07294571676158</v>
       </c>
     </row>
     <row r="337" spans="1:4" x14ac:dyDescent="0.3">
@@ -5141,10 +5141,10 @@
         <v>12</v>
       </c>
       <c r="C337">
-        <v>331.88483601953277</v>
+        <v>327.57503709446769</v>
       </c>
       <c r="D337">
-        <v>336.72508880396026</v>
+        <v>331.62204875429507</v>
       </c>
     </row>
     <row r="338" spans="1:4" x14ac:dyDescent="0.3">
@@ -5155,10 +5155,10 @@
         <v>1</v>
       </c>
       <c r="C338">
-        <v>312.89797654305369</v>
+        <v>309.10736817577009</v>
       </c>
       <c r="D338">
-        <v>309.68000775827858</v>
+        <v>305.46919091963042</v>
       </c>
     </row>
     <row r="339" spans="1:4" x14ac:dyDescent="0.3">
@@ -5169,10 +5169,10 @@
         <v>2</v>
       </c>
       <c r="C339">
-        <v>330.80587857445784</v>
+        <v>327.70756615697451</v>
       </c>
       <c r="D339">
-        <v>319.9595703778059</v>
+        <v>316.44004318685893</v>
       </c>
     </row>
     <row r="340" spans="1:4" x14ac:dyDescent="0.3">
@@ -5183,10 +5183,10 @@
         <v>3</v>
       </c>
       <c r="C340">
-        <v>473.86809065435637</v>
+        <v>468.84279693223056</v>
       </c>
       <c r="D340">
-        <v>459.37896184566586</v>
+        <v>453.55882764743643</v>
       </c>
     </row>
     <row r="341" spans="1:4" x14ac:dyDescent="0.3">
@@ -5197,10 +5197,10 @@
         <v>4</v>
       </c>
       <c r="C341">
-        <v>628.11525280876424</v>
+        <v>623.35204539842107</v>
       </c>
       <c r="D341">
-        <v>584.65212754255742</v>
+        <v>578.59879377273535</v>
       </c>
     </row>
     <row r="342" spans="1:4" x14ac:dyDescent="0.3">
@@ -5211,10 +5211,10 @@
         <v>5</v>
       </c>
       <c r="C342">
-        <v>517.2872310382146</v>
+        <v>511.6903036177236</v>
       </c>
       <c r="D342">
-        <v>484.71578432716711</v>
+        <v>478.0368720970759</v>
       </c>
     </row>
     <row r="343" spans="1:4" x14ac:dyDescent="0.3">
@@ -5225,10 +5225,10 @@
         <v>6</v>
       </c>
       <c r="C343">
-        <v>371.66034760749568</v>
+        <v>368.5934566761253</v>
       </c>
       <c r="D343">
-        <v>358.55888236939552</v>
+        <v>354.56811696009703</v>
       </c>
     </row>
     <row r="344" spans="1:4" x14ac:dyDescent="0.3">
@@ -5239,10 +5239,10 @@
         <v>7</v>
       </c>
       <c r="C344">
-        <v>412.35583625732295</v>
+        <v>406.88756978050156</v>
       </c>
       <c r="D344">
-        <v>395.34453389485452</v>
+        <v>388.65482755686861</v>
       </c>
     </row>
     <row r="345" spans="1:4" x14ac:dyDescent="0.3">
@@ -5253,10 +5253,10 @@
         <v>8</v>
       </c>
       <c r="C345">
-        <v>348.55903429722025</v>
+        <v>343.33905971926498</v>
       </c>
       <c r="D345">
-        <v>332.07479705017988</v>
+        <v>325.91192997446291</v>
       </c>
     </row>
     <row r="346" spans="1:4" x14ac:dyDescent="0.3">
@@ -5267,10 +5267,10 @@
         <v>9</v>
       </c>
       <c r="C346">
-        <v>311.53140085687312</v>
+        <v>308.47823098184006</v>
       </c>
       <c r="D346">
-        <v>297.6189053615164</v>
+        <v>294.03603477909218</v>
       </c>
     </row>
     <row r="347" spans="1:4" x14ac:dyDescent="0.3">
@@ -5281,14 +5281,28 @@
         <v>10</v>
       </c>
       <c r="C347">
-        <v>389.43001518245899</v>
+        <v>404.87305248366022</v>
       </c>
       <c r="D347">
-        <v>404.56293470540879</v>
-      </c>
-    </row>
-    <row r="349" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A349" t="s">
+        <v>413.51659879866469</v>
+      </c>
+    </row>
+    <row r="348" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A348">
+        <v>2025</v>
+      </c>
+      <c r="B348">
+        <v>11</v>
+      </c>
+      <c r="C348">
+        <v>371.09535172579444</v>
+      </c>
+      <c r="D348">
+        <v>373.28416010013092</v>
+      </c>
+    </row>
+    <row r="350" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A350" t="s">
         <v>4</v>
       </c>
     </row>
